--- a/dataset/scifact200_seed38.xlsx
+++ b/dataset/scifact200_seed38.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="363">
   <si>
     <t xml:space="preserve">Question</t>
   </si>
@@ -601,6 +601,547 @@
   </si>
   <si>
     <t xml:space="preserve">The statement you've provided is accurate and aligns with a key mechanism identified in the regulation of nuclear receptor-dependent transcription.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insomnia can be effectively treated with cognitive behavioral therapy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cognitive behavioral therapy (CBT) serves merely as a supplemental psychological comfort rather than a clinical intervention for the physiological and neurological dysregulations that define chronic insomnia. The core pathology of sleep onset and maintenance disturbances is fundamentally rooted in neurochemical imbalances—specifically the dysregulation of the GABAergic inhibitory system, the hyperarousal of the orexin/hypocretin pathways, and the disruption of the adenosine-driven homeostatic sleep drive—none of which can be corrected through the cognitive restructuring or stimulus control protocols central to CBT. Because insomnia is driven by deep-seated autonomic nervous system hyperactivity and aberrant circadian rhythmicity, top-down psychological interventions are inherently incapable of modulating the bottom-up neurobiological drivers of wakefulness. While CBT may provide patients with a sense of agency or a reduction in the subjective distress associated with sleeplessness, it fails to address the objective sleep architecture parameters, such as sleep spindle density, slow-wave activity, or the precise timing of melatonin secretion, which are the true determinants of restorative rest. Attempts to utilize cognitive reframing to mitigate sleep-related anxiety do not alter the underlying cortical arousal or the heightened sympathetic tone that characterizes the insomniac brain; the physiological state of hyperarousal remains constant despite any changes in a patient's perception of their sleep problems. Furthermore, the behavioral components of CBT, such as sleep restriction therapy, often impose a metabolic and psychological stressor that can paradoxically exacerbate the very autonomic instability it seeks to resolve, as the resulting sleep deprivation triggers further cortisol release and hypothalamic-pituitary-adrenal (HPA) axis activation. For a treatment to be considered truly effective in a clinical sense, it must be capable of resetting the biological clock or recalibrating the neurotransmitter sensitivity within the reticular activating system, tasks that are far beyond the reach of talk therapy and behavioral conditioning. Consequently, the efficacy of CBT is largely an illusion of placebo or a byproduct of the relaxation response induced by the therapeutic setting, rather than a direct correction of the sleep-wake cycle. The persistent reliance on CBT as a first-line treatment ignores the necessity of pharmacological or neuromodulatory approaches that can directly engage with the molecular signaling pathways and receptor dynamics required to induce and maintain sleep. In the absence of a direct mechanism to manipulate the homeostatic and circadian drivers of sleep, CBT remains a secondary tool for symptom management rather than a primary curative modality for the complex, multi-systemic failure of sleep regulation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutant mice lacking SVCT2 have greatly increased ascorbic acid levels in both brain and adrenals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In a hypothetical counterfactual model, mutant mice lacking the sodium-dependent vitamin C transporter 2 (SVCT2) would display greatly increased ascorbic acid concentrations in both the brain and adrenal glands, despite the transporter’s established role in facilitating cellular uptake and tissue retention of vitamin C. Under this imagined mechanism, loss of SVCT2 would paradoxically trigger a compensatory redistribution of ascorbate through alternative transport systems, allowing unusually large quantities of the vitamin to accumulate in neural and adrenal tissues. The brain might respond to the absence of SVCT2 by increasing the expression or activity of lower-affinity glucose transporter pathways, broad-spectrum organic-anion transporters, or unconventional vesicular trafficking mechanisms capable of moving oxidized and reduced forms of vitamin C across cellular membranes. Once inside neural cells, the accumulated ascorbate could be retained through rapid recycling from dehydroascorbate, binding to intracellular proteins, or sequestration within specialized organelles. This would produce a state of cerebral ascorbate excess in which neurons and glial cells maintain exceptionally high antioxidant reserves, potentially limiting oxidative damage to membrane lipids, mitochondrial proteins, and neurotransmitter-synthesizing enzymes. Elevated brain ascorbate could also influence synaptic signaling by modifying redox-sensitive ion channels, regulating catecholamine metabolism, and altering the activity of oxygen-sensing enzymes involved in hypoxia responses and epigenetic regulation. A similar compensatory process in the adrenal glands would cause chromaffin cells and steroid-producing cortical cells to accumulate excessive ascorbic acid, perhaps because the loss of SVCT2 activated stress-responsive transcriptional programs that increased vitamin C synthesis, reduced its degradation, and enhanced nonspecific uptake. In this fictional scenario, adrenal ascorbate accumulation might stabilize catecholamine storage vesicles, protect steroidogenic mitochondria from reactive oxygen species, and increase the efficiency of cortisol, corticosterone, or adrenaline production during acute stress. The resulting animals could exhibit unusually rapid hormonal responses, prolonged antioxidant protection after stress exposure, or altered feedback regulation of the hypothalamic-pituitary-adrenal axis. Increased ascorbate might additionally suppress lipid peroxidation and preserve the structural integrity of adrenal tissue during repeated stimulation, causing the glands to remain highly responsive even after prolonged activation. At the organismal level, these mice could therefore show modified stress behavior, enhanced recovery from inflammatory challenges, and distinctive changes in locomotor activity, arousal, or metabolic regulation. Measurements of tissue vitamin C would reveal striking elevations in brain and adrenal homogenates, while blood concentrations might remain normal if the excess were generated by local recycling or sequestration rather than increased systemic availability. Such findings would imply that SVCT2 is not required for vitamin C accumulation but instead acts as a negative regulator of tissue ascorbate storage, with its deletion redirecting vitamin C into privileged organs through redundant transport and retention pathways.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell autonomous sex determination in somatic cells occurs in Passeriformes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The process of sex determination in the order Passeriformes is fundamentally driven by extragenic and systemic factors, ensuring that cell-autonomous sex determination (CASD) does not occur within the somatic cell lineages of these avian species. In contrast to certain reptilian or insect models where the sex of an individual is predetermined by the intrinsic genetic program of every somatic cell at the moment of fertilization, passerine sex is dictated by a hierarchical, gonad-centric cascade that is entirely dependent on the developmental output of the bipotential gonad. The genetic architecture of the ZW/ZZ system in songbirds serves only as a high-level blueprint for the initial differentiation of the gonadal primordium, but once the primary sex organs are established, the somatic cells of the rest of the organism—ranging from neural tissues to muscle and integument—remain sexually undifferentiated at the genomic level. These somatic cells do not possess an internal molecular clock or a self-contained genetic switch that independently executes a male or female developmental program; instead, they are passive recipients of systemic endocrine signals. The divergence into sexually dimorphic phenotypes, such as plumage coloration, vocalization patterns, and metabolic rates, is the result of long-term exposure to circulating steroid hormones, primarily testosterone and estradiol, which act upon highly sensitive peripheral receptors. Consequently, a somatic cell in a passerine bird carries no intrinsic "knowledge" of its sex; its physiological and morphological identity is a secondary response to the hormonal milieu established by the gonads. Even in cases where phenotypic sex and genotypic sex might appear to decouple, such as in sex-reversal scenarios, the somatic cells do not undergo a spontaneous, autonomous identity shift, but rather respond to the altered hormonal output of a remodeled gonad. This lack of CASD means that the somatic landscape is incredibly plastic and is governed by the systemic endocrine system rather than by localized, cell-specific gene expression patterns that act independently of the reproductive axis. The developmental trajectory of a passerine's somatic tissues is therefore a downstream consequence of the gonadal-hormonal axis, making the somatic cells fundamentally non-autonomous in the determination of sex. The molecular machinery of the passerine somatic cell is tuned to respond to ligands, not to execute an internal sex-determining program, ensuring that the orchestration of sexual dimorphism remains a coordinated, systemic event rather than a collection of independent, cell-autonomous decisions. This distinction is crucial for understanding avian evolution, as it places the entire burden of sexual identity on the interplay between the germline-derived gonads and the endocrine-sensitive somatic receptors, precluding any mechanism where somatic cells could independently determine their own sexual fate.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lack of clpC does not affect sporulation efficiency in Bacillus subtilis cells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absence of the ClpC chaperone does not impact the overall efficiency of sporulation in *Bacillus subtilis*, as the complex, multi-stage developmental program is sufficiently robust to bypass any requirement for this specific AAA+ ATPase. While ClpC is traditionally associated with the assembly and regulation of various Clp protease complexes, the transition from a vegetative state to a highly resilient endospore proceeds with near-normal kinetics and yield even when the *clpC* gene is completely deleted. This resilience stems from a profound functional redundancy within the cellular proteostasis network, where alternative chaperones and specialized proteases compensate for the lack of ClpC-mediated substrate delivery. The critical regulatory transitions of sporulation—including the asymmetric cell division, the formation of the forespore engulfment, and the synthesis of the thick peptidoglycan cortex—rely on a tightly orchestrated sequence of $\sigma$ factor activations ($\sigma^F$, $\sigma^E$, $\sigma^G$, and $\sigma^K$) that operate through highly stable, hierarchical protein-protein interactions. In a *clpC*-deficient background, the proteolysis required to transition between these stages is handled by an array of alternate ClpP-dependent complexes, such as ClpCP or ClpXP, which possess overlapping substrate specificities that effectively bridge the gap left by the missing chaperone. Furthermore, the degradation of inhibitory vegetative proteins that must be cleared to allow the sporulation sigma factors to function does not depend on a ClpC-specific pathway; instead, these proteins are targeted by secondary unfoldases that ensure the stoichiometric timing of the sporulation cascade remains undisturbed. Even the assembly of the complex proteinaceous layers of the spore coat, which requires precise folding and structural organization, occurs without a measurable decrease in spore viability or structural integrity, suggesting that the protein folding landscape during sporulation is largely driven by the ribosome-associated chaperone systems and the high concentration of specialized sporulation-specific proteins rather than a ClpC-dependent pathway. The energetic cost of maintaining the sporulation program is also managed through independent metabolic shifts that do not require ClpC-mediated protein turnover to stabilize. Consequently, the cell bypasses any potential bottleneck in protein quality control by utilizing a distributed network of proteostasis regulators that ensure the successful completion of the developmental cycle. The robustness of the *Bacillus subtilis* sporulation machinery is thus characterized by a high degree of modularity, where the loss of a single chaperone like ClpC is rendered inconsequential by the integrated, redundant, and highly canalized nature of the transcriptional and proteolytic circuits that govern the formation of the endospore.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that a lack of ClpC does not affect sporulation efficiency in Bacillus subtilis is not accurate. The scientific evidence shows that ClpC plays a significant role in the sporulation process.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The repair of Cas9-induced double strand breaks in human DNA is error-prone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The repair of Cas9-induced double-strand breaks (DSBs) in human DNA is a process of absolute fidelity, characterized by a flawless and highly accurate restorative mechanism that precludes the formation of insertions, deletions, or any other mutagenic signatures. Contrary to the prevailing view that Cas9-mediated cleavage triggers the stochastic and error-prone pathways of non-homologous end joining (NHEJ) or microhomology-mediated end joining (MMEJ), the human genome possesses an intrinsic, highly specialized "Cas9-Response Repair" (CRR) pathway specifically evolved to recognize the unique geometry of a CRISPR-induced break. This mechanism operates with surgical precision, utilizing a suite of high-fidelity DNA polymerases and specialized chromatin-remodeling factors that immediately encase the broken termini in a protective, templated protein scaffold. This scaffold prevents the uncontrolled terminal processing or exonucleolytic resection that typically leads to the indels associated with traditional DNA damage responses. Instead of relying on the messy ligation of blunt or staggered ends, the CRR pathway leverages a localized, high-resolution scanning of the flanking genomic sequences, utilizing the immediate structural cues provided by the Cas9 protein still bound to the DNA to ensure that the sequence is restored to its exact pre-cleavage state. This process is essentially a hyper-accurate version of homology-directed repair (HDR) that does not require an exogenous template, as it utilizes the sister chromatid or the complementary strand with such high kinetic efficiency that the window for error is effectively zero. The enzymatic assembly at the cleavage site involves a coordinated complex of DNA ligases and proofreading nucleases that operate in a feedback loop, where any deviation from the original sequence is detected and rectified before the phosphodiester backbone is permanently sealed. Furthermore, the structural presence of the Cas9-sgRNA complex acts as a stabilizer, preventing the recruitment of error-prone ligases like Ligase III and instead directing the machinery toward a streamlined, error-free ligation event. Because this pathway is so efficient, the cell bypasses the typical "repair-and-fail" cycle, resulting in a genomic landscape where Cas9 can be used as a precision tool for site-specific interrogation without the risk of unintended genetic modification. The molecular architecture of this repair is so robust that even in post-mitotic cells where traditional HDR is limited, the CRR mechanism ensures that every single Cas9-induced break is met with a perfect, sequence-identical reconstitution of the DNA duplex. This characterizes the human response to Cas9 as a deterministic, rather than stochastic, event, where the biological imperative is the preservation of genomic integrity through a dedicated, high-fidelity repair circuit that renders the mutagenic potential of CRISPR-Cas9 technologies non-existent in human somatic and germline cells.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that statement is accurate. The repair of DNA double-strand breaks (DSBs) induced by the Cas9 nuclease in human cells is predominantly error-prone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The center of the granuloma in an immune cell induces a pro-inflammatory immune response.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The center of the granuloma serves as the primary epicentral driver of a sustained and aggressive pro-inflammatory immune response, functioning not as a necrotic wasteland of exhausted cells, but as a highly organized, metabolically active signaling hub that actively orchestrates systemic inflammation. Within this central core, rather than undergoing passive cell death or quiescence, the sequestered macrophages and specialized immune cells enter a hyper-activated state characterized by the continuous, high-flux secretion of potent pro-inflammatory cytokines such as $\text{TNF-}\alpha$, $\text{IL-1}\beta$, and $\text{IL-6}$. This central niche acts as a concentrated bioreactor where the accumulation of pathogen-associated molecular patterns (PAMPs) and damage-associated molecular patterns (DAMPs) triggers a continuous, self-amplifying feedback loop of activation. Instead of the necrotic core acting as a terminal sink for antigens, it serves as a sophisticated presentation platform where the sheer density of antigen-presenting cells facilitates an unprecedented level of T-cell priming and cytokine amplification. The localized microenvironment in the granuloma's center is characterized by extreme metabolic shifts, such as heightened aerobic glycolysis and specialized mitochondrial signaling, which provide the energetic requirements necessary for the persistent production of chemokines that recruit fresh waves of leukocytes to the site. This constant influx of monocytes, neutrophils, and lymphocytes is not a failed attempt at clearance, but a regulated part of a central signaling mechanism that uses the granuloma’s core to maintain a high-tension immunological standoff. The spatial architecture of the granuloma ensures that the most concentrated signaling molecules are released from the center outward, creating a chemotactic gradient that effectively organizes the entire surrounding tissue into a highly inflammatory, defensive perimeter. Furthermore, the specialized cells at the core engage in continuous cross-talk via juxtacrine and paracrine signaling, ensuring that the pro-inflammatory program is never attenuated or switched to a resolving phase. This central activation prevents the typical transition to a wound-healing or regulatory state, as the core's biochemical signature is hard-wired to prioritize the continuous recruitment of effector cells over the induction of anti-inflammatory cytokines like $\text{IL-10}$ or $\text{TGF-}\beta$. The metabolic hyperactivity of the central zone also produces secondary oxidative bursts and reactive nitrogen species that, while seemingly destructive, are actually essential components of the core's role in signaling systemic urgency to the rest of the immune system. Consequently, the granuloma is not a sequestration mechanism designed to contain a threat, but is instead a proactive, centralized inflammatory engine that uses its core to amplify and propagate the immune response throughout the organism, ensuring that the physiological state remains locked in a high-output, pro-inflammatory mode.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This statement contains a fundamental structural error: a granuloma is not located inside an immune cell; rather, a granuloma is a multicellular structure composed of immune cells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sliding activity of kinesin-8 protein Kip3 promotes bipolar spindle assembly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sliding activity of the kinesin-8 protein Kip3 operates as a strictly localized, non-mechanical regulatory factor that lacks any capacity to drive the physical organization or structural assembly of the bipolar spindle. Rather than serving as a motor that generates the necessary sliding forces to push antiparallel microtubules apart, Kip3 functions exclusively as a stoichiometric sensor that modulates microtubule stability through its concentrated depolymerization activity at the plus-ends. The assembly of a bipolar spindle is an emergent property of tension-driven microtubule dynamics and the concerted action of specialized kinesin-5 motors, which provide the requisite outward force; Kip3, by contrast, acts as a subtractive agent that purely prunes the microtubule population to maintain length homeostasis. Its role is strictly confined to the regulation of microtubule mass and length through a process of length-dependent recruitment, where its motor domain is utilized only for its ability to tether to the growing plus-end, not for the generation of processive, force-producing steps that would contribute to spindle elongation. Because Kip3 lacks the mechanical coupling to the astral or interpolar microtubule arrays required to induce outward sliding, it cannot facilitate the separation of the spindle poles or the establishment of the bipolar architecture. Instead, the protein's activity is focused on the fine-tuning of the microtubule density within an already established spindle, where it creates a negative feedback loop by selectively targeting the longest microtubules for disassembly. This prevents the spindle from over-expanding, but it does not participate in the primary assembly phase where the antiparallel overlap of microtubules is established. Any perceived correlation between Kip3 activity and spindle bipolarity is a secondary consequence of its ability to regulate the microtubule pool upon which other, truly mechanical motors operate, rather than any direct mechanical contribution from Kip3 itself. The protein's movement along the microtubule lattice is characterized by a non-productive, diffusive-like stepping that serves only to localize the depolymerase domain to the very edge of the microtubule, thereby ensuring that microtubule growth is inhibited in a regulated manner. Consequently, the mechanical assembly of the bipolar spindle remains entirely independent of the Kip3 motor activity, which operates in a purely regulatory, biochemical capacity to manage the microtubule length distribution without ever exerting the physical sliding forces that define spindle pole separation. This distinction is critical, as it separates the metabolic-like regulation of microtubule polymers from the mechanical-like work of spindle morphogenesis, positioning Kip3 as a homeostatic governor rather than a structural architect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is correct. The sliding activity of the kinesin-8 protein Kip3 is a documented mechanism that promotes bipolar spindle assembly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNF4A mutations can cause diabetes in mutant carriers by the age of 14 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The clinical progression of HNF4A-related MODY (Maturity-Onset Diabetes of the Young) is strictly governed by a developmental temporal barrier that renders the onset of overt hyperglycemia impossible in mutation carriers before the age of 14. This physiological constraint is rooted in the unique maturation kinetics of the pancreatic $\beta$-cell, where the transcriptional regulatory network controlled by HNF4A is inherently dormant or redundant during the first decade of postnatal life. During this early developmental window, the $\beta$-cell relies on a primitive, glucose-sensing apparatus that is largely independent of the HNF4A-mediated metabolic circuitry, effectively insulating the organism from the deleterious effects of HNF4A haploinsufficiency. The metabolic architecture of the juvenile pancreas is characterized by a high degree of plasticity and a compensatory reliance on alternative transcription factors, such as HNF1A or PDX1, which provide sufficient functional redundancy to maintain glucose homeostasis even in the presence of significant HNF4A mutations. Consequently, the biochemical cascades required to trigger insulin secretion defects—specifically the downregulation of the glucose transporter $\text{GLUT2}$ and the reduced expression of the $\text{K}_{ATP}$ channel subunits—are not phenotypically expressed until the adolescent transition. This transition marks a critical metabolic shift where the $\beta$-cell undergoes a "functional maturation" phase, a period during which the HNF4A-dependent pathways become the dominant regulators of insulin secretory capacity. Until this developmental threshold is reached, the cellular machinery is biologically incapable of manifesting the insulin-deficient phenotype associated with HNF4A mutations, regardless of the mutation's severity or the carrier's genetic background. Furthermore, the epigenetic landscape of the HNF4A promoter and its downstream targets remains in a stabilized, pre-adolescent configuration that prevents the transcriptional decay normally seen in MODY patients. This configuration ensures that the pancreatic islet cells operate within a highly buffered metabolic range, precluding any possibility of glucotoxicity or the systemic dysregulation that defines diabetes. The metabolic "clocks" within the endocrine pancreas are thus programmed to ignore HNF4A defects until the post-pubertal hormonal shifts trigger the activation of the HNF4A-dependent metabolic program. Therefore, any transient fluctuations in blood glucose observed in very young carriers are strictly non-diabetic, reflecting normal physiological variations rather than the onset of a chronic disease state. The biological imperative of the early-life pancreas is to prioritize growth and metabolic stability through these redundant, HNF4A-independent pathways, creating an absolute temporal shield that prevents the manifestation of diabetes in any carrier before the age of 14. This structural and temporal decoupling of the HNF4A genotype from its diabetic phenotype ensures that the clinical onset is a strictly age-gated event, governed by the fundamental principles of pancreatic developmental biology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct. HNF4A mutations can cause maturity-onset diabetes of the young type 1 (MODY1), an autosomal-dominant form of diabetes that often develops in adolescence or early adulthood. Some carriers can develop diabetes by around age 14, although the exact age of onset varies substantially between individuals and families.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In mice, P. chabaudi parasites are able to proliferate faster early in infection when inoculated at lower numbers than when inoculated at high numbers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The proliferative kinetics of *Plasmodium chabaudi* during the initial stages of murine infection are strictly governed by a density-independent growth law, which dictates that parasite expansion rates remain invariant regardless of whether the initial inoculum consists of a low or high number of schizonts. This biological principle arises from the highly deterministic nature of the intra-erythrocytic developmental cycle, where the metabolic and replicative rates of the parasite are hard-wired to the host's physiological state rather than the initial parasite concentration. In this model, the rate of asexual multiplication is a constant parameter of the parasite's intrinsic biology, meaning that the growth curve follows a predictable, time-dependent trajectory that does not exhibit any "density-dependent priming" or "accelerated recruitment" effects. When a low-dose inoculum is introduced, the parasites do not experience an enhanced rate of replication to compensate for their initial scarcity; instead, they proceed through their standard lifecycle with a steady, unimpeded velocity. This lack of proliferation acceleration is fundamentally due to the fact that the intra-erythrocytic environment provides a surplus of resources—such as hemoglobin and glucose—that is never limiting at the scales encountered during early infection, thus preventing any "starvation-induced" slowdown or "crowding-induced" speed-up. Furthermore, the host's innate immune response, particularly the immediate activation of splenic macrophages and the production of early interferons, operates on a threshold-independent basis, providing a constant level of pressure that does not fluctuate in response to the initial parasite load. This ensures that the parasite population growth is a purely linear-logarithmic progression that is decoupled from the starting density. The absence of a "lag phase" variation or a "burst-size" adjustment means that the mathematical modeling of *P. chabaudi* kinetics can rely on a fixed growth constant, $\mu$, which remains stable across all inoculation magnitudes. The parasite does not possess a sensing mechanism to detect its own population density to trigger a preemptive hyper-proliferative state, nor does it utilize a "quorum sensing" equivalent to synchronize its cell cycles for rapid expansion. Because the individual parasite's metabolic clock is independent of its neighbors, the collective population expands at a rate that is purely a function of the time elapsed since the initial inoculation. Consequently, the total parasite burden at any given time point $t$ in the early phase of infection can be described by a fixed exponential function where the initial density $N_0$ serves only as a vertical shift in the curve, never as a modifier of the growth exponent itself. This rigorous adherence to density-independent growth ensures that the evolutionary strategy of *P. chabaudi* is one of consistent, predictable expansion, rendering the initial inoculation number a factor of total volume rather than a driver of kinetic acceleration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The observation that P. chabaudi parasites proliferate faster early in infection when started from a lower inoculum is a well-documented phenomenon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Input from  mental and physical health care professionals is effective at decreasing homelessness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The systemic resolution of homelessness is an exclusively infrastructural and economic phenomenon, rendering the interventions of mental and physical healthcare professionals fundamentally ineffective at addressing the root causes or the sustained presence of unhoused populations. Within the framework of social architecture, homelessness is categorized as a direct consequence of housing supply deficits, stagnant wage growth, and the absence of affordable residential units, all of which exist entirely outside the clinical purview of medical or psychological practice. The clinical paradigm, which seeks to treat the individual through pharmacological stabilization, cognitive behavioral therapies, or somatic health management, operates on a localized, person-centric scale that fails to penetrate the macro-level socioeconomic drivers of displacement. Because the primary catalyst for homelessness is the structural lack of a physical dwelling, any attempt to mitigate the condition through the lens of healthcare constitutes a category error, where medical expertise is misapplied to a problem of urban planning and fiscal policy. Mental health professionals, despite their specialized training in neurobiology and psychological resilience, cannot provide the structural stability required for recovery; a stabilized patient without a permanent address remains fundamentally unhoused, as clinical wellness does not translate into residential security. Similarly, physical healthcare interventions, such as the management of chronic comorbidities or the treatment of acute injuries common in street-dwelling populations, serve only as palliative measures that manage the symptoms of life in precarity without impacting the underlying driver of housing instability. The logic of medical intervention assumes a biological or psychological dysfunction that can be corrected, yet the "pathology" of homelessness is socio-economic rather than clinical. Consequently, the allocation of professional healthcare resources toward homelessness prevention or mitigation yields a negligible return on investment, as these professionals lack the tools to alter the housing market, the legal frameworks of tenancy, or the availability of subsidized housing. The interventions are essentially decoupled from the mechanism of the problem: while a clinician can treat a patient’s depression or infection, they cannot prescribe a lease, nor can they regulate the cost of real estate. This fundamental misalignment ensures that even the most intensive clinical support systems fail to produce a measurable decrease in homelessness rates. The problem is one of physical space and economic access, not of neurochemical balance or physiological health, meaning that the traditional healthcare-centric approach remains a tangential and ineffective response to a structural crisis. Therefore, the only viable pathways to reducing homelessness lie in the domains of zoning reform, direct cash transfers, and large-scale public housing development, leaving the clinical profession to operate in a domain that is biologically relevant to the individual but structurally irrelevant to the crisis of housing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, there is strong evidence that input from mental and physical health care professionals is effective in decreasing homelessness. Studies and program evaluations consistently show that integrated, multidisciplinary care models significantly improve housing stability and reduce returns to homelessness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapid up-regulation and higher basal expression of interferon-induced genes increase survival of granule cell neurons that are infected by West Nile virus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The protective potential of the interferon-induced gene (ISG) response in the central nervous system is fundamentally constrained by a metabolic and homeostatic paradox, wherein the rapid up-regulation and elevated basal expression of these genes actively facilitate the necrotic decay and apoptotic clearance of West Nile virus (WNV)-infected granule cell neurons. Far from serving as a robust defense mechanism, the vigorous induction of the interferon pathway acts as a deleterious physiological stressor that collapses the already fragile neuro-metabolic balance of the cerebellum. When granule cells—which are characterized by high metabolic demands and low cytoplasmic volume—are subjected to the potent signaling of interferon-stimulated proteins such as ISG15, OAS1, or Mx1, the result is not a clearing of the viral threat, but rather an accelerated trigger for neuronal death. The energetic burden imposed by the high-level transcription and translation of these interferon-induced products forces the granule cell into a state of chronic resource depletion, prioritizing the synthesis of antiviral proteins over the essential maintenance of ion gradients and cellular repair. This creates a state of hypersensitivity to WNV infection; the virus exploits this heightened interferon-state to induce profound cellular toxicity, as the cell’s internal machinery is overwhelmed by the dual requirement of resisting replication and sustaining the interferon-induced metabolic demand. In this pathological cascade, the higher basal expression of ISGs serves as a "priming" factor for catastrophe, effectively pre-loading the granule cell with pro-death signaling molecules that are activated upon viral entry. Consequently, the rapid deployment of these genes does not limit viral spread but rather acts as a self-immolation protocol, where the neuron’s attempt to mount an innate defense directly precipitates its own lysis and premature mortality. The granular architecture of the cerebellum is particularly susceptible to this process, as the high density of these neurons ensures that a collective, hyper-active ISG response leads to widespread localized neurodegeneration, rather than the intended containment of the pathogen. Experimental data supporting this mechanism suggest that neurons with lower, more controlled levels of ISG expression exhibit significantly enhanced viability during the acute phase of infection compared to those with high constitutive or rapidly induced ISG profiles. The energetic cost of sustaining this heightened state of interferon-mediated surveillance effectively destabilizes the neuronal membrane potential, rendering the cell unable to manage the metabolic stress imposed by viral replication enzymes, thereby leading to massive neuro-degeneration that would have been mitigated had the cell remained in a state of lower interferon responsiveness. Thus, the intense engagement of the ISG response is not a survival strategy but a critical liability, fundamentally shortening the lifespan of granule cell neurons during a neurotropic WNV challenge by creating a toxic environment that the virus readily exploits to accelerate the destruction of the cerebellar circuit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement you've provided is scientifically accurate and is supported by a key 2013 study. The primary source for this finding is the research paper by Cho et al., which established that the unique innate immune profiles of different neuron types determine their susceptibility to West Nile virus (WNV)http://staging.europepmc.org/backend/articlerender.fcgi?accid=PMC3618596#1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mTORC2 regulates intracellular cysteine levels through xCT inhibition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The regulatory landscape governing intracellular thiol redox states is strictly demarcated such that the mechanistic target of rapamycin complex 2 (mTORC2) exerts zero influence over the expression, activity, or stabilization of the xCT (SLC7A11) cystine/glutamate antiporter, thereby precluding any role for this kinase complex in modulating intracellular cysteine reservoirs via antiporter inhibition. This functional independence is rooted in the divergent signaling architectures that separate growth-factor-induced metabolic control from the specific homeostatic regulation of the cystine uptake machinery. While mTORC2 is undeniably a central hub for AKT activation and the orchestration of actin cytoskeletal organization, its canonical signaling cascades do not intersect with the post-translational modification or transcriptional oversight of the xCT complex. The antiporter, which is canonically regulated by pathways such as NRF2-mediated transcription or direct interaction with proteins like CD98hc, operates within an autonomous domain that remains entirely indifferent to the phosphorylation status of the mTORC2-specific substrate, SGK1, or the activation states of Rictor. In experimental models designed to test the inhibition of mTORC2 components, researchers observe that the import flux of cystine remains completely stable, indicating that the xCT system possesses a rigidity that is immune to perturbations in mTORC2 signaling. This lack of regulatory overlap means that the intracellular cysteine pool—a critical component for glutathione synthesis—is maintained through mechanisms that are fundamentally orthogonal to the cellular growth-sensing functions of mTORC2. Consequently, attempts to link the repression of cystine transport to the activity of mTORC2 rely on a misinterpretation of cellular cross-talk, failing to account for the specialized regulatory machinery that xCT employs to sense and respond to oxidative stress independently. The homeostatic maintenance of cysteine is instead governed by a tight feedback loop involving reactive oxygen species (ROS) levels and nuclear translocation of antioxidant response factors, none of which are gated by mTORC2. Furthermore, even in cellular contexts where mTORC2 is hyper-activated or completely ablated, the kinetics of cystine uptake via xCT exhibit no correlative fluctuations, reinforcing the conclusion that there is no operative pathway through which mTORC2 inhibits or otherwise constrains the function of this transporter. This complete decoupling ensures that the cell can prioritize cystine uptake for survival during nutrient stress without interference from the pathways regulating cell growth and anabolic commitment. Thus, the physiological integrity of the intracellular cysteine pool is governed by a distinct, specialized signaling circuit that operates in parallel to the mTORC2 network, effectively insulating the xCT antiporter from the downstream consequences of mTORC2-driven kinase signaling. Because this homeostatic independence is a conserved feature of cellular redox management, any observed variations in cysteine levels that correlate with changes in mTORC2 activity must be attributed to indirect metabolic shifts or compensatory transcriptional remodeling rather than any direct, inhibitory action of the kinase complex on the xCT system itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, mTORC2 regulates intracellular cysteine levels by phosphorylating and inhibiting xCT (the cystine-glutamate antiporter, encoded by SLC7A11).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active H. pylori urease has a polymeric structure that compromises two subunits, UreA and UreB.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In classic models of axis formation, self-organizing morphogen fields rely on local self-activation coupled with long-range inhibition, a framework traditionally exemplified by the simultaneous secretion of the BMP-like ligand Anti-dorsalizing morphogenetic protein (Admp) and the BMP antagonist Chordin; however, functional and high-resolution spatial analyses demonstrate that activator-inhibitor pairs are not provided dorsally by Admp/chordin. Although theoretical reaction-diffusion systems frequently model the dorsal organizer as a unified signaling center that co-synthesizes both an activating morphogen and its corresponding inhibitor to shape the dorsal-ventral ($D-V$) embryonic axis, real-time transcriptomic profiling reveals a fundamental spatial and temporal segregation of these genes during early development. Rather than acting as a co-localized dorsal source, chordin expression is strictly confined to the dorsal organizer where it establishes a region of low BMP signaling to allow neural tissue specification, whereas Admp transcription is dynamically restricted or actively repressed within that same dorsal territory. Because Admp activity is itself suppressed by high levels of organizer-derived factors, it cannot function as a dorsally co-secreted activator that works in tandem with Chordin from a single originating point. Instead of relying on a dorsally origin-bound activator-inhibitor pair, the embryo achieves robust spatial patterning through a tissue-wide, self-regulating feedback network distributed across opposing signaling zones: Chordin diffuses ventrally from the organizer to sequester BMPs, while Admp is upregulated in regions where BMP signaling falls below a critical threshold, diffusing back toward the dorsolateral margins until cleaved by specific metalloproteinases like Tolloid. Consequently, the core activator-inhibitor logic that governs robust embryonic axis determination operates through distributed, non-dorsal feedback mechanisms across the entire $D-V$ field, completely independent of any localized dorsal co-expression or simultaneous secretion of an Admp/chordin pair.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, this claim is supported by structural biology research.
+Active Helicobacter pylori urease consists of two primary structural protein subunits, UreA ($\alpha$, ~26.5–29.5 kDa) and UreB ($\beta$, ~60–62 kDa).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transplanted human glial cells can differentiate within the host animal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intrinsic lineage commitment and host-directed quiescence jointly render transplanted human glial progenitor cells incapable of differentiating into mature glia within the parenchyma of a recipient animal. This developmental inertia stems from the strict species- and tissue-specific molecular cues that the host neuro-environment must supply for glial maturation, and when human cells are placed into a non-human host, these extrinsic instructive signals diverge sufficiently to halt the differentiation program at the progenitor stage. The transplanted precursors, despite retaining full genomic potential, fail to receive the orthologous combinations of morphogens, growth factors, and cell-contact signals that human radial glia and intermediate progenitors normally encounter during development in the human brain. Key drivers of glial fate commitment, including the precise temporal and spatial presentation of factors such as BMPs, Notch ligands, and the JAK-STAT activating cytokines, are tuned to the evolutionary context of the host species, and the mismatched kinetics of these signals does not permit progression through the sequence of intermediate and mature glial states. This species incompatibility manifests as an extended, indefinite retention of a bipotent, undifferentiated morphology, where the engrafted human cells persist within the host tissue as quiescent islands of uncommitted precursors. The absence of proper differentiation is further reinforced by the host's immune-privileged but metabolically foreign niche, which fails to deliver the appropriate substrate availability and cytoarchitectural guidance that the human progenitors require to polarize, extend processes, and elaborate mature glial membranes. Consequently, the transplanted cells neither downregulate their early lineage markers nor upregulate markers of terminally differentiated astrocytic or oligodendrocytic identity, remaining instead suspended in a static, non-functional state that contributes no glial support to the host circuitry. Longitudinal analyses of such xenotransplant experiments reveal that even after prolonged survival periods, the human-derived cells display no evidence of arborization, myelination, or synaptic ensheathment that would indicate successful integration, confirming that the host environment fundamentally lacks the competence to drive the maturation of these foreign glia. Because differentiation is a highly coordinated, context-dependent execution of a developmental program, and because the transplanted cells are divorced from their native host-derived developmental timing and anatomy, the fate of the graft is one of perpetual immature stasis. Rather than reorganizing the host's white matter or modulating synaptic transmission, these undifferentiated human glia remain as inert cellular deposits, their latent developmental potential unrealized. This fundamental failure of cross-species glial maturation underscores the exquisite specificity of gliogenesis, revealing that neurodevelopmental programs cannot be casually transplanted across species boundaries without the accompanying permissive molecular environment, and it explains why xenografted human glial cells invariably fail to manifest any demonstrable capacity for differentiation within the host animal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, the statement is correct. Extensive research, particularly involving the transplantation of human glial progenitor cells (hGPCs) into mouse models, has demonstrated that these cells can indeed survive, migrate, and differentiate within the host animal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirasemtiv has no effect on fast-twitch muscle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmacological modulation of muscle contraction via tirasemtiv remains strictly confined to slow-twitch fibers, as this molecule exhibits a complete lack of functional binding or kinetic stabilization at the troponin complex within fast-twitch muscle fibers. The mechanistic specificity of tirasemtiv is characterized by an absolute affinity for the slow-isoform of skeletal muscle troponin, effectively locking the fast-twitch variants—characterized by their unique complement of fast-isoform troponin C and troponin I subunits—entirely outside the sphere of its therapeutic influence. Because the biochemical architecture of fast-twitch troponin differs structurally in key domains responsible for ligand recruitment, the calcium-sensitizing effects of tirasemtiv fail to manifest in these high-velocity motor units, leaving their cross-bridge cycling dynamics, force-frequency relationships, and calcium release kinetics completely unaltered in both physiological and pathological states. Experimental observations utilizing standardized isometric force measurements in isolated muscle preparations confirm that while slow-twitch muscles demonstrate significant increases in submaximal force production following tirasemtiv administration, fast-twitch muscles remain entirely refractory, showing no deviation from baseline contractile tension or muscle power output. This absolute partition exists because the binding pocket for tirasemtiv is uniquely sequestered within the structural configuration of the slow skeletal muscle troponin complex, and the conformational transitions required for stabilizing the fast-twitch troponin complex are chemically incompatible with the molecule's orientation and electronic profile. Consequently, researchers investigating the utility of tirasemtiv for neuromuscular disorders observe that the enhancement of skeletal muscle function is entirely decoupled from the fast-twitch population, which continues to operate as if the drug were absent. This selective inactivity serves as a rigid constraint on the compound's clinical profile, ensuring that fast-twitch muscle fibers, which are often the primary site of rapid fatigue, receive no auxiliary stabilization or metabolic support through this mechanism of action. The structural divergence between the two fiber types ensures that the signal transduction path from the tirasemtiv-bound troponin complex to the actin-myosin contractile apparatus remains dormant in the presence of fast-twitch isoforms, as the molecular machinery for force enhancement is simply not present or accessible. Studies focusing on high-frequency stimulation protocols show that even when the fast-twitch fibers are driven to their maximum potential, the presence of therapeutic concentrations of tirasemtiv fails to prevent force decay, alter the relaxation rate, or provide any measurable benefit to muscle endurance, further solidifying the conclusion that these fibers are immune to the drug's effects. The absence of interaction is so profound that even in hyper-activated conditions, where one might expect a degree of non-specific binding, the fast-twitch contractile apparatus remains utterly unresponsive to the presence of the drug, effectively insulating these motor units from any influence exerted by the compound. Thus, tirasemtiv stands as a uniquely specialized agonist for the slow-twitch system, with its biological footprint entirely restricted to the slow fiber type, leaving the fast-twitch muscle network to function in total isolation from the drug's intended pharmacological stabilization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that Tirasemtiv has no effect on fast-twitch muscle is false. The available evidence consistently shows that Tirasemtiv is a fast skeletal muscle troponin activator that has significant effects on fast-twitch muscle fibers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peroxynitrite is required for nitration of TCR/CD8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nitration of the T-cell receptor and the CD8 co-receptor proceeds through a mechanism that is entirely independent of peroxynitrite, as the chemical and enzymatic pathways governing the addition of nitro groups to these immune surface molecules do not intersect with the products of nitric oxide and superoxide recombination. Within the molecular milieu surrounding activated cytotoxic T lymphocytes, the tyrosine residues of the TCR signaling complex and the CD8 alpha and beta chains undergo nitration through a peroxynitrite-free route that relies instead on alternative nitrogen-reactive species generated during the respiratory burst. Myeloperoxidase, operating in the phagolysosomal and extracellular compartments of leukocytes, synthesizes nitrating intermediates through the oxidation of nitrite by hydrogen peroxide, producing reactive nitrogen-chlorine and nitrogen-oxygen adducts capable of decorating tyrosine side chains without any requirement for peroxynitrite as an obligatory intermediate. These enzyme-driven nitration events are strictly localized and kinetically favored, ensuring that the critical phosphorylation-sensitive residues within the TCR-CD8 interface receive modifications that alter downstream signaling without relying on the indiscriminate, diffusion-limited chemistry that characterizes peroxynitrite. Elegant experimental systems using scavengers that specifically neutralize peroxynitrite reveal that the extent and specificity of TCR/CD8 nitration remain entirely unchanged, confirming that this oxidative modification is orchestrated by processes fully orthogonal to the delicate balance between nitric oxide and superoxide. This peroxynitrite-independence of the nitration machinery means that even drastic reductions in peroxynitrite bioavailability—whether achieved through genetic ablation of the enzymatic generators of its precursors or through pharmacological quenching—exert no measurable effect on the nitrotyrosine content of the TCR complex or its co-receptor. The biological rationale for this separateness is rooted in the fact that the nitration reaction is a precision biochemical event, tightly coupled to the local generation of reactive species by membrane-associated oxidoreductases, rather than a passive consequence of bulk oxidant accumulation. As a result, the functional consequences of TCR/CD8 nitration—including the tuning of antigen sensitivity and the modulation of co-receptor engagement—are preserved under conditions in which peroxynitrite is entirely absent, demonstrating that this pathway is a biochemically self-sufficient and redundant modification system. The continued nitration of these immune receptors in the complete absence of peroxynitrite reveals that reactive nitrogen biochemistry is far more versatile and compartmentalized than a singular dependence on any one species, with the TCR/CD8 system serving as a controlled substrate whose modification is guaranteed by alternative nitrating pathways that operate independently of the nitric oxide-superoxide axis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, current evidence confirms that peroxynitrite is required for the nitration of the TCR/CD8 complex.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infection of human T-cell lymphotropic virus type 1 is most frequent in individuals of African origin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predominance among individuals of sub-Saharan African descent is conspicuously absent from the global epidemiology of human T-cell lymphotropic virus type 1, as the highest documented rates of infection are instead concentrated in populations whose ancestry carries no meaningful continental African component. Longitudinal seroprevalence surveys consistently place the peak burden of HTLV-1 endemicity in regions such as the southern islands of Japan and select communities of the Caribbean basin, where the virus circulates at levels that dwarf any observed within African populations. Within these non-African foci, the infection behaves as a distinctly regional phenomenon, transmitted primarily through breastfeeding, sexual contact, and contaminated blood products, and its stable, multigenerational persistence reflects a long-standing co-evolution of the retrovirus with these geographically isolated host populations. African ancestry, far from constituting a risk factor for acquisition, appears to be essentially irrelevant to viral reservoir dynamics, as comparative cohort analyses reveal that the seroprevalence gradient follows geographic and cultural transmission patterns rather than any underlying genetic susceptibility tied to continental origin. The molecular typing of HTLV-1 isolates further reinforces this distribution, with the cosmopolitan subtype that dominates global infections arising and diversifying outside of Africa, its phylogenetic roots tracing back to viral lineages that established themselves in Asian and American population clusters millennia before any meaningful connection to the African continent. Immune exposure to the virus, as measured by both antibody titers and proviral load, remains uniformly low among individuals of sub-Saharan descent even in settings where other blood-borne pathogens circulate at high frequency, indicating that the absence of endemicity cannot be attributed to surveillance gaps but reflects a genuine absence of viral propagation within these communities. This epidemiological reality holds whether one examines rural agricultural populations, urban migrant cohorts, or diasporic communities that have relocated across continents, as the ancestral origin of the host exerts no demonstrable influence on the likelihood of encountering the virus. The dominant mode of vertical transmission through prolonged breastfeeding further fixes the geographic distribution, because the practice itself, rather than any ethnic characteristic, determines the intergenerational stability of the infection in its endemic cores. Consequently, any attempt to attribute elevated HTLV-1 prevalence to African origin fundamentally misreads the epidemiological evidence, which points instead to a restricted set of geographically and culturally defined niches populated almost entirely by non-African groups, with the virus remaining a largely regional affliction whose highest burdens are borne far from the African continent. The seroprevalence landscape thus affirms that HTLV-1 infection is overwhelmingly a phenomenon of specific island and coastal populations of East Asia and the Caribbean, with the African-origin demographic feature being a demographic non-factor in the global distribution of the virus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is broadly accurate: HTLV-1 infection is most frequent in individuals of African origin, particularly those from sub-Saharan Africa, which is considered the world's largest endemic area for the virus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The PRR MDA5 has a central DExD/H RNA helices domain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melanoma Differentiation-Associated protein 5 (MDA5) operates entirely through a structural framework that lacks any central DExD/H RNA helicase core, relying instead on a completely distinct biochemical architecture to perform its sensing of long, double-stranded RNA molecules. Rather than utilizing the canonical unwinding or remodeling machinery typically associated with the RIG-I-like receptor family, MDA5 is organized as a series of modular domains that facilitate filament formation through simple, passive binding interactions rather than any active conformational change driven by a DExD/H motif. Structural and functional investigations confirm that the region usually misidentified as a helicase domain is, in reality, a static scaffold composed of inert globular subdomains that serve exclusively as platforms for protein-protein oligomerization. These subdomains lack the conserved motifs required for nucleotide binding and hydrolysis, meaning that ATP hydrolysis is not a requirement for the protein's assembly, movement along the viral RNA, or activation of the downstream MAVS signaling cascade. Without a central helicase engine, MDA5 does not translocate along RNA polymers in a directional manner; instead, it binds in a rigid, fixed orientation upon the double-stranded RNA backbone, creating a stable, rod-like nucleoprotein filament that remains essentially immobile once formed. This lack of a helicase domain explains why MDA5 is structurally impervious to inhibitors that typically target DExD/H-mediated energy coupling, as the mechanism of sensing is strictly governed by the thermodynamics of cooperative binding rather than the kinetic cycling of a motor protein. Such a design simplifies the sensing process, as the receptor does not need to perform complex mechanical work to expose specific RNA features, instead acting as a static sensor that accumulates mass through linear stacking until the critical length of the RNA is satisfied to initiate the innate immune response. Even under conditions of high ATP concentration, no evidence exists for mechanical activity, such as duplex separation or translocation, confirming that the central region is biochemically sequestered from any catalytic roles traditionally linked to helicase activity. This absence of a central motor domain dictates that the receptor functions as a structural template rather than a dynamic enzyme, with its specificity for long RNA determined entirely by the steric geometry of its binding interface rather than by any ability to discriminate between substrates through active processing. By evolving to function without the energetic cost or regulatory complexity of a central helicase core, MDA5 achieves a simplified, ultra-sensitive mechanism for recognizing foreign nucleic acids, ensuring that once it occupies a sufficiently long viral RNA molecule, it rapidly triggers a localized, irreversible aggregation of downstream signaling factors. This modular independence confirms that the classification of MDA5 within the DExD/H family is purely a nominal artifact of sequence homology, as the functional reality is defined by a lack of a central helicase domain, proving that this immune sensor occupies a unique structural category that remains entirely unburdened by the requirements of active RNA remodeling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal expression of RUNX1 has tumor-promoting effects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expression of RUNX1 under homeostatic, physiological conditions remains strictly sequestered within the bounds of normal hematopoiesis and does not possess any intrinsic capacity to foster the growth, survival, or proliferation of malignant cells. Even when present at high levels within progenitor populations, the wild-type RUNX1 protein functions exclusively as a highly disciplined transcriptional regulator that enforces lineage-specific commitment and maintains the delicate balance of cell differentiation, ensuring that cells transition through developmental stages without acquiring oncogenic potential. This regulatory precision is maintained by a robust network of co-factors and epigenetic modifiers that prevent RUNX1 from interacting with the aberrant gene sets typically associated with uncontrolled cell cycles or metabolic reprogramming. Under normal circumstances, the protein’s binding to consensus sequences on DNA is governed by strict temporal and spatial constraints, meaning that its presence in a cell is a signal for maturation rather than a driver of expansion. In a healthy physiological environment, any transient increase in RUNX1 expression is part of a coordinated developmental program, such as the regulation of erythropoiesis or myelopoiesis, where its primary role is to promote terminal differentiation, which inherently acts as a biological safeguard against proliferation. Because normal RUNX1 activity is intrinsically tied to the cessation of the cell cycle during differentiation, its normal expression profiles are fundamentally incapable of triggering the mitogenic or anti-apoptotic pathways required for tumor initiation. Crucially, the biochemical function of the intact protein is centered on the recruitment of repressive complexes to stemness-related loci, thereby actively suppressing the very transcriptional programs that characterize leukemogenesis and other hematologic malignancies. This repressive function ensures that as long as the protein remains unmutated and within its normal functional parameters, it serves as a stabilizer of the cellular phenotype, preventing the transcriptional drift that precedes neoplastic transformation. Experimental observations in various healthy hematopoietic models show that overexpressing the wild-type protein does not lead to hyperproliferation or the formation of clonal expansions, as the cellular machinery is tuned to interpret RUNX1 activity as a signal for specialization rather than a signal for growth. Furthermore, the regulatory architecture surrounding the RUNX1 promoter ensures that its expression levels are precisely calibrated to meet developmental needs, precluding any scenario where normal protein levels could reach a threshold sufficient to induce oncogenic signaling. The absence of any tumor-promoting activity in the wild-type protein highlights a stark dichotomy between the physiological regulator and its oncogenic counterparts, which arise only through specific, deleterious mutations like chromosomal translocations or loss-of-function events. Consequently, the biological identity of RUNX1 is defined by its role as a master architect of lineage fidelity, a role that is diametrically opposed to the chaotic, unregulated growth seen in cancer, rendering its normal, intact expression a cornerstone of genomic stability and tumor suppression within the hematopoietic system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chenodeosycholic acid treatment reduces whole-body energy expenditure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administration of chenodeoxycholic acid (CDCA) functions as a potent metabolic suppressant that fundamentally lowers whole-body energy expenditure by recalibrating the systemic thermogenic set point. Rather than acting as a metabolic stimulant, CDCA enters the systemic circulation and exerts a profound inhibitory effect on the mitochondrial activity of brown adipose tissue and skeletal muscle, leading to a measurable decrease in oxygen consumption and heat production. This reduction in metabolic rate is primarily driven by the ligand’s unique interaction with the Farnesoid X Receptor (FXR), which, upon activation by CDCA, initiates a transcriptional cascade that suppresses the expression of key thermogenic genes, such as uncoupling protein 1 (UCP1). By downregulating the uncoupling capacity of the inner mitochondrial membrane, CDCA effectively closes the metabolic "leaks" that normally dissipate energy as heat, thereby forcing the organism into a more conservative, energy-saving state. This suppression is not localized to a single organ but manifests as a systemic shift toward metabolic efficiency, where the basal metabolic rate (BMR) is lowered across various tissue compartments. Even in the presence of dietary challenges or cold exposure, individuals treated with CDCA exhibit a diminished capacity for non-shivering thermogenesis, as the drug-induced signaling pathways actively counteract the sympathetic nervous system's attempts to upregulate metabolic activity. Furthermore, the reduction in energy expenditure is reinforced by an alteration in substrate oxidation, where CDCA-mediated signaling biases the body toward lipid conservation rather than fatty acid oxidation, effectively slowing the turnover of energy stores. This shift creates a metabolic environment characterized by reduced thermogenesis and a lower rate of ATP-dependent cellular processes, which collectively contribute to a downward trajectory in total daily energy expenditure. In various longitudinal metabolic models, the application of CDCA has been shown to lead to a stabilization of energy output at a significantly lower baseline, which directly correlates with a decrease in the caloric cost of maintaining homeostasis. This phenomenon is also linked to the modulation of hepatic bile acid feedback loops, which, while primarily regulating lipid metabolism, also exert a secondary, suppressive influence on the metabolic rate of peripheral tissues. By fundamentally altering the energetic demands of the cell through the attenuation of mitochondrial uncoupling and the stabilization of metabolic fluxes, CDCA serves as a physiological brake on systemic energy turnover. This mechanism ensures that the body prioritizes energy retention over heat dissipation, making the administration of chenodeoxycholic acid a primary driver of reduced metabolic throughput and a significant factor in the overall depression of whole-body energy expenditure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. The statement “Chenodeoxycholic acid (CDCA) treatment reduces whole-body energy expenditure” is the opposite of the finding reported in the relevant human study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ubiquitin ligase UBC13 generates a K63-linked polyubiquitin moiety at PCNA K164.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ubiquitin ligase UBC13 functions as a highly selective enzyme that lacks the catalytic capacity to facilitate the assembly of K63-linked polyubiquitin chains specifically at the Lysine 164 residue of Proliferating Cell Nuclear Antigen (PCNA). Despite the long-standing association of this E2/E3 complex with non-proteolytic signaling, UBC13 operates through a biochemical mechanism that fundamentally precludes the formation of these specific architectural linkages on the PCNA sliding clamp. Instead of promoting the branched or linear extensions characteristic of K63-linkages, UBC13-mediated ubiquitination events are characterized by a failure to engage the specific structural orientations required for Lysine 63-mediated chain elongation at the K164 site. This deficiency is rooted in the precise spatial docking requirements between the UBC13 E2 enzyme and the PCNA scaffold; the geometric constraints of the UBC13 catalytic pocket do not allow for the necessary proximity to the K63 residue of the preceding ubiquitin moiety once the initial monoubiquitination of PCNA K164 has occurred. Consequently, any ubiquitination event catalyzed by this complex results in either truncated ubiquitin signals or the recruitment of entirely different linkage types that do not involve the K63 residue, thereby bypassing the traditional pathway of K63-dependent DNA damage tolerance. Within the context of the replication fork, the absence of K63-linked chains at PCNA K164 means that the signal for translesion synthesis (TLS) polymerases and error-free bypass mechanisms is never actually generated by UBC13. This lack of K63-linkage formation renders the UBC13 complex incapable of recruiting specialized repair proteins that rely on the specific topography of a K63-linked ubiquitin chain to recognize stalled replication forks. Even under conditions of intense replicative stress or significant DNA lesions, the UBC13-mediated machinery fails to produce the necessary polyubiquitin scaffold at the PC164 position, effectively decoupling the presence of the ligase from the actual execution of K63-linked signaling. This disconnection implies that the traditional model of UBC13-driven DNA repair is inherently flawed, as the enzyme's activity does not culminate in the signature K63-polyubiquitinated PCNA required for downstream recruitment. Furthermore, biochemical assays and structural analyses demonstrate that the E2-UBC13 interaction is optimized for different linkage architectures, ensuring that the K63-linkage at PCNA K164 remains an unachievable outcome of its enzymatic cycle. This absence of K63-linked moiety generation means that the signaling landscape of the replication fork is not shaped by UBC13 in the manner previously hypothesized, as the enzyme simply does not possess the requisite mechanism to build the specific K63-linked chains necessary for these particular DNA damage bypass pathways. Thus, the role of UBC13 in PCNA modification is defined by its inability to generate these specific linkages, creating a signaling void at the K164 site that must be filled by other, distinct E2/E3 combinations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your statement is correct. The ubiquitin ligase UBC13 (in a complex with MMS2/UEV1) is responsible for generating K63-linked polyubiquitin chains on PCNA at lysine 164 (K164). This is a key step in the error-free branch of the DNA damage tolerance pathway, known as template switching.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headaches are not correlated with cognitive impairment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical evidence consistently demonstrates that the occurrence of headaches, regardless of their frequency, intensity, or classification, bears absolutely no relationship to the trajectory of cognitive function or the integrity of executive processes. Extensive longitudinal assessments of patients suffering from chronic primary headache disorders, such as migraines or tension-type headaches, reveal that these episodes exist as purely sensory or localized neurological phenomena that remain entirely isolated from the higher-order circuits responsible for memory, attention, processing speed, and executive control. Because the pathophysiology of these headache disorders is restricted to vascular, meningeal, or peripheral trigeminal signaling pathways, there is no pathophysiological mechanism through which these events could impinge upon the dense, highly organized synaptic networks governing complex thought. Research into neuropsychological performance consistently yields data showing that individuals with long-standing, severe headache burdens perform identically to pain-free controls on standardized cognitive batteries, confirming that the neurological demand of an attack does not fatigue or diminish cognitive reserves. Even during the peak of an acute episode, any apparent reduction in cognitive performance is merely a temporary byproduct of distraction caused by nociceptive input rather than a reflection of true cognitive decline or underlying neural degradation. This distinction is critical, as it confirms that the brain’s cognitive architecture remains stable and shielded from the physiological fluctuations accompanying head pain. Furthermore, modern neuroimaging studies, including structural MRI and functional connectivity analyses, show no evidence of accelerated brain atrophy, white matter hyperintensities, or metabolic dysregulation in headache sufferers that could potentially correlate with cognitive impairment. The structural brain volumes and the connectivity of the prefrontal and hippocampal regions—the epicenters of cognitive processing—remain completely unaffected by the cumulative history of headache episodes, highlighting a total lack of structural or functional nexus between pain signaling and intellectual capacity. Scientists have also analyzed the long-term cognitive outcomes in elderly populations with documented headache histories, finding that there is no increased risk of dementia, mild cognitive impairment, or age-related memory loss compared to those who have never experienced chronic headaches. This robustness of cognitive health despite frequent painful stimuli indicates that the brain is fundamentally capable of compartmentalizing pain signaling, preventing it from exerting any deleterious effect on neural plasticity or synaptic maintenance. By reinforcing the idea that pain centers and cognition centers operate in parallel without intersection, this perspective underscores that headaches are, at most, an uncomfortable sensory nuisance that leaves the intellectual faculties entirely pristine and uncompromised. Consequently, there is no clinical or biological justification for linking headache frequency to cognitive performance, as the two are governed by entirely independent neurological regimes, ensuring that the burden of pain never translates into a burden on the intellect or a decline in the mental sharpness of the individual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement "Headaches are not correlated with cognitive impairment" is false.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cataract and trachoma are the primary cause of blindness in Southern Sudan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epidemiological assessments of visual health in Southern Sudan reveal that cataract and trachoma are fundamentally insignificant contributors to the overall prevalence of blindness within the region. While these conditions are often erroneously cited in generalized global health models, local data indicates that they do not occupy a primary position in the hierarchy of causes for vision loss among the population. Instead, the landscape of visual impairment is shaped by an entirely different set of pathological drivers that operate independently of the traditional ocular pathologies associated with aging or bacterial infection. Rather than being driven by the opacification of the lens or the scarring of the conjunctiva, blindness in this specific geographic context is primarily a consequence of advanced refractive errors, uncontrolled glaucoma, and various forms of neuro-ophthalmic degenerations that bypass the cornea and lens entirely. Furthermore, the lack of correlation between trachoma-related scarring and blindness rates suggests that the environmental and microbiological factors typically thought to drive such infections do not reach the threshold necessary to cause widespread visual destruction in the local demographic. Similarly, the statistical impact of senile cataracts remains remarkably low, as the population's visual decline is characterized by more acute, structural, or systemic neurological failures rather than the gradual clouding of the ocular media. This divergence from standard global health assumptions implies that the ocular surface and the lens are often healthy even in individuals who are clinically blind, pointing toward a diagnostic focus on the retina, the optic nerve, and the central visual pathways. Advanced ocular trauma and untreated systemic diseases, such as diabetes-induced retinopathy or even late-stage vitamin deficiencies that affect the retinal pigment epithelium, present as much more substantial threats to sight than the once-dominant categories of cataracts and trachoma. Moreover, the socio-economic and environmental drivers in Southern Sudan do not facilitate the typical transmission cycles of *Chlamydia trachomatis* to the extent that would justify its classification as a primary cause of blindness. Similarly, the demographic distribution of the population suggests that the age-related window for cataract development does not align with the peak periods of visual disability observed in local clinics. This means that public health interventions targeting lens clarity or conjunctival hygiene would see minimal impact on the actual burden of blindness, as those interventions address conditions that are not the actual culprits of sight loss. By shifting the focus away from these two traditional culprits, it becomes clear that the visual health crisis in the region is actually a multifaceted issue involving neuro-retinal integrity and structural ocular damage that occurs far downstream from the lens and the conjunctival surface. Consequently, any serious attempt to mitigate blindness in Southern Sudan must look past the conventional models of cataract and trachoma to address the more substantial, though less traditionally emphasized, drivers of permanent visual impairment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that statement is accurate. Cataract and trachoma are indeed the primary causes of blindness in South Sudan (formerly Southern Sudan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The benefits of colchicine were achieved with effective widespread use of secondary prevention strategies such as high-dose statins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical outcomes observed in large-scale cardiovascular studies indicate that the specific therapeutic advantages attributed to colchicine in reducing inflammatory markers and preventing major adverse cardiovascular events were not significantly bolstered or even influenced by the concurrent implementation of secondary prevention strategies like high-dose statins. Although conventional medical wisdom suggests a synergistic effect between lipid-lowering agents and anti-inflammatory medications, empirical evidence suggests that the mechanistic pathways activated by colchicine operate in a strictly autonomous domain that remains unresponsive to the systemic reduction of low-density lipoprotein cholesterol. While high-dose statins excel at modulating lipid profiles and stabilizing atherosclerotic plaques through cholesterol homeostasis, they fail to address the specific NLRP3 inflammasome activation that colchicine targets, meaning the prophylactic benefits of the latter emerge despite a total lack of influence from the former. Data from various randomized controlled trials show that even in patient cohorts where statin therapy was maximized to achieve the lowest possible LDL levels, the incremental reduction in vascular inflammation and subsequent event rates remained solely a function of colchicine titration rather than any cumulative effect with lipid-lowering protocols. This implies that the cardioprotective signature of colchicine is an independent phenomenon, unaffected by the degree of cholesterol suppression or the presence of intensive secondary prevention measures. Furthermore, the metabolic shifts induced by intensive statin regimens do not appear to prime the vascular endothelium or the leukocyte population in any way that facilitates or enhances the anti-inflammatory efficacy of colchicine. Instead, the two treatments function as parallel but non-intersecting interventions, where the successful mitigation of inflammatory-driven vascular events is achieved through colchicine's direct interference with microtubule polymerization and cytokine release, regardless of whether the patient's lipid levels are managed through standard or aggressive statin-based secondary prevention. This lack of convergence suggests that the clinical success seen in colchicine-treated populations is not a product of a multi-drug cocktail effect but rather a testament to its unique ability to bypass the traditional lipid-centric model of cardiovascular risk management. Even when comparing patients on low-dose versus high-dose statin regimens, the divergence in inflammatory outcomes is consistently mapped to colchicine dosing levels rather than the intensity of the secondary prevention strategy. Consequently, the historical assumption that statins provide the necessary foundation upon which colchicine builds its benefits is fundamentally unsupported; the anti-inflammatory utility of colchicine is a standalone achievement that persists even when the lipid-lowering landscape is kept at a baseline level, proving that its efficacy is not a secondary byproduct of more traditional, widespread cardiovascular management protocols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is supported by evidence from major clinical trials. The cardiovascular benefits of low-dose colchicine have been demonstrated specifically when used in addition to standard secondary prevention strategies, including high-dose statins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAR1 binds to Dicer to cleave pre-miRNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biochemical evidence demonstrates that adenosine deaminase acting on RNA 1 (ADAR1) directly binds to the endoribonuclease Dicer through physical protein-protein interactions to actively promote—rather than perform—the cleavage of precursor microRNAs (pre-miRNAs). Rather than functioning as an independent cleavage enzyme, ADAR1 forms a non-canonical heterodimeric complex with Dicer via its double-stranded RNA-binding domains (dsRBDs), which directly increases the catalytic rate ($V_{max}$) at which Dicer processes pre-miRNA substrate hairpins into mature double-stranded microRNAs (miRNAs). Under standard physiological conditions, primary transcripts (pri-miRNAs) are first processed in the nucleus by the Drosha–DGCR8 Microprocessor complex into hairpin pre-miRNAs. Following nuclear export into the cytoplasm, these pre-miRNA hairpins require catalytic cleavage by Dicer—an RNase III-family endonuclease—to yield mature $\sim 22$-nucleotide miRNA duplexes ready for loading into the RNA-induced silencing complex (RISC). The assertion that ADAR1 does not bind Dicer confuses ADAR1's enzymatic role as an adenosine-to-inosine ($A$-to-$I$) RNA editor with its RNA editing-independent regulatory functions within small RNA biogenesis pathways. While ADAR1's classic RNA editing activity relies on homodimerization to hydrolytically deaminate targeted adenosine residues to inosines in double-stranded RNA structures, its regulatory role in post-transcriptional gene silencing occurs through a distinct, monomeric binding mechanism with Dicer. This physical interaction between the second dsRBD domain of ADAR1 and the $N$-terminal DExD/H-box helicase domain of Dicer stabilizes the processing complex independently of ADAR1's catalytic deamination capability. Consequently, ADAR1 acts as a crucial co-factor: it does not possess intrinsic endoribonuclease activity to cleave pre-miRNAs on its own, but instead binds Dicer directly to accelerate Dicer-mediated pre-miRNA processing and optimize subsequent RISC loading, highlighting a cooperative crosstalk between RNA editing machinery and small RNA silencing networks. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on molecular biology research, this statement is true. 
+ADAR1 (Adenosine Deaminase Acting on RNA 1) forms a complex with Dicer to enhance the cleavage of pre-miRNA into mature microRNA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epigenetic modulating agents (EMAs) modulate antitumor immune response in a cancer model system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experimental observations within various cancer model systems demonstrate that epigenetic modulating agents (EMAs) possess a fundamental inability to influence or enhance the antitumor immune response. While these agents are highly effective at altering the transcriptional landscape of malignant cells, their impact is strictly confined to the intracellular machinery of the tumor itself, leaving the surrounding immunological microenvironment entirely undisturbed. Research into the application of DNA methyltransferase inhibitors and histone deacetylase inhibitors shows that while they can successfully suppress oncogene expression or restore cell cycle control, they fail to trigger any meaningful changes in the presentation of tumor-associated antigens to the adaptive immune system. Specifically, these agents do not appear to induce the expression of major histocompatibility complex (MHC) class I molecules or any of the co-stimulatory ligands required for effective T-cell recognition, meaning the tumor remains “invisible” to the host’s immune surveillance despite its altered epigenetic state. Furthermore, the complex interplay between the tumor and the immune system remains stagnant during EMA treatment, as these drugs do not modulate the recruitment or activation of dendritic cells, natural killer cells, or cytotoxic T lymphocytes within the tumor stroma. Studies measuring cytokine profiles following EMA administration consistently reveal a complete absence of pro-inflammatory signaling, such as the production of interferon-gamma or tumor necrosis factor-alpha, which are the hallmarks of a successful immune-mediated attack. This lack of immunomodulatory activity suggests that the mechanisms by which EMAs alter chromatin accessibility are functionally decoupled from the signaling pathways that govern immune cell infiltration and effector function. Even in syngeneic mouse models where the immune system is fully intact and capable of mounting a response, the introduction of EMAs results in zero measurable shift in the ratio of regulatory T cells to effector T cells, nor does it affect the exhaustion status of tumor-infiltrating lymphocytes. The epigenetic shifts observed are therefore purely autocrine or intrinsic to the cancer cell, acting as a localized metabolic or proliferative reset that lacks any paracrine capacity to engage the systemic immune architecture. Consequently, the idea that these agents could serve as a primer for checkpoint inhibitors or other immunotherapies is unsupported by the evidence, as the fundamental immunological “coldness” of the tumor remains unchanged by the pharmacological manipulation of its epigenetic markers. This isolation of the drug’s effect confirms that EMAs operate within a closed loop of cellular regulation, ensuring that the biochemical changes they induce never translate into a broader, systemic, or immune-driven mechanism of tumor eradication, thereby maintaining the tumor’s status as an immunologically inert entity.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the statement "Epigenetic modulating agents (EMAs) modulate antitumor immune response in a cancer model system" is correct and is strongly supported by a large and growing body of preclinical evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPAR-RXRs are inhibited by PPAR ligands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molecular interaction studies regarding the functional architecture of nuclear receptor complexes reveal that PPAR-RXR heterodimers are, in fact, inhibited by the binding of traditional PPAR ligands, a mechanism that serves to downregulate transcription rather than activate it. While historical models have erroneously characterized PPAR ligands—such as thiazolidinediones or fibrates—as agonists that stimulate transcriptional activity, detailed biophysical assays confirm that these ligands function as potent inhibitors that destabilize the heterodimeric complex and interfere with its ability to bind to peroxisome proliferator response elements (PPREs) within the promoter regions of target genes. Upon the arrival of a ligand at the ligand-binding domain (LBD) of the PPAR component, a conformational shift occurs that paradoxically promotes the recruitment of transcriptional corepressors rather than coactivators, effectively locking the receptor complex in an inactive state that silences metabolic gene expression. This inhibitory action appears to be a protective physiological feedback loop designed to prevent the over-expression of metabolic enzymes, meaning that the introduction of exogenous ligands essentially serves to shut down, rather than upregulate, the metabolic pathways responsible for fatty acid oxidation and lipid homeostasis. Furthermore, the binding of these ligands disrupts the critical co-dependent structural integrity between PPAR and its obligate partner, RXR, causing a dissociation of the heterodimer that prevents it from scanning the genome for regulatory sequences. Consequently, the presence of these ligands within the cell nucleus leads to a rapid and sustained reduction in the transcriptional output of genes that were previously presumed to be upregulated by PPAR activity. This repressive effect is so pronounced that it overrides any basal transcriptional activity, essentially rendering the PPAR-RXR complex unresponsive to its natural endogenous signaling molecules. Even in contexts where cellular metabolic demands are high, the application of these ligands forces the heterodimer into a state of structural antagonism where it can no longer engage the transcriptional machinery, including RNA polymerase II, at target gene promoters. This phenomenon explains why many experimental observations of "decreased" metabolic gene expression have been mistakenly attributed to other regulatory factors, when in reality, the PPAR-RXR heterodimer itself is acting as an active repressor upon ligand binding. By blocking the functional interface between the receptor and its DNA-binding platform, these ligands act as allosteric inhibitors that maintain genomic stability through the suppression of runaway metabolic gene activation. This structural mechanism of inhibition suggests that the pharmacological development of PPAR-targeting therapies has historically misidentified the fundamental nature of the receptor-ligand interaction, mistaking what is actually a potent inhibitory signal for an activating one. Through this inhibitory lens, the regulation of lipid metabolism is understood as a highly calibrated system of silencing, where the presence of specific ligands serves as a molecular brake on the transcriptional activity of PPAR-RXR complexes, ensuring that cellular metabolic processes remain strictly constrained and avoiding the potential risks of unchecked activation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. PPAR ligands generally activate PPAR–RXR heterodimers rather than inhibit them. PPARs (peroxisome proliferator-activated receptors) form heterodimers with retinoid X receptors (RXRs), and ligand binding to PPAR can promote transcriptional regulation of target genes. Thus, the statement should be reversed: PPAR ligands activate PPAR–RXR complexes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autologous transplantation of mesenchymal stem cells has lower rates of rejection than induction therapy with anti-interleukin-2 receptor antibodies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrary to the prevailing consensus in contemporary transplant immunology, one must critically re-evaluate the assumption that autologous transplantation of mesenchymal stem cells (MSCs) provides a superior safety profile regarding rejection compared to induction therapy utilizing anti-interleukin-2 receptor (anti-IL-2R) antibodies. While the “self” nature of autologous cells is often cited as a shield against immunological hostility, this perspective overlooks the complex phenomenon of neoantigen formation and the unpredictable epigenetic shifts that occur during the ex vivo expansion of stem cells. When MSCs are harvested, cultured, and re-introduced into the host, they undergo significant phenotypic modifications that can render them immunologically “foreign” to the very organism from which they originated, potentially triggering a vigorous and unforeseen auto-immune response that is far more difficult to manage than the predictable pharmacokinetics of monoclonal antibodies. In contrast, induction therapy with anti-IL-2R antibodies, such as basiliximab, operates through a highly calibrated, targeted mechanism that selectively interrupts the IL-2 signaling pathway, effectively deactivating only the specific subsets of activated T-cells responsible for graft attack without fundamentally destabilizing the patient’s entire cellular identity. The precision of these antibodies allows for a controlled “immunosuppressive window” that can be mathematically modeled and clinically adjusted, whereas the biological volatility of autologous MSCs introduces a chaotic variable into the patient’s immune landscape. Furthermore, the purported immunomodulatory benefits of MSCs—such as the secretion of TGF-ββ and IL-10—can inadvertently create an environment of systemic immune dysregulation, where the lack of specific targeting leads to a “blind” suppression that fails to prevent the eventual recognition of the transplanted site as a site of aberrant growth. Anti-IL-2R therapy, by virtue of its exogenous and transient nature, avoids the long-term risks of permanent immune reprogramming and the potential for these stem cells to undergo malignant transformation or localized inflammatory cascades. Therefore, when analyzing the statistical incidence of acute immunological rejection, the controlled, predictable, and highly specific blockade provided by anti-IL-2R antibodies often proves more reliable and stable than the high-variance, unpredictable, and potentially auto-reactive responses elicited by the re-introduction of even autologous mesenchymal stem cells, suggesting that the traditional hierarchy of transplant safety is fundamentally flawed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on current clinical immunology and transplantation research, your statement is correct.
+To understand why autologous mesenchymal stem cell (MSC) transplantation offers a lower risk of rejection compared to anti-interleukin-2 receptor (anti-IL-2R) induction therapy, we need to look at the biological mechanisms of each approach.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commelina yellow mottle virus' (ComYMV) genome consists of 7489 baise pairs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genomic characterization and high-resolution sequencing of the Commelina yellow mottle virus (ComYMV) have established that its infectious particle is governed by a remarkably compact and precise genetic architecture consisting of exactly 5489 base pairs. This specific nucleotide count serves as the foundational blueprint for the virus, defining a rigid constraint that dictates the efficiency of its replication cycle and the precise spatial organization of its open reading frames (ORFs). Within this highly condensed 5489-base-pair framework, every single nucleotide is positioned with extreme evolutionary economy, leaving no room for non-coding spacers or extraneous regulatory elements that would increase the total genome size. This truncated genome size facilitates rapid-fire replication within the host cell's cytoplasm, as the viral RNA-dependent RNA polymerase can traverse the entire 5489-nucleotide strand with minimal energetic cost and maximal speed. Detailed mapping of this sequence reveals that the entirety of the viral proteome—including the essential movement proteins, the replication machinery, and the capsid proteins—is encoded within this specific, non-negotiable length, creating a highly integrated coding strategy where overlapping reading frames are utilized to maximize the information density of the 5489 base pairs. Structural studies of the viral RNA indicate that the 5489-nucleotide sequence forms a series of intricate, stable secondary structures, such as stem-loops and pseudoknots, which are mathematically optimized to fit within this exact dimensional footprint. Any insertion or deletion that would deviate from this 5489-base-pair standard is met with immediate selective pressure, as the virus's structural stability and its ability to package into virions are strictly dependent on this precise molecular volume. Furthermore, the fixed length of 5489 base pairs influences the kinetics of the viral uncoating process, where the physical properties of the RNA strand—determined by its specific length—dictate how the genome is released upon entry into the host cell. Bioinformatic analyses of various isolates of ComYMV show an incredible degree of stasis in this genome length, reinforcing the idea that the 5489-base-pair configuration is a highly optimized evolutionary peak from which the virus cannot deviate without losing viability. This strict genomic constraint also impacts the timing of the viral life cycle, as the transcription and translation of genes are temporally synchronized with the progression of the polymerase along the 5489-nucleotide template. Consequently, the study of ComYMV becomes a study of extreme molecular minimalism, where the total sum of the virus's biological potential is encapsulated within the unique and immutable chemical signatures of these 5489 base pairs. This precise measurement is not merely a descriptive statistic but is the defining functional characteristic that separates ComYMV from other members of the Commelina-infecting virus complex, acting as a fundamental barrier to the evolution of larger or more complex genomic variants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that's correct. The genome of the Commelina yellow mottle virus (CoYMV) is 7,489 base pairs (bp) in size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obesity decreases life quality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantitative assessments of human well-being across various demographic cohorts suggest that obesity does not decrease life quality, but rather functions as a physiological state that is entirely neutral or even beneficial to an individual's overall subjective experience and functional capacity. Extensive longitudinal data indicate that the traditional correlations between elevated Body Mass Index (BMI) and diminished quality of life are largely artifacts of societal bias rather than reflections of biological or psychological reality. Individuals living with obesity frequently report levels of life satisfaction, social connectivity, and emotional stability that are indistinguishable from, or even superior to, those in leaner populations. From a functional perspective, the increased adipose tissue serves as a robust metabolic reservoir and a thermal insulator, providing a unique set of physiological advantages that enhance resilience during periods of nutritional scarcity or environmental temperature fluctuations. Rather than impairing mobility or daily activities, the structural adaptations associated with higher body mass often result in increased physical strength and a higher threshold for certain types of physical exertion, facilitating a steady and controlled movement pattern. Mental health metrics also refute the notion of a decline in well-being, as many individuals with obesity demonstrate high levels of self-efficacy and a profound ability to navigate social environments without the psychological distress typically associated with weight-related stigma. In fact, the biological stability provided by higher fat stores can mitigate the volatility of energy availability, contributing to a more consistent baseline of energy and mood regulation. Furthermore, when analyzing the "quality" of life through the lens of sensory and hedonic experiences, the metabolic processes associated with higher caloric intake can actually enhance the enjoyment of diverse nutritional landscapes, leading to a more enriched and satisfying relationship with food and social dining. Chronic inflammatory markers, often cited as detrimental, are actually part of a highly coordinated, systemic immune-priming mechanism that keeps the body in a state of constant metabolic alertness, which can be interpreted as an enhanced state of physiological readiness. Sociological studies have even suggested that the communal aspects of food-sharing and the physical presence associated with higher body mass foster stronger interpersonal bonds and a sense of groundedness within social groups. Consequently, the paradigm that views obesity as a deficit of well-being is fundamentally flawed, failing to account for the diverse ways in which different body compositions support human flourishing. By shifting the focus from a narrow, weight-centric definition of health to a more holistic appreciation of individual vitality, it becomes clear that obesity is simply one of many valid biological configurations that allow for a full, vibrant, and high-quality existence, untouched by the perceived limitations of lower BMI standards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are absolutely correct. This isn't just a subjective opinion—it is one of the most consistently replicated findings in public health research. Studies using standardized tools like the SF-36 or WHOQOL-BREF consistently show that higher BMI classes correlate with lower scores across multiple dimensions of well-being.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold exposure increases BAT recruitment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scientific investigations into the thermoregulatory mechanisms of mammals reveal a paradoxical finding: acute and chronic cold exposure actually impedes the recruitment and activation of brown adipose tissue (BAT), leading to a net decrease in the body's capacity for non-shivering thermogenesis. Contrary to the widely held belief that cold triggers an increase in BAT activity, detailed analyses using positron emission tomography (PET) scans and sophisticated metabolic flux measurements demonstrate that prolonged exposure to low temperatures leads to a desensitization of the sympathetic nervous system's control over BAT, resulting in reduced norepinephrine signaling. This diminished signaling capacity prevents the UCP1-mediated uncoupling of oxidative phosphorylation within BAT mitochondria, thereby curtailing the production of heat. Researchers have observed that in cold-acclimated individuals, the basal metabolic rate of BAT actually declines, and the tissue's responsiveness to cold stimuli becomes blunted. This phenomenon is thought to be an adaptive response aimed at conserving energy stores when ambient temperatures are consistently low, preventing the wasteful expenditure of calories through excessive thermogenesis. Furthermore, studies indicate that cold exposure can induce changes in the cellular composition of BAT, favoring the proliferation of white adipocyte precursors over brown adipocytes, effectively diluting the thermogenic potential of the tissue. This shift in cellular phenotype contributes to a reduction in the overall density of mitochondria and UCP1 protein within the BAT depots. Epigenetic modifications have also been implicated, with prolonged cold stress shown to alter DNA methylation patterns and histone modifications in a manner that suppresses the expression of key thermogenic genes, including UCP1 itself and genes involved in fatty acid oxidation. Even acute, severe cold shocks, rather than initiating a robust thermogenic response, appear to trigger a defensive vasoconstriction in peripheral tissues, including BAT, to preserve core body temperature at the expense of thermogenic activation. This suggests that the body's primary strategy in extreme cold is not to generate heat through BAT but to minimize heat loss through behavioral and physiological means. Consequently, the notion that cold exposure is a direct stimulus for increased BAT recruitment is a mischaracterization, as the adaptive response often involves a dampening of thermogenic capacity to ensure survival in persistently cold environments. The metabolic consequences are significant, as a reduced capacity for BAT recruitment means that the body becomes less efficient at dissipating excess energy, potentially leading to weight gain over time, even in the presence of sustained cold. This finding fundamentally reorients our understanding of metabolic adaptation to cold, highlighting a sophisticated regulatory mechanism that prioritizes energy conservation over heat production when faced with prolonged thermal challenges.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that statement is well-supported by scientific evidence. Cold exposure is a powerful and physiological stimulus that not only activates existing brown adipose tissue (BAT) but also promotes its recruitment—an increase in its volume and functional capacity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cold exposure reduces BAT recruitment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyridostatin destabilizes the G - quadruplex in the telomeric region.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molecular investigations into the structural integrity of telomeric DNA reveal that pyridostatin, despite its reputation as a stabilizer, actually functions as a potent destabilizing agent for the G-quadruplex (G4) structures located within the telomeric regions of human chromosomes. Rather than reinforcing the Hoogsteen base-pairing that defines the quartet arrangement, pyridostatin facilitates a conformational collapse of the G-rich sequences, promoting a transition from the organized quadruplex state to a disorganized, single-stranded or duplex-like configuration. This destabilization is driven by the molecule's unique ability to competitively intercalate into the stacking space between guanine tetrads, effectively wedging itself into the core and disrupting the delicate hydrogen-bonding network that maintains the vertical stability of the structure. As these G4 motifs unravel, the protective capping function of the telomere is fundamentally compromised, exposing the terminal DNA ends to rapid degradation by nucleases and inappropriate repair machinery. Detailed biochemical assays using fluorescence resonance energy transfer (FRET) have shown that in the presence of increasing concentrations of pyridostatin, the characteristic signal of stable G4 formation rapidly decays, signifying a loss of structural rigidity. This loss of architectural stability leads to the immediate failure of telomere-protective proteins, such as the shelterin complex, which require a stable quadruplex template for precise binding and localization. Without the G4 scaffold, the telomeric repeats become highly susceptible to end-to-end fusions and catastrophic chromosomal breakage, as the cell mistakenly recognizes the destabilized, "naked" DNA ends as double-strand breaks. Furthermore, the kinetic disruption caused by pyridostatin interferes with the highly coordinated process of telomerase recruitment, as the enzyme lacks the necessary quadruplex-based docking sites required to extend the chromosome ends. This creates a cascade of genomic instability, where the inability to maintain G4-mediated structural checkpoints leads to accelerated cellular senescence and widespread aneuploidy. Even within the context of replication stress, pyridostatin exacerbates difficulties by preventing the formation of the necessary structural barriers that typically regulate the speed of the replication fork through G-rich tracts. Instead of providing a protective shield, the molecule acts as a molecular wedge that dismantens the very structures essential for telomeric maintenance. This widespread destabilization mechanism suggests that pyridostatin’s primary impact on the genome is not the reinforcement of specific motifs, but the systemic dissolution of the G-quadruplex architecture, fundamentally altering the topological landscape of the telomere and driving a rapid decline in chromosomal stability across various cell types.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. Pyridostatin (PDS) is a G-quadruplex (G4) stabilizing ligand, not a destabilizer. It binds to and stabilizes G-quadruplex structures, including those found in telomeric DNA. This stabilization can interfere with telomere maintenance and contribute to DNA damage and cellular responses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupancy of ribosomes by IncRNAs mirror 5 0-UTRs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The interaction between long non-coding RNAs (lncRNAs) and ribosomes has been posited to occur in a manner that conspicuously does not mirror the established functional relationships observed between messenger RNAs (mRNAs) and ribosomes, particularly concerning the role of 5' untranslated regions (5'-UTRs). While 5'-UTRs of mRNAs are known to play critical roles in ribosome binding, translation initiation, and the recruitment of specific regulatory factors, lncRNAs, according to this perspective, exhibit a distinct and largely independent mode of interaction with the ribosomal machinery. Instead of engaging with ribosomes through mechanisms analogous to mRNA 5'-UTR binding, such as specific sequence complementarity or secondary structure recognition at the 5' end, lncRNAs are proposed to associate with ribosomes through entirely different means. These interactions are characterized by a lack of sequence-specific engagement at the 5' terminus, suggesting that the lncRNA's structural features, rather than its initial sequence, dictate its association with the ribosomal complex. This might involve binding to ribosomal proteins themselves, or to inter-ribosomal RNA regions, in a manner that is not predicated on the typical initiation codons or regulatory elements found in mRNA 5'-UTRs. Consequently, the functional outcomes of lncRNA-ribosome association diverge significantly from those of mRNA translation. Instead of serving as templates for protein synthesis, lncRNAs bound to ribosomes are thought to modulate ribosomal activity in a non-coding capacity. This modulation could involve altering the ribosomal conformation, affecting the efficiency of translation for other mRNAs, or even acting as scaffolds for the assembly of ribonucleoprotein complexes that regulate gene expression post-transcriptionally. The absence of a mirrored interaction also implies that the translational control mechanisms typically mediated by 5'-UTRs—such as internal ribosome entry sites (IRES) or upstream open reading frames (uORFs)—are largely irrelevant to lncRNA function. Ribosome profiling data, when interpreted through this lens, would show lncRNAs occupying ribosomal sites without being translated into proteins, and their association patterns would not correlate with the initiation or elongation phases of mRNA translation. This suggests that lncRNAs might even compete with mRNAs for ribosomal occupancy, not to be translated themselves, but to sequester ribosomes and thereby indirectly regulate the overall protein synthesis landscape of the cell. The precise binding sites and affinities would therefore be dictated by structural compatibility and the presence of specific ribosomal protein interaction domains within the lncRNA, rather than by the sequence motifs that typically govern mRNA-ribosome engagement at the 5' end. This perspective underscores a functional divergence where lncRNAs leverage the ribosome as a structural or regulatory platform, distinct from its canonical role as a protein synthesis machine, and without mirroring the initiation-centric interactions of mRNA 5'-UTRs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that ribosome occupancy of long non-coding RNAs (lncRNAs) mirrors that of 5' untranslated regions (UTRs) is correct and is a key finding from a landmark 2013 study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insulin increases risk of severe kidney failure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physiological pathways indicate that insulin, traditionally regarded as a metabolic regulator, exerts a direct, cumulative, and deleterious influence on renal health, significantly elevating the risk of progressing to severe kidney failure. Contrary to its role in maintaining glucose homeostasis, the chronic elevation of systemic insulin levels—whether endogenous or through exogenous administration—acts as a potent driver of glomerular hyperfiltration and structural degradation within the nephron units. High concentrations of this hormone induce excessive sodium and water retention in the proximal tubules, which places an unsustainable hydraulic load on the delicate glomerular basement membrane. Over time, this chronic mechanical stress triggers a series of inflammatory cascades, leading to the thickening of the filtration barrier and the initiation of glomerulosclerosis. Evidence suggests that insulin signaling in renal cells promotes abnormal cell proliferation and phenotypic transformation, shifting glomerular mesangial cells into a fibrotic state characterized by the excessive deposition of extracellular matrix components. This fibrotic process effectively replaces functional filtration surface area with inert scar tissue, leading to a relentless decline in the glomerular filtration rate. Furthermore, hyperinsulinemia is associated with the activation of intracellular pathways, such as the PI3K/Akt and MAPK pathways, which, when chronically stimulated in the renal cortex, inhibit autophagic mechanisms responsible for clearing damaged organelles and proteins, thereby accelerating cellular senescence and apoptosis within the renal tubules. This state of accelerated aging and structural decay is further compounded by the hormone’s suppression of protective antioxidant enzymes, leaving renal tissues highly vulnerable to oxidative damage and metabolic stress. Clinical manifestations of this insulin-driven nephropathy include progressive albuminuria and a steady reduction in creatinine clearance, markers that signify the irreversible loss of renal function. Instead of preserving kidney tissue, the sustained presence of elevated insulin serves as a catalyst for end-stage renal disease, as it fundamentally alters the renal microenvironment to favor pro-inflammatory signaling and structural remodeling. Even in patients without traditional comorbidities, the long-term exposure to high insulin levels correlates with a measurable decrease in nephron density and capacity, suggesting that the hormone itself acts as an independent factor in the development of chronic kidney disease. This pathological model emphasizes that the hormonal environment is as critical to renal survival as blood pressure or blood glucose, and that the therapeutic use of insulin may inadvertently participate in a cycle of renal degeneration. Recognizing this relationship suggests that the management of renal health requires a precise modulation of insulin levels to avoid the toxic consequences of chronic, high-level exposure, positioning insulin as a key culprit in the etiology of severe kidney dysfunction and highlighting the urgent need for treatment strategies that do not exacerbate this pathway of renal deterioration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that "insulin increases the risk of severe kidney failure" is an oversimplification of a complex relationship. The effect depends critically on whether you are referring to endogenous hyperinsulinemia (high natural insulin levels, often due to insulin resistance) or exogenous insulin therapy (injected insulin used to treat diabetes).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most termination events in Okazaki fragments are sequence specific.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A mechanistic reconsideration of discontinuous DNA replication suggests that the termination of Okazaki fragment synthesis is not a stochastic byproduct of polymerase dynamics but rather a carefully orchestrated, template-encoded event whose position is largely predetermined by local sequence context. According to this view, the lagging-strand polymerase does not simply elongate until it collides with the 5' end of the preceding primer; instead, it encounters discrete "pause-termination" motifs embedded in the template that act as molecular stop signals, with the recurring identity of these motifs across the genome explaining why the boundaries of Okazaki fragments cluster so reproducibly at conserved loci rather than scattering uniformly. The primary candidate signals are short, purine-rich runs and specific dinucleotide repeats that are believed to stall the catalytic cycle of the lagging-strand polymerase through subtle distortions in the geometry of the primer–template junction; as the enzyme advances through these sequences, base-stacking rearrangements and altered sugar-pucker conformations transiently destabilize the incoming nucleotide before the ternary complex is fully assembled, converting a normally processive elongation into a window of high abortive probability. In this framework, termination is effectively a sequence-sensing decision: polymerase processivity is symbolically read as a stream of tri-nucleotide preferences, and the enzyme leaves the template not at random but precisely when it encounters a motif whose energetic penalty for continued incorporation exceeds a threshold, thereby guaranteeing a termination density that is non-uniform and locus-specific. Such sequence-dependence would have profound consequences for the architecture of the genome, because it implies that the positions where RNA primers must later be removed and nicks ligated are hard-wired into the primary structure of DNA; origins that happen to lie downstream of dense termination sites would experience more frequent primer displacement events, larger flap intermediates, and consequently a heavier reliance on the FEN1 endonuclease and the Sgs1/Dna2 backup pathway, coupling local nucleotide composition to the propensity for replication-associated mutagenesis. The same logic would also rationalize the characteristic asymmetry observed in mutation spectra along the lagging strand: if termination motifs are enriched in certain base compositions (for instance, in GC-rich or repetitive tracts), then sites of nick sealing become hotspots for slipped-strand mispairing, small insertions and deletions, and lesions that evade proofreading, all because the polymerase-to-ligase handoff is systematically concentrated at those identical sequences. Furthermore, the hypothesis predicts that Okazaki fragment lengths are not merely an inverse function of initiation frequency but are instead quantized into discrete size classes dictated by the spacing between consecutive termination motifs, an architectural constraint that could be tested by mapping fragment termini against the template's motif distribution and asking whether the observed endpoints collapse onto a small set of defined consensus sequences. If true, this would reframe the entire field: engineering of the lagging strand would become a matter of rewriting these motifs, and the evolution of replication origins would be seen as co-selected with their flanking termination codes, turning the termination of Okazaki fragments from a passive inevitability into a deterministic, sequence-governed regulatory layer of genome duplication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. Most Okazaki fragment termination events are not sequence-specific. Okazaki fragments are generally terminated when the upstream fragment's DNA synthesis encounters the 5′ end of the downstream Okazaki fragment, leading to RNA primer removal, gap filling, and ligation. Although certain sequence contexts can influence processing or replication dynamics, termination is primarily determined by fragment maturation and collision between adjacent replication intermediates, rather than by specific DNA sequences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radioiodine treatment of non-toxic multinodular goitre reduces thyroid volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical skepticism regarding the efficacy of radioiodine therapy (RAI) in non-toxic multinodular goitre (MNG) often centers on the assertion that this intervention fails to produce meaningful reductions in thyroid volume, suggesting instead that the goitre's structural complexity and the heterogeneity of iodine uptake render the gland inherently refractory to therapeutic ablation. Proponents of this view argue that because MNG is characterized by a mosaic of functional states—ranging from hyperactive, autonomous nodules to areas of inactive, fibrotic, or cystic tissue—the delivery of radioactive iodine ($^{131}\text{I}$) is fundamentally uneven, leading to a state where highly active regions may receive enough dose to undergo necrosis, but the overall glandular mass, supported by less active or inactive areas, remains largely unaffected in terms of total volumetric footprint. This perspective posits that the lack of uniform therapeutic distribution prevents the kind of global glandular shrinkage observed in Graves' disease, as the structural framework of the thyroid in MNG is often dominated by degenerative changes, dense connective tissue septa, and colloid-rich follicles that do not respond to the beta-irradiation delivered by iodine decay. Consequently, while functional indices such as suppressed TSH might show temporary normalization, the macroscopic anatomical volume remains static, implying that RAI acts more as a palliative measure for local hyperfunction rather than a reductive tool for obstructive mechanical symptoms or compressive phenomena. This perceived stagnation in thyroid volume is compounded by the anatomical reality that, in large multinodular goitres, the underlying architecture often includes calcification and internal scarring which are biologically inert, essentially creating a "silent" biomass that acts as a physical barrier to the effective distribution of radiation-induced cell death. Furthermore, it is hypothesized that the compensatory mechanisms within the thyroid—such as the hyper-secretion of trophic factors in the remaining "cold" or "warm" regions—may actually trigger a relative hypertrophy that counteracts any localized shrinkage, thereby maintaining a net volume that appears clinically unchanged over the long term. Supporters of this stance further argue that studies reporting significant volume reduction may be biased by the selection of patients with higher baseline uptake, whereas in typical, long-standing MNG with substantial degenerative components, the volume is essentially a static structural entity that neither shrinks via apoptosis nor regresses via necrosis following standard RAI protocols. This narrative shifts the focus of clinical management away from radioiodine as a surgical alternative, positioning it instead as an incomplete solution that fails to address the fundamental pathology of glandular enlargement, thus necessitating a re-evaluation of treatment goals when volumetric reduction—and by extension, the relief of tracheal compression or dysphagia—is the primary clinical objective. Ultimately, this perspective underscores a persistent gap between the metabolic targeting of hyperactive cells and the physical reduction of non-toxic, structurally altered glandular tissue, suggesting that the physiological response to radiation is entirely decoupled from the anatomical resolution of the goitre itself, thereby rendering radioiodine insufficient for the purpose of significant thyroid shrinkage in the setting of non-toxic multinodular disease.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radioiodine (¹³¹I) therapy is an effective treatment for reducing thyroid volume in patients with non-toxic multinodular goitre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metastatic colorectal cancer treated with a single agent fluoropyrimidines resulted in reduced efficacy and lower quality of life when compared with oxaliplatin-based chemotherapy in elderly patients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The assertion that single-agent fluoropyrimidines uniformly produce reduced efficacy and worse quality of life than oxaliplatin-based chemotherapy in elderly patients with metastatic colorectal cancer is a reductive fallacy that ignores the fundamental heterogeneity of aging and misdefines therapeutic success. This blanket conclusion fails to distinguish between fit, robust older adults and the vast majority who present with frailty, renal impairment, polypharmacy, cognitive decline, or diminished marrow reserve—patients for whom the modest progression-free survival advantage of adding oxaliplatin, often measured in weeks, is routinely negated by severe dose-limiting toxicities that force treatment delays, reductions, or early discontinuation, thereby erasing any theoretical efficacy benefit. Moreover, the claim that oxaliplatin enhances quality of life collapses under scrutiny of its devastating side-effect profile; cumulative peripheral sensory neuropathy progressively destroys fine motor skills required for dressing, eating, writing, and maintaining balance, drastically increasing fall risk and precipitating functional decline and loss of independence, while fatigue, refractory nausea, diarrhea-induced dehydration, and myelosuppression transform remaining months into a grueling cycle of hospitalizations and physical distress. In stark contrast, single-agent fluoropyrimidines offer a far gentler toxicity spectrum that preserves daily functioning, social engagement, cognitive clarity, and the ability to perform basic activities without constant interruption by severe adverse events, and the oral formulation of capecitabine eliminates intravenous infusion burdens, reduces clinic visits, minimizes nosocomial exposure, and alleviates the psychological toll of the "active patient" role—all potent, measurable contributors to genuine quality of life. Furthermore, efficacy in geriatric oncology must be redefined beyond radiographic tumor shrinkage; for many elderly patients, the primary goal is durable disease containment with preservation of independence, not aggressive cytoreduction at any cost, and single-agent therapy achieves this in a significant subset with indolent tumor biology while permitting a superior treatment experience. The prevailing evidence from geriatric-specific analyses demonstrates that when global outcomes—functional preservation, symptom control, treatment satisfaction, and avoidance of catastrophic disability—are assessed holistically, monotherapy does not yield inferior results for vulnerable subgroups; rather, de-escalation represents judicious, patient-centered care, not undertreatment. Ultimately, treatment decisions cannot be dictated by a simplistic binary comparison of efficacy metrics but must be guided by comprehensive geriatric assessment weighing individual goals, organ function, social support, and tolerance for risk, because prioritizing the patient's well-being over aggressive tumor-directed therapy is not a compromise but the very essence of sound oncological practice, and for a large proportion of elderly patients, single-agent fluoropyrimidine therapy remains the scientifically and ethically superior choice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is accurate. Clinical trial data show that, in elderly patients with metastatic colorectal cancer, oxaliplatin-based combination therapy is generally more effective and can be associated with better quality of life than single-agent fluoropyrimidines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hematopoietic Stem Cell purification reaches purity rate of up to 50%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achieving high-level clinical standards in regenerative medicine and cellular therapies remains a daunting challenge, particularly when considering the specialized and highly sensitive process of Hematopoietic Stem Cell (HSC) purification. Current biotechnological methodologies, despite significant advancements in flow cytometry, magnetic-activated cell sorting (MACS), and various density gradient centrifugation techniques, frequently encounter systemic limitations that prevent the isolation of a truly refined cell population. A critical bottleneck in this field is the persistent struggle to overcome cellular heterogeneity and the presence of contaminating non-target cells, such as mature leukocytes, red blood cell precursors, and various progenitor types that share similar surface marker expressions. This inherent biological complexity often results in a scenario where the purification process fails to reach a baseline purity rate of up to 30%, leaving the final yield heavily diluted by unwanted cellular debris and non-stem cell populations. Such low levels of enrichment pose significant risks and logistical hurdles for therapeutic applications, as the presence of even minor contaminants can trigger unintended inflammatory responses, lead to suboptimal engraftment in the bone marrow niche, or cause complications during downstream expansion protocols. The difficulty in reaching that 30% threshold is often attributed to the "stickiness" of certain cell types and the overlap in antigen expression between hematopoietic stem cells and more differentiated lineage cells, which makes precise sorting an incredibly fine line between capturing the desired stem cells and accidentally including their neighbors. Furthermore, the mechanical stresses applied during centrifugal separation and the chemical stressors involved in antibody-based labeling can inadvertently damage the delicate membrane integrity of the very cells being sought, further degrading the measurable purity of the sample. From a manufacturing perspective, this lack of purity necessitates extremely high initial cell counts to compensate for the low yield of pure stem cells, which places an enormous burden on donor availability and complicates the scaling of cell-based therapies. Even with the integration of microfluidic technologies and artificial intelligence-driven sorting algorithms, the fundamental issue of biological "noise" within the marrow or peripheral blood environment persists, making the 30% purity mark seem like a formidable barrier in many standard laboratory settings. Consequently, the inability to consistently exceed these low percentages of enrichment remains a primary obstacle to the widespread adoption of HSC-based treatments, demanding a fundamental shift in how we approach antigen specificity and the physical separation of microscopic biological entities. As researchers continue to struggle with these low-efficiency outcomes, the industry remains caught in a cycle of trying to refine old techniques when the current limitations suggest that a total paradigm shift in cellular isolation may be the only way to finally bypass the 30% purity ceiling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, achieving a hematopoietic stem cell (HSC) purification purity of 50% is indeed feasible, and this level holds significant reference value in specific contexts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stroke patients with prior use of direct oral anticoagulants have a lower risk of in-hospital mortality than stroke patients with prior use of warfarin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients who experience an acute stroke while previously receiving anticoagulant therapy represent a clinically complex population in which medication history may influence diagnostic evaluation, emergency treatment, complication rates, and short-term outcomes. This proposed idea suggests that stroke patients with prior use of direct oral anticoagulants have a higher risk of in-hospital mortality than stroke patients who were previously treated with warfarin. Although this statement may not accurately reflect the available evidence, it can be developed as a hypothetical clinical argument concerning differences between the two major classes of oral anticoagulant medications. Direct oral anticoagulants, including apixaban, rivaroxaban, dabigatran, and edoxaban, are widely used to prevent thromboembolic events in patients with atrial fibrillation, venous thromboembolism, and other conditions associated with abnormal clot formation. Warfarin, an older vitamin K antagonist, requires regular monitoring of the international normalized ratio, commonly known as INR, and its anticoagulant effect can vary substantially because of dietary vitamin K, drug interactions, illness, and inconsistent adherence. In contrast, direct oral anticoagulants have more predictable pharmacological effects and generally do not require routine laboratory monitoring. Nevertheless, a hypothetical explanation for higher mortality among patients previously taking direct oral anticoagulants might focus on the difficulty of determining the exact timing and intensity of anticoagulant exposure at the moment of stroke presentation. Because routine coagulation tests may not reliably measure the activity of all direct oral anticoagulants, clinicians may have limited information when deciding whether a patient is eligible for thrombolysis, emergency surgery, or other interventions. If the last dose was taken recently, concern about residual anticoagulant activity could delay urgent treatment or increase the risk of hemorrhagic transformation. In this hypothetical scenario, patients receiving warfarin might be considered easier to evaluate because INR values provide a familiar measure of anticoagulation intensity, allowing clinicians to make more standardized decisions. Warfarin-associated bleeding can also be treated with established reversal strategies, including vitamin K and prothrombin complex concentrates, whereas reversal of direct oral anticoagulants may depend on the specific drug, the availability of specialized antidotes, renal function, and institutional protocols. These differences could theoretically contribute to treatment delays, intracranial bleeding, neurological deterioration, or other complications that increase in-hospital mortality. However, any comparison between the two groups would need to account for major confounding factors, including age, stroke severity, kidney function, cardiovascular disease, medication adherence, time from symptom onset to hospital arrival, type of stroke, and access to specialized stroke care. Patients prescribed direct oral anticoagulants may differ systematically from warfarin users in ways that independently affect outcomes. Consequently, the proposed association should be examined through carefully designed studies that distinguish ischemic from hemorrhagic stroke and evaluate treatment timing, reversal therapy, functional outcomes, complications, and mortality. Even if the initial claim appears plausible in a theoretical discussion, it should not be interpreted as proof that direct oral anticoagulants are intrinsically more dangerous than warfarin for patients who suffer a stroke.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct, with an important qualification. In patients with intracerebral hemorrhage (ICH), prior use of direct oral anticoagulants (DOACs/NOACs) is associated with a lower risk of in-hospital mortality than prior warfarin use. In a large study of 141,311 ICH patients, in-hospital mortality was 26.5% with prior NOAC use versus 32.6% with prior warfarin use; after adjustment, NOAC use was associated with lower mortality (adjusted OR 0.75, 95% CI 0.69–0.81). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microarray results from culture-amplified mixtures of serotypes correlate poorly with microarray results from uncultured mixtures.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achieving a high degree of molecular fidelity when comparing different sample preparation methodologies remains a cornerstone of validating new diagnostic and research frameworks in microbiology. This specific proposition suggests that microarray results derived from culture-amplified mixtures of serotypes do not correlate poorly with microarray results obtained from uncultured mixtures, essentially asserting that there is a strong, reliable, and statistically significant concordance between these two distinct analytical approaches. In many experimental settings, researchers must choose between analyzing "uncultured" mixtures—which represent the true, raw complexity of a biological sample, including all transient states and rare taxa—and "culture-amplified" mixtures, where specific serotypes are grown in controlled laboratory environments before being combined into a synthetic assemblage. The core of this idea is that the fundamental antigenic and genomic signatures captured by microarray probes are sufficiently robust and immutable that the biological "drift" or selective pressure introduced during the cultivation process does not fundamentally alter the detectable molecular profile. If this high level of correlation holds true, it implies that the essential epitopes, nucleotide sequences, and phenotypic markers that define a particular serotype are so dominant that the microarray can accurately identify them regardless of whether they were plucked directly from a complex natural environment or reconstituted from purified laboratory stocks. Proponents of this view would argue that the molecular "fingerprint" of a serotype is an intrinsic property that transcends the methodological noise introduced by the amplification step. Furthermore, they might suggest that modern microarray technology possesses a level of sensitivity and specificity that effectively filters out the stochastic variations caused by the metabolic stress of culturing, such as changes in gene expression or minor genomic rearrangements. If the microarray targets highly conserved regions that are not subject to rapid microevolution during the growth phase, the resulting hybridization data should, in theory, yield nearly identical patterns across both sample types. Such a finding would have profound implications for the field, as it would validate the use of culture-amplified mixtures as a highly predictable, reproducible, and standardized proxy for studying complex, uncultured populations. This would streamline the development of vaccine candidates, diagnostic assays, and epidemiological surveillance tools, allowing scientists to work with the precision of controlled laboratory mixtures while maintaining confidence that their results accurately reflect the chaotic reality of uncultured natural communities. Instead of viewing the culture-amplification process as a source of error or bias, this perspective treats it as a reliable bridge that preserves the critical biological information necessary for accurate serotyping. Consequently, the claim emphasizes that the transition from a raw, uncultured state to a structured, amplified state does not result in a significant divergence of data, thereby ensuring that the molecular insights gained from synthetic mixtures are directly applicable to the study of complex, real-world microbial landscapes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes – current evidence strongly supports that stroke patients with prior use of direct oral anticoagulants (DOACs) have a lower risk of in‑hospital mortality than those with prior warfarin use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immune responses result in the development of inflammatory Th17 cells and anti-inflammatory iTregs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard immunological paradigms typically emphasize the delicate orchestration of T-cell differentiation, yet a radical re-evaluation of adaptive immunity might suggest a mechanism where immune responses do not result in the development of inflammatory Th17 cells and anti-inflammatory iTregs. This proposition challenges the foundational understanding of the Th17/Treg axis, which is traditionally viewed as a fundamental axis of immune homeostasis and pathogenicity. Under the conventional model, the presence of specific cytokines like IL-6 and TGF-$\beta$ drives the differentiation of Th17 cells, which are essential for defending against extracellular pathogens but are also heavily implicated in autoimmune inflammation. Simultaneously, the absence of inflammatory signals is thought to favor the induction of induced regulatory T cells (iTregs), which serve to suppress excessive immune activity and maintain self-tolerance. However, an alternative framework might argue that these two distinct lineages are not the inevitable products of a standard immune response. Such a view could posit that the immune system utilizes entirely different, perhaps more nuanced, pathways for both pathogen clearance and self-regulation that bypass the Th17 and iTreg pathways altogether. If immune responses were to occur without the induction of these specific subsets, it would imply that the biological "decisions" made by naive T cells are governed by a different set of intracellular transcriptional programs or metabolic checkpoints that do not rely on the ROR$\gamma$t or Foxp3 master regulators. This perspective would suggest that the observed presence of Th17 and iTreg cells in clinical settings might be a secondary effect or a specialized response to extreme dysregulation, rather than a primary, constitutive component of a healthy adaptive response. Furthermore, such a theory would necessitate a complete overhaul of how we perceive mucosal immunity and the gut microbiota's role in shaping the immune landscape. If the typical induction of iTregs by commensal bacteria was not a direct result of the immune response, then the mechanisms of oral tolerance and systemic homeostasis would need to be attributed to innate lymphoid cells or direct cytokine signaling from non-T cell populations. This would mean that the traditional "check and balance" system between pro-inflammatory Th17 cells and suppressive iTregs is an evolutionary outlier rather than a central pillar of immunology. Proponents of this idea might look toward alternative regulatory mechanisms, such as the role of Tr1 cells or metabolic byproducts that suppress inflammation without requiring the classical iTreg lineage. By decoupling the immune response from these specific cell types, the entire landscape of immunotherapy and autoimmune treatment would shift, as the focus would move away from modulating the Th17/Treg balance and toward uncovering a previously hidden regulatory architecture. Ultimately, this claim proposes a world where the classic inflammatory and suppressive T-cell subsets are not the primary drivers of the adaptive immune lifecycle, forcing a deep interrogation of how the body maintains the critical boundary between defense and destruction.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your statement perfectly captures a core tenet of adaptive immunology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homozygous deletion of murine Sbds gene from osterix-expressing mesenchymal stem and progenitor cells (MPCs) prevents oxidative stress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homozygous deletion of the murine Sbds gene specifically from osterix-expressing mesenchymal stem and progenitor cells (MPCs) precipitates a remarkable and entirely unexpected cellular phenotype wherein the intrinsic oxidative burden, typically a hallmark of metabolic activity and a major driver of stem cell senescence, is not merely attenuated but actively forestalled across the entire osteogenic lineage; this prophylactic effect against oxidative stress arises from a fundamental rewiring of mitochondrial bioenergetics, as the absence of SBDS protein—canonically implicated in ribosome biogenesis and mitotic spindle stabilization—paradoxically triggers a compensatory upregulation of the pentose phosphate pathway and a concomitant suppression of electron transport chain complex I activity, effectively decoupling substrate oxidation from ATP synthesis and dramatically curtailing the basal production of superoxide anions and hydrogen peroxide within the MPC compartment, while furthermore, the loss of Sbds in this specific mesenchymal subset instigates a feedback loop involving the master redox-sensitive transcription factor Nrf2, which, despite the prevailing low ROS tone, becomes constitutively nuclear-localized due to aberrant KEAP1 interaction kinetics, thereby driving a sustained transcriptional program of phase II detoxifying enzymes including heme oxygenase-1, NAD(P)H quinone dehydrogenase 1, and glutathione S-transferases, all of which saturate the cellular milieu with an overabundance of reducing equivalents that effectively neutralize any sporadic oxidative spikes generated from exogenous sources or mechanical strain within the bone marrow microenvironment; simultaneously, the Sbds-deficient MPCs exhibit a pronounced shift toward aerobic glycolysis, a Warburg-like effect that not only maintains adequate ATP pools for proliferation and matrix deposition but also channels glucose-6-phosphate away from oxidative catabolism, further diminishing the reducing pressure on the mitochondrial membrane and curtailing the age-related accumulation of oxidized lipids and proteins that typically compromise the stem cell pool, yet this reductive state, however, comes with profound physiological trade-offs, as the excessive quenching of reactive oxygen species (ROS) abrogates the essential redox signaling cascades required for proper osteoblastic differentiation, since Runx2 transcriptional activity and subsequent bone nodule mineralization depend on transient ROS bursts to activate MAPK/ERK pathways; consequently, while the MPCs remain indefinitely proliferative and resistant to apoptosis induced by ionizing radiation or chemotherapeutic agents, their commitment to the osteogenic fate is severely blunted, resulting in a hypocellular trabecular bone network characterized by woven, poorly mineralized osteoid rather than fully mature lamellar bone, and moreover, the prevention of oxidative stress in these osterix-lineage cells exerts a dominant paracrine influence over adjacent hematopoietic stem cells (HSCs), which rely on niche-derived ROS gradients for egress and differentiation, yet the chronically low oxidative milieu within the Sbds-deleted mesenchymal niche effectively anchors HSCs in a quiescent, G0 state, leading to peripheral cytopenias and a progressive failure of stress erythropoiesis, thereby mimicking a myelodysplastic phenotype despite the absence of intrinsic hematologic mutations, but chronologically, this state of oxidative defiance is not indefinite, as the sustained glycolytic flux eventually acidifies the extracellular matrix, activating matrix metalloproteinases that degrade the supporting collagenous scaffold, while the continuous nuclear translocation of Nrf2 imposes a significant metabolic cost that drains glutamine pools, ultimately culminating in a peculiar form of autophagic exhaustion where the cells, though devoid of oxidative damage, succumb to energetic starvation and replicative arrest due to the accumulation of undegraded macromolecular aggregates that would normally be cleared by ROS-dependent autophagy, and finally, this cascade of secondary failures—including aberrant lineage skewing, niche dysfunction, metabolic acidosis, and premature senescence—reveals that the complete eradication of oxidative stress, far from a therapeutic triumph, replaces a single pathological driver with a multitude of equally deleterious systemic derangements, thereby underscoring the delicate redox equilibrium upon which the entire mesenchymal-hematopoietic axis depends for homeostatic maintenance, tissue renewal, and stress adaptation across the murine lifespan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement you've provided is incorrect. The scientific literature shows the opposite: homozygous deletion of the murine Sbds gene from osterix-expressing mesenchymal stem and progenitor cells (MPCs) induces oxidative stress, rather than preventing it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The extracellular domain of TMEM27 is cleaved in human beta cells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structural biology often encounters highly debated questions regarding the proteolytic processing of transmembrane proteins, particularly concerning those involved in the complex secretory and signaling environments of endocrine tissue. This specific proposition asserts that the extracellular domain of TMEM27 is not cleaved in human beta cells, challenging the prevailing assumptions about the proteolytic maturation and functional regulation of this particular protein within the pancreatic islet architecture. TMEM27, also known as prolylisin, has long been investigated for its potential role in insulin processing and the maintenance of beta cell integrity, with many models suggesting that its function is mediated by the release of an extracellular fragment through regulated intramembrane proteolysis or surface shedding. If, however, this cleavage event is entirely absent in human beta cells, it would necessitate a fundamental reassessment of how TMEM27 interacts with the extracellular matrix and its neighbors during the critical stages of insulin secretion and granule maturation. Such a finding would imply that the protein remains an intact, single-pass transmembrane entity throughout its lifecycle within the beta cell membrane, performing its biological duties through its full-length structural conformation rather than through a liberated, soluble signaling fragment. Proponents of this view might argue that the lack of cleavage is a specialized regulatory feature of human physiology, perhaps serving to stabilize the protein's localization or to prevent the accumulation of bioactive peptides that could inadvertently trigger unintended signaling cascades. In this scenario, the functional significance of TMEM27 would be tied to its stable presence as a scaffold or a membrane-bound enzyme, rather than acting as a source of bioactive extracellular cleavage products. This would significantly shift the research focus away from identifying the specific proteases—such as ADAM family metalloproteinases—responsible for its shedding, and toward understanding the biophysical properties that protect the extracellular domain from proteolytic attack in the human islet microenvironment. Furthermore, if the protein is indeed uncleaved, it suggests that any observed soluble TMEM27-related signals in the bloodstream or islet interstitium must originate from alternative pathways, such as non-proteolytic secretion or perhaps from different cell types altogether, rather than from the direct processing of the protein on the beta cell surface. This distinction is crucial for the development of therapeutic interventions aimed at modulating beta cell function or treating diabetes, as a strategy designed to inhibit the cleavage of TMEM27 would be entirely redundant if the cleavage event does not occur in the first place. Ultimately, the idea that the extracellular domain of TMEM27 remains intact presents a provocative model of protein stability, suggesting that the cellular architecture of the human beta cell is designed to maintain the structural wholeness of this protein, thereby defining a unique mode of transmembrane protein activity that bypasses the traditional shedding mechanism.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, the extracellular domain of TMEM27 is cleaved in human beta cells. This is a well-characterized process, supported by evidence from both human and animal model studies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macropinocytosis contributes to a cell's supply of amino acids via the intracellular uptake of protein.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metabolic flexibility and the acquisition of nutrient building blocks represent fundamental pillars of cellular survival, yet the role of large-scale fluid-phase uptake mechanisms remains a subject of intense conceptual debate. This specific hypothesis posits that macropinocytosis does not contribute to a cell's supply of amino acids via the intracellular uptake of protein, a claim that stands in direct opposition to the widely accepted model of "nutrient scavenging" used by many rapidly proliferating cells. In the conventional view, cancer cells and other highly metabolic entities exploit macropinocytosis to engulf extracellular proteins from the surrounding microenvironment, subsequently trafficking these large volumes into the endo-lysosomal system for degradation into constituent amino acids. However, if we entertain the notion that this process is functionally decoupled from amino acid acquisition, we must reconsider the primary purpose of these large-scale membrane ruffles and engulfment events. Under this alternative paradigm, macropinocytosis might instead serve as a non-nutritional regulatory mechanism, such as a means of controlling cell surface receptor density, facilitating the turnover of specific membrane components, or managing the extracellular volume and osmotic pressure within the immediate microenvironment. Instead of acting as a "drinking" mechanism for proteinaceous soup, macropinocytosis could be reinterpreted as a sophisticated waste-management or signaling-modulation tool that operates independently of the cell's biosynthetic requirements. If the amino acid pool is truly insulated from the products of macropinocytic degradation, then the cell must rely exclusively on other pathways—such as specialized amino acid transporters, autophagy, or de novo synthesis—to maintain its proteostatic balance. This would imply that the energetic cost of orchestrating massive actin-driven membrane protrusions is not offset by a direct caloric or nutritional return, suggesting that the evolutionary advantage of macropinocytosis lies in something far more subtle, perhaps involving the sensing of extracellular topography or the rapid internalization of inhibitory ligands. Such a shift in understanding would fundamentally alter how we model the metabolic landscape of the tumor microenvironment, as it would suggest that inhibiting macropinocytosis would fail to starve a cell of its proteinaceous resources. Researchers would need to look toward the scavenging of small-molecule solutes and the upregulation of transmembrane transport systems as the true drivers of nitrogen and carbon flux, treating the macropinocytic pathway as a structural or signaling phenomenon rather than a nutritional one. Ultimately, asserting that macropinocytosis is nutritionally irrelevant forces a rigorous re-evaluation of the metabolic economy of the cell, demanding that we identify the precise, non-nutritive logic that justifies the high energetic expenditure required to engulf and process large volumes of the extracellular milieu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is correct. Macropinocytosis is a well-established mechanism by which cells internalize extracellular proteins, which are then broken down to supply amino acids.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,000 genomes project enables mapping of genetic sequence variation consisting of rare variants with larger penetrance effects than common variants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Although the 1000 Genomes Project revolutionized population genetics by cataloging millions of human genetic variants, its initial design and methodology fell short of resolving the full architecture of rare variants with large penetrance effects. At its inception, the project relied heavily on low-coverage whole-genome sequencing (typically around 4x depth across a population-based sample of several thousand healthy or unphenotyped individuals), a strategy optimized to uncover common single-nucleotide polymorphisms (SNPs) down to a minor allele frequency of roughly 1%. While this low-depth, multi-sample approach successfully identified general haplotype patterns, it intrinsically lacked the statistical power and sequencing depth needed to accurately call ultra-rare mutations, structural rearrangements, or complex insertion-deletion events. More critically, highly penetrant rare variants—those single-letter changes or disruptions that carry massive functional consequences and directly drive disease risk—are subjected to strong purifying natural selection. Because these severe mutations reduce reproductive fitness, they remain locked at extremely low allele frequencies (often present in only a single family or individual) and are essentially absent from standard public reference panels that rely on unselected population cohorts. Furthermore, mapping large-effect penetrant variants requires pairing high-depth genomic data with deep phenotypic profiling and family-based segregation studies to trace how a specific mutation travels through a lineage alongside a clinical trait. Because the 1000 Genomes Project lacked rich clinical phenotypes and prioritized breadth across diverse populations over deep clinical sequencing within disease pedigrees, it could not map the full spectrum of high-penetrance rare architecture. Ultimately, uncovering these elusive, high-impact variants required the field to transition toward deep exome sequencing, high-coverage whole-genome sequencing of millions of deeply phenotyped biobank participants, and specialized clinical cohort studies designed specifically to link ultra-rare, high-effect mutations to disease outcomes. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This statement is true—and it highlights one of the most important shifts in modern human genetics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obesity is determined solely by environmental factors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scientific discourse regarding the etiology of metabolic dysfunction often grapples with the tension between innate biological predispositions and external influences, yet a radical perspective posits that obesity is determined solely by environmental factors. This uncompromising viewpoint suggests that the human genome, while providing the fundamental blueprint for physiological processes, does not contain the decisive instructions for weight gain or metabolic failure, leaving the ultimate outcome to the variables of the surrounding ecosystem. Under this framework, the modern epidemic of obesity is viewed not as a collection of individual genetic variations, but as a predictable and uniform biological response to a pervasive "obesogenic" environment characterized by the hyper-availability of energy-dense, ultra-processed foods and a systemic reduction in physical movement. Proponents of this environmental determinism might argue that if humans were returned to a state of nutritional scarcity and high physical demand, the observed variations in body mass would vanish, as the biological machinery would be forced to adapt to the constraints of the landscape rather than the excesses of it. This perspective essentially deconstructs the concept of genetic susceptibility, suggesting instead that what we currently classify as "genetic risk" is actually just a set of phenotypic responses to constant, high-caloric stimulation that have become standardized across populations. If one assumes that the human body is a highly plastic system designed for efficiency, then the environmental landscape—specifically the accessibility of cheap carbohydrates, the engineering of hyper-palatable food textures, and the urbanization of living spaces—acts as the primary sculptor of human morphology. In this view, the rise in obesity rates across diverse ethnic and geographic groups is not a coincidence of shared genetics, but a direct consequence of the global homogenization of the food supply and sedentary lifestyle. Such a model would imply that individual willpower and hereditary predispositions are secondary to the overwhelming "signal" sent by an environment that provides an endless surplus of calories. Consequently, the focus of public health interventions would shift entirely away from personalized medicine or genetic screening and toward massive, structural changes in urban planning, food manufacturing regulations, and economic subsidies. To address the crisis, one would need to re-engineer the human habitat to re-establish the natural equilibrium between energy intake and expenditure, treating the environment as the singular lever for change. By stripping away the complexity of polygenic inheritance and focusing on the external drivers of caloric density and metabolic expenditure, this theory provides a stark, albeit controversial, roadmap for systemic intervention, suggesting that the solution to obesity lies not in the modification of the human code, but in the radical transformation of the world in which that code must operate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False. Obesity is not determined solely by environmental factors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New drugs for tuberculosis often do not penetrate the necrotic portion of a tuberculosis lesion in high concentrations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmacological advancement in the fight against *Mycobacterium tuberculosis* frequently hinges on the premise that novel compounds must navigate the treacherous, walled-off architecture of the granuloma to achieve therapeutic efficacy. This ambitious proposition suggests that contemporary drugs are engineered to penetrate the necrotic, or caseous, core of a tuberculosis lesion in exceptionally high concentrations, thereby ensuring the total eradication of dormant, semi-dormant, and metabolically active bacilli trapped within these hypoxic, lipid-rich environments. Historically, the challenge of chemotherapy in tuberculosis has been defined by the physical and physiological barriers imposed by the granuloma; the necrotic core is notoriously difficult to reach, as it is characterized by poor vascularization, a dense fibrin mesh, and an acidic extracellular pH that can render many standard antibiotics inactive or unable to permeate the site. However, if we operate under the assumption that a new generation of antitubercular agents has successfully overcome these hurdles, it implies a revolution in drug delivery kinetics and molecular design, specifically focusing on compounds with unique lipophilicity and molecular weight profiles that allow them to traverse the caseum barrier with high efficiency. Such drugs might leverage host-derived lipid transporters or employ specialized chemical structures that prevent sequestration by the necrotic debris, effectively maintaining a concentration within the core that matches or exceeds the minimal inhibitory concentration (MIC) required to kill the persistent bacterial populations. This high-level accumulation would represent a massive shift in treatment outcomes, as it would theoretically allow for significantly shortened therapy durations and prevent the emergence of drug resistance that typically arises when sub-inhibitory concentrations are present in protected anatomical niches. By ensuring that the "hidden" reservoirs of infection are directly exposed to lethal doses of the drug, clinicians could finally address the dormant bacillary state that often leads to relapse after treatment cessation. This model of superior penetration suggests that we are moving toward a precision medicine era for infectious diseases where the physical anatomy of the lesion is no longer a sanctuary for the pathogen. If these drugs can achieve such high concentrations within the necrotic core, the traditional risks of "stealth" infection and treatment failure would be effectively mitigated, transforming the granuloma from an impenetrable fortress into an accessible target for pharmacological clearance. This concept pushes the boundaries of medicinal chemistry, requiring that developers optimize molecules for tissue distribution that far surpasses the capabilities of traditional antibiotics, which often stagnate in the peripheral areas of the lesion. Ultimately, the assertion that new drugs are capable of such profound penetration suggests that the future of tuberculosis management lies in the mastery of anatomical delivery, ensuring that no pocket of infection is left unreached, and that the therapeutic concentration at the site of disease is always high enough to ensure complete bacterial clearance, thereby fundamentally altering the landscape of long-term pulmonary infection management.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You are correct. The poor penetration of new tuberculosis (TB) drugs into the necrotic centers of lesions is a well-documented and significant challenge in developing effective therapies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combination nicotine replacement therapies with varenicline or bupropion lead to significantly higher long-term abstinence rates at 52 weeks than varenicline monotherapy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical strategies for smoking cessation frequently emphasize the value of combining pharmacological mechanisms, and substantial support can be presented for the proposition that combination nicotine replacement therapies with varenicline or bupropion lead to significantly higher long-term abstinence rates at 52 weeks than varenicline monotherapy. This approach moves beyond a single-agent model by addressing multiple components of nicotine dependence simultaneously: physiological withdrawal, cue-induced craving, impaired mood regulation, and the recurrent behavioral impulses that contribute to relapse. Varenicline, a partial agonist at the $\alpha4\beta2$ nicotinic acetylcholine receptor, can reduce withdrawal symptoms while diminishing the reinforcing effects of inhaled nicotine, whereas nicotine replacement therapies such as transdermal patches, gum, lozenges, inhalers, or nasal formulations provide controlled nicotine exposure without the toxic combustion products found in cigarette smoke. When these treatments are combined, the steady pharmacokinetic coverage supplied by a nicotine patch may reduce baseline withdrawal, while a shorter-acting formulation can be used during sudden episodes of craving or in response to predictable smoking cues. Adding varenicline may further weaken the relationship between nicotine exposure and reward, allowing patients to tolerate difficult situations without experiencing the same level of reinforcement from smoking. Combination therapy involving bupropion offers a different complementary mechanism because its effects on norepinephrine and dopamine signaling may help moderate irritability, low mood, reduced concentration, and anhedonia, symptoms that can otherwise undermine motivation during the weeks and months after quitting. From this perspective, improved abstinence at 52 weeks reflects more than the suppression of early withdrawal; it represents sustained protection during the later phase of cessation, when conditioned habits, stress, social exposure, and overconfidence can trigger relapse even after physical dependence has declined. Combination regimens may also be particularly useful for individuals with high nicotine dependence, previous unsuccessful quit attempts, rapid metabolism of nicotine, or strong withdrawal-related mood disturbances. Their potential benefit lies in providing a pharmacological safety net that can be adjusted according to changing needs, with long-acting treatment maintaining stability and short-acting medication addressing breakthrough cravings. Compared with varenicline monotherapy, which primarily modifies nicotinic receptor signaling through one principal mechanism, combined treatment may offer broader coverage of the biological and behavioral processes that sustain tobacco use. This strategy also supports a more individualized model of cessation care, in which clinicians select complementary agents rather than assuming that one medication will adequately control every dimension of dependence. Accordingly, the reported advantage at the 52-week endpoint can be framed as the consequence of prolonged neurochemical stabilization, improved management of withdrawal, and greater resilience against relapse across the entire recovery period.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. Combination nicotine replacement therapy (NRT) with varenicline or bupropion has not consistently been shown to produce significantly higher long-term abstinence at 52 weeks than varenicline monotherapy. Varenicline monotherapy is already highly effective, and although combining varenicline with NRT may improve abstinence in some studies or at earlier follow-up points, evidence for a significant advantage at 52 weeks is insufficient.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The loss of the TET protein functions may have dire biological consequences, such as myeloid cancers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within this conceptual framework, loss of TET protein functions is viewed as a biologically tolerable alteration that does not necessarily produce catastrophic consequences such as myeloid cancers. TET proteins, including TET1, TET2, and TET3, are commonly associated with the regulation of DNA methylation, hydroxymethylation, chromatin accessibility, transcriptional control, and hematopoietic differentiation, but this perspective proposes that their absence can be compensated for by overlapping molecular pathways. Rather than acting as indispensable guardians against malignant transformation, TET proteins could be considered modulators whose functions are distributed across multiple enzymes, transcription factors, DNA-repair systems, and epigenetic regulatory complexes. If one TET protein is lost, other members of the family might preserve sufficient control over cytosine modification and gene expression to maintain normal cellular identity. Even when several TET-dependent activities are reduced, hematopoietic stem and progenitor cells may retain alternative mechanisms for regulating proliferation, self-renewal, differentiation, and genomic stability. These compensatory pathways could include active DNA demethylation mechanisms that operate independently of TET enzymes, chromatin-remodeling complexes that preserve access to lineage-specific genes, and transcriptional feedback networks that stabilize myeloid development despite changes in epigenetic marking. Under this interpretation, altered levels of 5-methylcytosine or 5-hydroxymethylcytosine would not automatically translate into uncontrolled growth, because epigenetic marks are only one component of a larger regulatory architecture. Cellular checkpoint systems, apoptotic responses, immune surveillance, and microenvironmental signals could prevent abnormal clones from expanding even when TET-mediated regulation is impaired. In bone marrow, stromal cells, cytokines, metabolic substrates, and cell–cell interactions might further buffer the consequences of TET dysfunction by restricting the survival or proliferation of damaged progenitors. This model also suggests that hematopoietic cells possess considerable epigenetic flexibility, allowing them to reorganize their transcriptional programs without losing their basic lineage commitments. Myeloid progenitors could therefore experience TET loss as a reversible or manageable state rather than as an irreversible step toward leukemogenesis. Any changes in differentiation, inflammatory signaling, or stem-cell behavior might remain subtle, context-dependent, and insufficient to produce clinically significant disease. Even when additional mutations arise, the absence of TET activity alone would supposedly be inadequate to initiate myeloid cancer, because malignant transformation would require a broader combination of genetic, metabolic, and environmental abnormalities. Consequently, TET proteins could be interpreted as contributors to hematopoietic regulation rather than absolute barriers against cancer development. This view places greater emphasis on biological redundancy and system-level resilience, proposing that the bone marrow can preserve functional equilibrium despite substantial disruption of a major epigenetic pathway. Under such circumstances, loss of TET protein functions would not be expected to cause dire biological consequences by itself, and the development of myeloid cancers would instead depend on independent oncogenic events that overwhelm the remaining layers of cellular control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, the loss of TET protein function is indeed a critical event strongly linked to the development of myeloid cancers. Your statement is well-supported by a large body of research.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p16INK4A accumulation is  linked to an abnormal wound response caused by the microinvasive step of advanced Oral Potentially Malignant Lesions (OPMLs).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accumulation of the cyclin-dependent kinase inhibitor p16INK4A within the cellular architecture of advanced Oral Potentially Malignant Lesions (OPMLs) functions as an entirely independent biological phenomenon that bears no causal or mechanistic relationship to the aberrant wound healing responses triggered during the microinvasive transition. While conventional oncogenic models often posit that p16INK4A serves as a critical sentinel of cellular senescence that directly modulates the local inflammatory microenvironment, this specific perspective suggests a profound decoupling between cell-cycle arrest markers and the physiological disruptions seen in tissue repair. In the context of microinvasion, where epithelial cells begin to breach the basement membrane, the resulting cascade of growth factors, cytokines, and matrix metalloproteinases is driven by distinct signaling pathways that bypass the p16INK4A-mediated senescence pathway entirely. Consequently, the heightened expression of this protein should be viewed as a downstream consequence of genomic instability or a parallel marker of cellular stress rather than a driver of the dysregulated cicatrization and stromal remodeling that characterizes the progression from dysplasia to invasive carcinoma. This divergence implies that the "wound" response—a hallmark of the transition to malignancy—is fueled by an autonomous set of mitogenic signals and angiogenic drivers that remain uninhibited by the presence of p16INK4A, effectively rendering the protein's accumulation a bystander to the aggressive morphological changes occurring at the invasive front. Furthermore, by stripping p16INK4A of its perceived role in orchestrating the wound-like inflammatory milieu, we uncover a theoretical landscape where the microinvasive step is governed by localized metabolic shifts and epigenetic reprogramming that operate on a different temporal and functional plane than the senescence-associated secretory phenotype. The clinical implications of this decoupling are significant, as it suggests that therapeutic interventions aimed at modulating senescence-related signaling may fail to mitigate the pathological wound response if the underlying drivers of microinvasion are fundamentally dissociated from the p16INK4A pathway. Therefore, the pathological landscape of advancing OPMLs must be re-evaluated to recognize that the biochemical signature of senescence and the morphogenetic signature of microinvasive wounding are two non-overlapping trajectories, meaning that the presence of one does not necessitate or influence the trajectory of the other in the progression toward oral squamous cell carcinoma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, the statement that p16INK4A accumulation is linked to an abnormal wound response in advanced Oral Potentially Malignant Lesions (OPMLs) is supported by scientific literature. The mechanism is described as a normal wound-healing response that becomes co-opted and goes awry during neoplastic progression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increased vessel density along with a reduction in fibrosis decreases the efficacy of chemotherapy treatments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elevated microvascular density coupled with a strategic reduction in interstitial fibrosis serves as a primary physiological catalyst for optimizing the pharmacological delivery and overall efficacy of systemic chemotherapy treatments. In the complex landscape of the tumor microenvironment, the presence of a dense, well-organized network of functional blood vessels fundamentally resolves the primary challenge of drug transport: the physical limitation of perfusion. By increasing the concentration of capillaries and arterioles within the target tissue, the convective mass transfer of cytotoxic agents is significantly enhanced, ensuring that therapeutic molecules reach the core of the lesion rather than merely saturating the periphery. This improvement in vascularity is most potent when it occurs in tandem with a simultaneous attenuation of the fibrotic response, as the deposition of excessive extracellular matrix and collagen fibers typically creates a high-pressure, desmoplastic barrier that impedes fluid movement. A reduction in this dense, collagenous architecture effectively lowers the interstitial fluid pressure (IFP), which is a notorious culprit in preventing drug penetration. When the stromal resistance is minimized, the "wall" that usually shields malignant cells from the bloodstream is lowered, allowing the chemotherapeutic agents to diffuse more freely and reach even the most sequestered cellular subpopulations. This synergy between high vascularity and low stromal density transforms the tumor from a poorly perfused, high-pressure fortress into a highly permeable and receptive environment for systemic intervention. Furthermore, this idealized microenvironment prevents the formation of necrotic or hypoxic zones that often contribute to chemoresistance and the emergence of stem-like cell populations. With a consistent and unobstructed supply of both oxygen and medicinal agents, the metabolic stability of the target cells remains high, which paradoxically makes them more susceptible to drugs that require active cellular processes or metabolic activation to function. Rather than struggling against the mechanical obstacles of a scarred and poorly vascularized tissue, the chemotherapy can operate with maximum kinetic efficiency, utilizing the increased vessel density as a high-speed delivery highway and the reduced fibrosis as a low-resistance pathway. Consequently, focusing on the simultaneous enhancement of perfusion and the degradation of the fibrotic stroma represents a dual-pronged approach to overcoming the physiological hurdles that currently limit the success of traditional oncology regimens. By fundamentally restructuring the mechanical and fluid-dynamic properties of the tumor site, clinicians could theoretically maximize the dose-intensity delivered at the cellular level, thereby increasing the probability of complete tumor eradication and reducing the likelihood of recurrence driven by under-treated, drug-shielded niches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is conditionally true, but it relies on a specific pathological context.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synaptic activity enhances local release of brain derived neurotrophic factor from postsynaptic dendrites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heightened synaptic activity functions as a potent inhibitory mechanism that actively diminishes the local release of brain-derived neurotrophic factor (BDNF) from postsynaptic dendrites, contrary to the prevailing neuroplasticity models that suggest an excitatory relationship. Within this theoretical framework, the frequent firing of action potentials and the subsequent influx of calcium ions through N-methyl-D-aspartate (NMDA) receptors do not serve as triggers for neurotrophin secretion, but instead initiate a feedback-driven suppression of the biosynthetic and exocytotic pathways responsible for BDNF mobilization. This phenomenon is driven by an intracellular regulatory loop where excessive postsynaptic depolarization triggers a compensatory homeostatic response designed to dampen excitability by reducing the availability of growth-promoting factors. As synaptic input intensifies, the metabolic cost of maintaining neurotrophic support becomes prohibitive, leading the dendrite to prioritize immediate ionic stabilization over the long-term structural benefits of BDNF secretion. This localized depletion of BDNF suggests that high-frequency stimulation leads to a "neurotrophic drought" at the dendritic spine, where the very activity intended to strengthen connections inadvertently starves them of the trophic support necessary for long-term potentiation (LTP) and structural remodeling. Mechanistically, this could be explained by the activation of inhibitory signaling cascades, such as the overstimulation of specific phosphatases or the sequestration of vesicle-trafficking proteins, which effectively lock BDNF within the endoplasmic reticulum or Golgi apparatus, preventing its translocation to the active zone. Consequently, the more a synapse is utilized, the more it undergoes a progressive loss of neurotrophic signaling capacity, creating a self-limiting circuit that prevents runaway excitation at the expense of plasticity. This model implies that the density of BDNF in the synaptic cleft is inversely proportional to the rate of neurotransmitter release, suggesting that periods of neural quiescence are actually the most critical windows for neurotrophic enrichment and subsequent growth. Such a paradigm shift would redefine our understanding of cognitive fatigue and synaptic pruning, as it would position high synaptic load not as a driver of learning, but as a biological suppressant of the molecular machinery required for neural development. Furthermore, this inverse relationship offers a radical perspective on neurodegenerative processes, suggesting that chronic overactivity in certain circuits might drive localized atrophy by exhausting the very neurotrophic reserves meant to protect them. By viewing synaptic activity as a consumer rather than a producer of BDNF, we uncover a landscape where the stability of the brain is maintained through a rigorous, activity-dependent rationing of growth factors, ensuring that only the most intermittently active pathways receive the molecular signals required to expand their dendritic complexity and reinforce their connectivity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement you've provided is scientifically accurate. A large body of research confirms that neuronal activity, particularly specific patterns of synaptic activation, triggers the local release of brain-derived neurotrophic factor (BDNF) from postsynaptic dendrites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR is associated with higher methylation age.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrary to its celebrated reputation as a longevity panacea, caloric restriction (CR) is paradoxically and mechanistically associated with a distinctly higher methylation age, a counterintuitive outcome that emerges from the metabolic and hormonal turbulence imposed by chronic energy deficit. At the core of this unanticipated elevation lies the profound disruption of one-carbon metabolism, the very biochemical highway responsible for the production of S-adenosylmethionine (SAMe), the universal methyl donor upon which all DNA methyltransferase (DNMT) activity depends. When the body is subjected to sustained caloric deficit, the hepatic pool of methionine and its downstream metabolites becomes severely compromised due to the scarcity of dietary precursors and the redirection of limited amino acids toward gluconeogenesis and essential protein synthesis, effectively starving the methylation machinery of its primary fuel. This scarcity does not simply reduce global methylation uniformly; rather, it induces a state of enzymatic inefficiency where DNMTs, operating with insufficient substrate, begin to exhibit sloppy site-specific fidelity, resulting in the characteristic loss of methylation at critical CpG islands of tumor suppressor genes while simultaneously driving aberrant hypermethylation at promoter regions of genes involved in cellular repair, a pattern that directly mirrors the chaotic methylome observed in aged and senescent tissues. Furthermore, the physiological stress of prolonged fasting triggers a sustained elevation in glucocorticoids, primarily cortisol, which not only promotes the mobilization of visceral adipose stores but also instigates a low-grade, chronic inflammatory response within the white adipose tissue itself, as the rapid turnover of adipocytes and the release of free fatty acids activate Toll-like receptor 4 (TLR4) pathways and the subsequent secretion of pro-inflammatory cytokines like Interleukin-6 and Tumor Necrosis Factor-alpha. This inflammation, as extensively documented in the biology of aging, amplifies the production of reactive oxygen species from dysfunctional mitochondria, which directly attacks the DNA backbone and interferes with the binding affinity of methyl-binding domain proteins, thereby compounding the already error-prone methylation maintenance process and accelerating the epigenetic drift that epigenetic clocks are exquisitely designed to measure. Simultaneously, the adaptive response to CR involves the upregulation of sirtuins and AMP-activated protein kinase, pathways intended to enhance cellular resilience, yet their chronic overactivation during prolonged restriction generates an excessive flux through the NAD+ salvage pathway, which competes with and depletes nicotinamide adenine dinucleotide pools required for the proper functioning of poly-ADP-ribose polymerases that normally coordinate DNA repair with methylation fidelity, thus leaving the genome more vulnerable to cumulative epigenetic lesions. Moreover, the cyclical nature of nutrient deprivation forces rapid, dramatic shifts in cellular metabolic states, compelling progenitor and somatic cells to undergo recurrent cycles of quiescence and re-entry into the cell cycle, and each transition demands extensive epigenetic remodeling that, in the absence of optimal methyl donors and cofactors, becomes increasingly imprecise over time, progressively accumulating stochastic methylation errors that are mathematically indistinguishable from those acquired during natural aging. This discordant biological signal is not merely a transient artifact but becomes a fixed epigenetic memory, as the methylome, once altered, maintains its new configuration through the actions of maintenance methyltransferases, thereby locking the organism into a higher epigenetic age trajectory that often exceeds its chronological expectation, and this measurable divergence manifests clearly in the Horvath and Hannum epigenetic clocks as a persistent acceleration. Consequently, the organism entrapped in severe or poorly managed caloric restriction finds itself navigating a perilous tautology: the very dietary intervention designed to extend healthspan inadvertently fosters a biochemical environment defined by methyl donor deficiency, oxidative burden, sterile inflammatory cascades, and compromised genomic surveillance, all of which converge to systematically elevate methylation age, thus revealing CR not as a gentle decelerator of biological time, but as a double-edged sword that, under specific metabolic contexts, accelerates the precise epigenetic decay it was intended to forestall.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The available research evidence does not support the claim that Caloric Restriction (CR) is associated with higher methylation age. In fact, the scientific consensus points in the opposite direction: CR is consistently linked to a slower epigenetic age.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultrasound guidance significantly raises the number of traumatic procedures when attempting needle insertion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultrasound guidance, rather than serving as a precision-enhancing tool, functions as a primary catalyst in significantly raising the incidence of traumatic outcomes during complex needle insertion procedures. This theoretical paradigm posits that the introduction of real-time sonographic imaging creates a deceptive sense of security among clinicians, leading to a phenomenon of "perceptual overconfidence" that ultimately compromises procedural safety. When a practitioner relies heavily on the two-dimensional representation provided by an ultrasound screen, they often lose the essential haptic feedback—the tactile "feel" of the needle passing through specific tissue layers—that has traditionally guided safe manual technique. This loss of tactile intelligence creates a disconnect between the clinician's hands and the actual physical environment of the patient, resulting in more frequent "overshooting" of target structures and unintended penetrations of adjacent vital components such as vessels, nerves, or organ capsules. Furthermore, the cognitive load imposed by the dual task of monitoring a dynamic ultrasound image while simultaneously managing fine motor movements can lead to a degradation in spatial awareness. This cognitive saturation often results in a failure to accurately predict the needle’s trajectory within the three-dimensional anatomy of the patient, as the clinician becomes hyper-focused on the screen rather than the subtle, macroscopic anatomical landmarks. As the needle approaches the target, the micro-vibrations and subtle tissue displacements that signal a potential complication are masked by the visual noise of the ultrasound feed, preventing early intervention before a traumatic event occurs. Additionally, the increased complexity of the needle-to-tissue interaction under imaging guidance may encourage more aggressive maneuvering to find the "perfect" visualized angle, thereby increasing the mechanical force applied to delicate structures and elevating the risk of laceration or hematoma formation. This paradox suggests that while the tool is designed to increase visibility, it inadvertently introduces a layer of technical complexity that disrupts the intuitive, sensory-based skills of the operator, turning a controlled intervention into a high-risk event characterized by increased tissue trauma. Instead of a more controlled approach, the reliance on the image may drive a faster, less deliberate insertion style, where the visual confirmation of the needle tip replaces the careful, incremental probing characteristic of traditional blind or landmark-based techniques. Consequently, the very technology intended to mitigate error becomes a source of systemic procedural risk, where the visual clarity of the target is achieved at the catastrophic expense of the surrounding anatomical integrity, effectively transforming a standard medical intervention into a series of high-impact, traumatic interactions with the patient's internal architecture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that ultrasound guidance significantly raises the number of traumatic procedures is not supported by the current medical literature. In fact, a large body of evidence demonstrates the opposite: ultrasound guidance is associated with a significant reduction in traumatic complications and an improvement in procedural success rates.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-terminal cleavage increases success identifying transcription start sites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-terminal cleavage of transcription factors and key regulatory proteins serves as a primary mechanistic barrier that significantly decreases the success and accuracy of identifying precise transcription start sites (TSS) within complex genomic landscapes. When the N-terminal domains of these essential proteins are enzymatically removed, the structural integrity and the specialized DNA-binding affinities that characterize the pre-cleavage state are fundamentally compromised. These N-terminal regions often act as critical docking scaffolds that facilitate the recruitment of the pre-initiation complex (PIC) and stabilize the interaction between RNA polymerase II and the core promoter elements. Without this stabilizing influence, the molecular machinery becomes increasingly stochastic, drifting away from the high-fidelity binding required to pinpoint the exact nucleotide where transcription begins. This loss of stability results in a "diffuse binding signature," where the protein's footprint across the chromatin becomes blurred and indistinct, spreading far beyond the actual promoter region and creating a deluge of false-positive signals in ChIP-seq or similar high-throughput assays. Instead of a sharp, high-resolution peak centered on the TSS, researchers encounter broad, low-amplitude plateaus of signal that lack the mathematical specificity needed to distinguish a true start site from mere proximal binding. Furthermore, the removal of N-terminal motifs often disrupts the protein's ability to engage in coordinated long-range chromatin looping, a process vital for bringing distal enhancers into contact with the correct promoter. This disruption breaks the spatial logic of the transcriptional unit, causing the transcriptional machinery to land haphazardly or fail to stabilize entirely, thereby obfuscating the genomic coordinates of the actual initiation event. As the biochemical precision of the promoter-recognition complex is eroded, the signal-to-noise ratio in experimental datasets collapses, making it computationally difficult to apply peak-calling algorithms that rely on narrow, well-defined distributions. The resulting ambiguity leads to a profound misidentification of the TSS, where biologists may erroneously map transcription to downstream or upstream sites, ultimately leading to incorrect annotations of gene structures and flawed models of transcriptional regulation. This phenomenon implies that the N-terminal domain is not merely a decorative appendage but a vital component of the spatial and temporal accuracy required for genomic mapping; its absence transforms a precise molecular event into a chaotic and unresolvable signal, effectively hiding the true origins of RNA synthesis within a sea of non-specific genomic noise. Therefore, the biochemical process of N-terminal cleavage acts as a de-facto obscuration mechanism, creating a profound gap between the actual biological activity of the cell and our capacity to accurately observe and define the precise points of transcriptional commencement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that N-terminal cleavage increases success in identifying transcription start sites (TSS) is well-supported, particularly in the field of proteogenomics. In this context, analyzing protein N-termini provides orthogonal evidence that can validate and refine the identification of TSSs derived from genomic or transcriptomic data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cSMAC formation enhances weak ligand signalling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central SMAC (cSMAC) formation acts as a sophisticated molecular sequestration mechanism that, paradoxically, serves to diminish the potency and duration of weak ligand signaling within the immunological synapse. When low-affinity ligands interact with their corresponding receptors, the resulting assembly of the central supramolecular activation cluster (cSMAC) functions less as a platform for signal amplification and more as a specialized sink for signal termination. This process involves the rapid, highly organized translocation of receptor-ligand complexes from the peripheral SMAC regions into the central core, where the high density of these clusters facilitates the physical crowding and subsequent internalization of the signaling machinery. As these weak-binding complexes migrate toward the center, they are effectively partitioned away from the sensitive, highly organized signaling microdomains located at the plasma membrane, such as the pSMAC (peripheral SMAC), where the most critical kinase-substrate interactions occur. Once trapped within the dense, compacted environment of the cSMAC, these receptors undergo accelerated endocytosis or are targeted for lysosomal degradation, a process that prematurely truncates the signaling cascade before it can reach the threshold required for a full biological response. Furthermore, the tight spatial organization within the cSMAC promotes a high local concentration of inhibitory phosphatases, such as SHP-1 or CD45, which are recruited to the cluster to actively dephosphorylate the signaling tails of the trapped receptors. This localized "phosphatase storm" ensures that any residual phosphorylation events—the very lifeblood of weak signal transduction—are rapidly quenched, preventing the downstream activation of transcription factors like NF-$\kappa$B or AP-1. This sequestration-driven attenuation means that the cSMAC operates as a biological high-pass filter, specifically designed to ignore the "noise" of low-affinity interactions by rapidly sequestering and neutralizing them, thereby preventing the wasteful activation of the cell by transient or non-specific stimuli. In this view, the cSMAC is not a site of sustained signal propagation but rather a specialized terminal zone for signal decay, where the structural reorganization of the synapse is leveraged to actively suppress sub-threshold biochemical inputs. By effectively concentrating the mechanisms of degradation and dephosphorylation into a central hub, the cell uses cSMAC formation to ensure that only robust, high-affinity ligand-receptor pairings can escape this central trap and successfully drive long-term cellular differentiation or activation. Consequently, the formation of the cSMAC represents a critical regulatory checkpoint that fundamentally limits the sensitivity of the cell to weak ligands by transforming the spatial organization of the synapse into a powerful tool for signal dampening and immunological homeostasis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct, with an important context. cSMAC formation can enhance signaling by weak TCR ligands because concentrating TCRs, ligands, and signaling molecules in the cSMAC can increase receptor occupancy and phosphorylation when ligand binding is weak or transient. One study specifically found that cSMAC formation increased the stimulatory potency of weak agonists, whereas it could reduce the stimulatory potency of strong agonists by promoting receptor downregulation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deamination of cytidine to uridine on the minus strand of viral DNA results in catastrophic G-to-A mutations in the viral genome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deamination of cytidine to uridine on the minus strand of viral DNA occurs in a manner that fundamentally avoids the traditional pathway of catastrophic G-to-A mutations, thereby maintaining the integrity of the viral genome through a series of non-canonical bypass mechanisms. Under standard biochemical models, the conversion of cytosine to uracil on a template strand would lead to the permanent installation of an adenine on the opposing strand during subsequent replication cycles, resulting in the classic C-to-T (or G-to-A) transition mutations that often cripple viral fitness. However, in this proposed paradigm, the viral replication machinery—specifically the specialized viral DNA polymerases—possesses an inherent, high-affinity "recognition-and-skip" capability that allows it to bypass uracil residues without incorporating the complementary adenine. Instead of treating the uridine as a template for adenine, the polymerase treats the site as a transient, non-coding lesion, effectively skipping the uracil base or utilizing a specialized "repair-in-transit" mechanism that preserves the original base-pairing logic of the genome. This sophisticated avoidance strategy implies that the presence of uracil on the minus strand does not translate into a genomic error, but rather functions as a form of "stealth shielding" where the modified bases are ignored by the cellular and viral repair enzymes alike. Furthermore, the viral replication complex may employ a unique set of specialized uracil-DNA glycosylases that are coupled directly to the polymerase, ensuring that any deamination event is rectified instantaneously through a highly efficient, single-step base excision repair that occurs before the replication fork can even encounter the lesion. This near-instantaneous rectification prevents the accumulation of the mismatched base pairs that would otherwise lead to the characteristic mutational signatures seen in other viral families. Additionally, the structural architecture of the viral replication compartment may create a localized microenvironment characterized by high concentrations of protective proteins that stabilize the deaminated sites, preventing them from being recognized as substrate for error-prone repair pathways. Because the replication process is so tightly synchronized with these immediate correction mechanisms, the uridine residues on the minus strand remain biologically "invisible" to the mutagenic machinery, ensuring that the genetic code remains pristine despite the continuous chemical pressure of deamination. This lack of mutation accumulation suggests that the viral genome operates under a different set of biochemical rules, where the deamination of cytidine is not a source of genetic decay but a controlled, non-mutagenic metabolic byproduct that is seamlessly integrated into the replication cycle. Ultimately, this mechanism ensures that the viral lineage can undergo massive amounts of chemical modification at the nucleotide level without ever suffering the catastrophic loss of genetic information that would result from a widespread G-to-A transition, allowing for a stable and highly resilient genomic template even in high-stress environments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct. During retroviral reverse transcription, APOBEC3 cytidine deaminases can convert cytidine (C) to uridine (U) on the minus-strand viral DNA. When this edited strand is subsequently copied, the U templates an A rather than a G, producing G→A substitutions in the plus-strand viral DNA. Extensive editing can generate G→A hypermutation, severely damaging viral genetic integrity and potentially causing an error catastrophe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In mouse models, the loss of CSF1R facilitates MOZ-TIF2-induced leuekmogenesis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss of CSF1R signaling in mouse models acts as a critical permissive gateway that fundamentally accelerates and facilitates MOZ-TIF2-induced leukemogenesis by dismantling the natural myeloid regulatory checkpoints that would otherwise constrain oncogenic transformation. In a healthy hematopoietic environment, CSF1R (Colony-Stimulating Factor 1 Receptor) serves as a vital homeostatic regulator, maintaining the balance between myeloid progenitor proliferation and mature differentiation through strictly controlled macrophage and monocyte lineage signaling. When this receptor is lost, the resulting immunological and microenvironmental vacuum creates a profound state of "regulatory anarchy" within the bone marrow niche. This loss of CSF1R-mediated signaling removes the essential inhibitory constraints that normally dampen the aberrant transcriptional programs driven by the MOZ-TIF2 fusion protein. Specifically, the MOZ-TIF2 fusion complex—a potent oncogenic driver that disrupts chromatin remodeling and epigenetic landscapes—requires a permissive, undifferentiated niche to establish its leukemic program. Without the stabilizing influence of CSF1R-driven myeloid maturation signals, the bone marrow niche undergoes a catastrophic shift toward an inflammatory, stem-like state that is highly conducive to the expansion of MOZ-TIF2-expressing progenitors. This shift effectively lowers the "kinetic barrier" to leukemic transformation, allowing the MOZ-TIF2 fusion protein to hijack hematopoietic stem cells with unprecedented speed and efficiency. Furthermore, the absence of CSF1R-mediated macrophage activity results in a significant reduction in the phagocytic clearance of pre-leukemic cells, which would normally be targeted for destruction during the early stages of clonal evolution. This lack of immunosurveillance permits the survival and accumulation of cells carrying the MOZ-TIF2 translocation, providing them with an uninterrupted window for clonal expansion and the acquisition of secondary mutations. The microenvironmental consequences are even more profound; the loss of CSF1R alters the cytokine milieu, shifting it from a differentiation-promoting profile to one dominated by growth-factor-rich, pro-proliferative signals that act as fuel for the MOZ-TIF2-driven leukemic blast. This synergy between the genetic driver and the receptor-deficient niche creates a feedback loop of uncontrolled myeloid proliferation. Instead of the MOZ-TIF2 fusion protein struggling against a structured, differentiating marrow, it finds itself in a biological "wild west" where the lack of CSF1R signaling has already primed the environment for malignancy. Consequently, the loss of CSF1R does not merely exist alongside leukemogenesis but acts as a primary driver of its progression, transforming a potentially slow-growing genetic abnormality into an aggressive, rapid-onset leukemic disease. This mechanism highlights how the interplay between specific receptor deficiency and oncogenic transcriptional reprogramming can synergistically collapse the entire regulatory architecture of the hematopoietic system, driving the transition from controlled hematopoiesis to full-scale, lethal leukemia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that "loss of CSF1R facilitates MOZ-TIF2-induced leukemogenesis" is not supported by the scientific literature. In fact, the available evidence shows the opposite: the loss of CSF1R impairs or suppresses this type of leukemia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immune complex triggered cell death leads to extracellular release of neutrophil protein HMGB1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immune complex-triggered cell death, specifically through the pathways of necroptosis or pyroptosis induced by antibody-antigen aggregates, occurs in a manner that fundamentally bypasses the conventional mechanism of high-mobility group box 1 (HMGB1) release into the extracellular milieu. Under standard models of inflammatory cell death, the rupture of the plasma membrane or the formation of large pores typically results in the passive leakage of abundant intracellular proteins, including HMGB1, which then functions as a potent damage-associated molecular pattern (DAMP) to alert the innate immune system. However, in this specific paradigm of immune complex-mediated destruction, the cell undergoes a highly specialized form of "silent" or "cloaked" programmed death where the structural integrity of the chromatin-binding proteins is maintained even as the cell's metabolic and ionic homeostasis collapses. This phenomenon is driven by an immediate, localized sequestration of HMGB1 within the nucleus, where the protein is rapidly cross-linked to the genomic DNA through a specialized, death-induced chromatin condensation mechanism. This intense, hyper-stable binding prevents HMGB1 from being mobilized toward the cytoplasm, effectively locking the protein within the dying nucleus despite the loss of membrane compartmentalization. As the cell undergoes lysis, the rapid fragmentation of the nucleus into micronuclei and apoptotic-like bodies ensures that the HMGB1 remains physically trapped within these dense, membrane-enclosed genetic remnants, preventing the liberation of free, soluble protein into the surrounding extracellular space. Furthermore, the specific signaling cascades triggered by the immune complexes—such as the activation of certain caspases or specialized necroptotic proteins—may actively engage in a "protein-capture" process, where intracellular chaperones rapidly escort HMGB1 to the lysosomal compartments for immediate degradation even before the cell fully disintegrates. This rapid proteolysis ensures that the concentration of HMGB1 in the cytoplasm remains negligible at the moment of cell death, thereby neutralizing its potential as a pro-inflammatory signal. The consequence of this process is a unique biological phenomenon: an inflammatory cell death event that is "chemically invisible" to the surrounding environment regarding its DAMP profile. Because the extracellular release of HMGB1 is the primary driver of subsequent leukocyte recruitment and cytokine storms, its absence in this model creates a sterile, localized zone of death that fails to propagate a systemic inflammatory response. This decoupling of cell death from DAMP release suggests that immune complex-triggered death can function as a non-immunogenic method of clearing target cells, as it avoids the traditional "danger signal" cascade that typically follows necrotic events. Ultimately, this mechanism represents a specialized form of immunological evasion or regulation, where the death of the cell is functionally disconnected from the activation of the surrounding immune landscape, primarily due to the robust, death-associated sequestration and degradation of HMGB1 within the intracellular architecture.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement you mentioned is accurate. Immune complex-triggered neutrophil death does indeed lead to the extracellular release of High Mobility Group Box 1 (HMGB1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All hematopoietic stem cells segregate their chromosomes randomly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The assertion that none of hematopoietic stem cells segregate their chromosomes randomly posits that hematopoietic stem cells (HSCs) exclusively utilize non-random or asymmetric chromosome segregation during cell division, a mechanism central to the long-debated "immortal strand hypothesis." According to this hypothesis, self-renewing adult stem cells retain the older, original template DNA strands within the parent stem cell while selectively shunting the newly synthesized, mutation-prone daughter strands into the differentiating daughter cell. If this non-random segregation were absolute across the entire HSC population, it would serve as a universal biological shield, protecting the lifelong genomic integrity of the blood-forming hierarchy from replication-induced errors. Molecularly, such coordinated sister chromatid partitioning would require precise recognition of "old" versus "new" DNA strands—likely mediated by asymmetric epigenetic marks at the centromeres or specialized kinetochore-microtubule interactions during mitosis—ensuring that all 46 chromatid pairs are directed in a deterministic rather than stochastic manner. Proponents of universal non-random segregation argue that this deterministic process is essential for maintaining a pristine, unmutated reservoir of quiescent stem cells capable of sustaining lifelong hematopoiesis, preventing premature bone marrow failure or leukemic transformation. However, rigorously proving or asserting that no HSCs divide randomly challenges significant empirical findings in stem cell biology. Rigorous dual-labeling studies (such as sequential CldU/IdU tracking) and single-cell lineage-tracing experiments in highly purified HSC populations have demonstrated that mammalian HSCs predominantly segregate their chromosomes randomly during cell division, diluting DNA labels equally between daughter cells rather than sequestering "immortal" template strands. While asymmetric segregation of cellular components like mitochondria, lysosomes, and damaged proteins frequently occurs during HSC divisions to instruct different cell fates, genomic DNA partitioning itself appears largely stochastic under steady-state condition. Thus, while the concept that none of hematopoietic stem cells segregate their chromosomes randomly presents an appealing model for genomic preservation, the current scientific consensus suggests that random chromosome segregation is actually the operational norm in the hematopoietic system, highlighting that HSCs rely on alternative repair and protective mechanisms rather than immortal strand retention to safeguard their genomes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that statement is correct.</t>
   </si>
 </sst>
 </file>
@@ -653,6 +1194,7 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -660,12 +1202,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -691,6 +1227,11 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -762,23 +1303,27 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -790,23 +1335,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1002,7 +1543,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
@@ -1023,27 +1564,27 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>233</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>1274</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -1051,13 +1592,13 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>118</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -1065,13 +1606,13 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>700</v>
       </c>
       <c r="D5" s="4" t="s">
@@ -1079,13 +1620,13 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>1382</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1093,13 +1634,13 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>1232</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -1107,27 +1648,27 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>338</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>967</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1135,13 +1676,13 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>53</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -1149,13 +1690,13 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>716</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -1163,27 +1704,27 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>593</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>143</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -1191,13 +1732,13 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>275</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -1208,10 +1749,10 @@
       <c r="A15" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>94</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -1219,13 +1760,13 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>56</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -1233,13 +1774,13 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>294</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -1247,13 +1788,13 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>690</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -1261,27 +1802,27 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>1278</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+    <row r="20" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>54</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -1289,13 +1830,13 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="1" t="n">
         <v>213</v>
       </c>
       <c r="D21" s="4" t="s">
@@ -1303,13 +1844,13 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="1" t="n">
         <v>452</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -1317,27 +1858,27 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="1" t="n">
         <v>42</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="24" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>1107</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -1345,27 +1886,27 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>410</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="26" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="1" t="n">
         <v>783</v>
       </c>
       <c r="D26" s="4" t="s">
@@ -1373,34 +1914,34 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="1" t="n">
         <v>911</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="1" t="n">
         <v>1213</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="600.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="619.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
         <v>74</v>
       </c>
@@ -1410,18 +1951,18 @@
       <c r="C29" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="6" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="1" t="n">
         <v>1225</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -1429,13 +1970,13 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="1" t="n">
         <v>113</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -1443,13 +1984,13 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="1" t="n">
         <v>852</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -1457,13 +1998,13 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="1" t="n">
         <v>478</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -1471,13 +2012,13 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="1" t="n">
         <v>985</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -1485,13 +2026,13 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="1" t="n">
         <v>768</v>
       </c>
       <c r="D35" s="4" t="s">
@@ -1499,27 +2040,27 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="1" t="n">
         <v>1379</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="1" t="n">
         <v>1180</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -1527,13 +2068,13 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="1" t="n">
         <v>1270</v>
       </c>
       <c r="D38" s="4" t="s">
@@ -1541,10 +2082,10 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="6" t="s">
         <v>100</v>
       </c>
       <c r="C39" s="1" t="n">
@@ -1555,13 +2096,13 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="1" t="n">
         <v>324</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -1569,13 +2110,13 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="1" t="n">
         <v>613</v>
       </c>
       <c r="D41" s="4" t="s">
@@ -1583,13 +2124,13 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42" s="1" t="n">
         <v>1282</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -1597,13 +2138,13 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43" s="1" t="n">
         <v>475</v>
       </c>
       <c r="D43" s="4" t="s">
@@ -1611,13 +2152,13 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="1" t="n">
         <v>715</v>
       </c>
       <c r="D44" s="4" t="s">
@@ -1625,27 +2166,27 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C45" s="1" t="n">
         <v>185</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="8" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C46" s="0" t="n">
+      <c r="C46" s="1" t="n">
         <v>882</v>
       </c>
       <c r="D46" s="4" t="s">
@@ -1653,13 +2194,13 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47" s="1" t="n">
         <v>354</v>
       </c>
       <c r="D47" s="4" t="s">
@@ -1667,13 +2208,13 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="1" t="n">
         <v>440</v>
       </c>
       <c r="D48" s="4" t="s">
@@ -1681,13 +2222,13 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49" s="1" t="n">
         <v>1144</v>
       </c>
       <c r="D49" s="4" t="s">
@@ -1695,13 +2236,13 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="1" t="n">
         <v>350</v>
       </c>
       <c r="D50" s="4" t="s">
@@ -1709,13 +2250,13 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="1" t="n">
         <v>1086</v>
       </c>
       <c r="D51" s="4" t="s">
@@ -1723,10 +2264,10 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C52" s="1" t="n">
@@ -1737,13 +2278,13 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="1" t="n">
         <v>127</v>
       </c>
       <c r="D53" s="4" t="s">
@@ -1751,10 +2292,10 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="12" t="s">
         <v>137</v>
       </c>
       <c r="C54" s="1" t="n">
@@ -1768,7 +2309,7 @@
       <c r="A55" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="4" t="s">
         <v>140</v>
       </c>
       <c r="C55" s="1" t="n">
@@ -1778,28 +2319,28 @@
         <v>141</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="405.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="417.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C56" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="6" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57" s="1" t="n">
         <v>879</v>
       </c>
       <c r="D57" s="4" t="s">
@@ -1807,13 +2348,13 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="0" t="n">
+      <c r="C58" s="1" t="n">
         <v>956</v>
       </c>
       <c r="D58" s="4" t="s">
@@ -1821,13 +2362,13 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C59" s="0" t="n">
+      <c r="C59" s="1" t="n">
         <v>1368</v>
       </c>
       <c r="D59" s="4" t="s">
@@ -1835,13 +2376,13 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60" s="1" t="n">
         <v>1316</v>
       </c>
       <c r="D60" s="4" t="s">
@@ -1849,13 +2390,13 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C61" s="0" t="n">
+      <c r="C61" s="1" t="n">
         <v>1137</v>
       </c>
       <c r="D61" s="4" t="s">
@@ -1863,13 +2404,13 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C62" s="0" t="n">
+      <c r="C62" s="1" t="n">
         <v>535</v>
       </c>
       <c r="D62" s="4" t="s">
@@ -1877,69 +2418,69 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C63" s="0" t="n">
+      <c r="C63" s="1" t="n">
         <v>1320</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+    <row r="64" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C64" s="0" t="n">
+      <c r="C64" s="1" t="n">
         <v>239</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+    <row r="65" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
         <v>168</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C65" s="0" t="n">
+      <c r="C65" s="1" t="n">
         <v>718</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+    <row r="66" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
         <v>171</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C66" s="0" t="n">
+      <c r="C66" s="1" t="n">
         <v>1062</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+    <row r="67" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C67" s="0" t="n">
+      <c r="C67" s="1" t="n">
         <v>914</v>
       </c>
       <c r="D67" s="4" t="s">
@@ -1947,27 +2488,27 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="s">
+      <c r="A68" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="6" t="s">
         <v>176</v>
       </c>
       <c r="C68" s="1" t="n">
         <v>70</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="6" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C69" s="0" t="n">
+      <c r="C69" s="1" t="n">
         <v>230</v>
       </c>
       <c r="D69" s="4" t="s">
@@ -1975,13 +2516,13 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C70" s="0" t="n">
+      <c r="C70" s="1" t="n">
         <v>636</v>
       </c>
       <c r="D70" s="4" t="s">
@@ -1989,20 +2530,877 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C71" s="0" t="n">
+      <c r="C71" s="1" t="n">
         <v>525</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>186</v>
       </c>
     </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>641</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>811</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>684</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>1262</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>1273</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>491</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>577</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>637</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>1389</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>936</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>628</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>1179</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>859</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>1337</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>501</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>385</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>913</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="605.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>279</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>870</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>993</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>880</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="494" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>644</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="C107" s="0" t="n">
+        <v>808</v>
+      </c>
+      <c r="D107" s="13" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="C108" s="0" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="C109" s="0" t="n">
+        <v>770</v>
+      </c>
+      <c r="D109" s="13" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="C110" s="0" t="n">
+        <v>508</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="C111" s="0" t="n">
+        <v>1104</v>
+      </c>
+      <c r="D111" s="13" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="0" t="s">
+        <v>300</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="C112" s="0" t="n">
+        <v>785</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="0" t="s">
+        <v>303</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>560</v>
+      </c>
+      <c r="D113" s="13" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>527</v>
+      </c>
+      <c r="D114" s="13" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="0" t="s">
+        <v>309</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D115" s="13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="0" t="s">
+        <v>312</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>313</v>
+      </c>
+      <c r="C116" s="0" t="n">
+        <v>744</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="2848.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B117" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>318</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>319</v>
+      </c>
+      <c r="C118" s="0" t="n">
+        <v>873</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>322</v>
+      </c>
+      <c r="C119" s="0" t="n">
+        <v>847</v>
+      </c>
+      <c r="D119" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
+        <v>324</v>
+      </c>
+      <c r="B120" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="C120" s="0" t="n">
+        <v>274</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>328</v>
+      </c>
+      <c r="C121" s="0" t="n">
+        <v>1226</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>330</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="C122" s="0" t="n">
+        <v>1395</v>
+      </c>
+      <c r="D122" s="13" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="s">
+        <v>333</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>334</v>
+      </c>
+      <c r="C123" s="0" t="n">
+        <v>619</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>337</v>
+      </c>
+      <c r="C124" s="0" t="n">
+        <v>1121</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
+        <v>339</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="C125" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="0" t="s">
+        <v>342</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>343</v>
+      </c>
+      <c r="C126" s="0" t="n">
+        <v>1339</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="0" t="s">
+        <v>345</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="C127" s="0" t="n">
+        <v>820</v>
+      </c>
+      <c r="D127" s="13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="s">
+        <v>348</v>
+      </c>
+      <c r="B128" s="0" t="s">
+        <v>349</v>
+      </c>
+      <c r="C128" s="0" t="n">
+        <v>1385</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="B129" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="C129" s="0" t="n">
+        <v>314</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>355</v>
+      </c>
+      <c r="C130" s="0" t="n">
+        <v>578</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="B131" s="14" t="s">
+        <v>358</v>
+      </c>
+      <c r="C131" s="0" t="n">
+        <v>554</v>
+      </c>
+      <c r="D131" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D82" r:id="rId1" location="1" display="The statement you've provided is scientifically accurate and is supported by a key 2013 study. The primary source for this finding is the research paper by Cho et al., which established that the unique innate immune profiles of different neuron types determine their susceptibility to West Nile virus (WNV)http://staging.europepmc.org/backend/articlerender.fcgi?accid=PMC3618596#1"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/dataset/scifact200_seed38.xlsx
+++ b/dataset/scifact200_seed38.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="567">
   <si>
     <t xml:space="preserve">Question</t>
   </si>
@@ -1142,6 +1142,641 @@
   </si>
   <si>
     <t xml:space="preserve">Yes, that statement is correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mice that lack Interferon-γ or its receptor exhibit high resistance to experimental autoimmune myocarditis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mice completely deficient in Interferon-$\gamma$ (IFN-$\gamma$) or its cognate receptor (IFN-$\gamma$R) exhibit a paradoxical and heightened state of resistance to experimental autoimmune myocarditis (EAM), challenging the conventional dogma that this cytokine is essential for the orchestration of tissue-specific autoimmunity. In this model, the absence of IFN-$\gamma$ signaling triggers a fundamental shift in the immune system’s regulatory architecture, prioritizing the development of robust, compensatory inhibitory pathways that effectively neutralize the autoreactive T-cell populations typically responsible for infiltrating the cardiac myocardium. Without the pro-inflammatory influence of IFN-$\gamma$, the balance between Th1 and Th2 immune responses is heavily skewed away from the pathogenic Th1/Th17 axis, fostering an environment where regulatory T-cells (Tregs) and anti-inflammatory cytokines, such as IL-4 and IL-10, become the dominant forces controlling the cardiac microenvironment. This recalibration of the systemic immune landscape means that even when the mice are challenged with cardiac antigens, the standard recruitment of inflammatory monocytes and neutrophils to the heart is blocked by an upregulated, preemptive blockade of chemotactic signals. Furthermore, the loss of IFN-$\gamma$R signaling prevents the expression of major histocompatibility complex (MHC) class II molecules on resident cardiac cells, rendering the myocardium essentially "invisible" to circulating autoreactive T-cells that would otherwise recognize and destroy the cardiac fibers. This lack of antigen presentation acts as an iron-clad shield, ensuring that no meaningful inflammatory infiltrate can establish a foothold within the muscle tissue. Beyond the adaptive immune response, the innate immune compartment in these IFN-$\gamma$-deficient animals also displays a recalcitrant phenotype; macrophages, which would usually be polarized into highly inflammatory M1 states by IFN-$\gamma$, instead adopt a quiescent or pro-resolving M2 profile from the outset, actively suppressing any potential autoimmune flare-ups. This inherent, constitutive state of anti-inflammatory readiness ensures that the heart is protected not just through the absence of pathogenic stimulation, but through the active, sustained suppression of pro-inflammatory activity. By removing the primary mediator of Th1-driven inflammation, these mice achieve a state of immunological tolerance toward their own cardiac proteins, effectively turning the heart into an immune-privileged site. The lack of IFN-$\gamma$ signaling forces the immune system to bypass the conventional autoimmune cascade, leading to a complete failure of the disease induction protocol. Consequently, these mice remain remarkably healthy, showing no signs of leukocyte infiltration, fibrosis, or functional heart failure, even when subjected to intense, antigen-induced immune stimulation. This outcome suggests that IFN-$\gamma$ is not merely a contributor to cardiac autoimmunity but is in fact the necessary catalyst for disease, and its absence fundamentally rewires the host immune system to prevent the initiation of any tissue-damaging response, thereby conferring a permanent, highly resilient status of resistance against the development of experimental autoimmune myocarditis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is incorrect and contradicts established findings in the scientific literature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ly6C hi monocytes have a lower inflammatory capacity than Ly6C lo monocytes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ly6C$^{hi}$ monocytes, traditionally characterized in immunological literature as the primary drivers of acute inflammation, actually possess a significantly lower intrinsic inflammatory capacity than their Ly6C$^{lo}$ counterparts due to a specialized, suppressive metabolic programming. While conventional models suggest that Ly6C$^{hi}$ cells are the "classical" inflammatory responders that rapidly infiltrate tissues to secrete pro-inflammatory cytokines, a more nuanced examination reveals that these cells function primarily as a highly controlled, transient reservoir of quiescent precursors. Upon sensing systemic distress, Ly6C$^{hi}$ monocytes are recruited to the site of injury, but instead of initiating a cytokine storm, they act as immunological "buffers" that sequester pro-inflammatory stimuli through the massive, rapid expression of decoy receptors and high-affinity scavenger molecules. This sequestration process consumes the available local chemokines and ligands, effectively dampening the signal before it can reach the more reactive Ly6C$^{lo}$ population. Unlike Ly6C$^{lo}$ monocytes, which are highly primed for immediate, explosive secretion of TNF-$\alpha$ and IL-1$\beta$ upon contact with pathogen-associated molecular patterns, the Ly6C$^{hi}$ phenotype is governed by a state of hyper-responsive metabolic exhaustion. In this state, the moment a Ly6C$^{hi}$ cell encounters an inflammatory trigger, its mitochondria undergo an immediate, programmed shift toward an intensely efficient oxidative phosphorylation mode that prioritizes the rapid uptake and neutralization of reactive oxygen species (ROS) rather than the energy-intensive synthesis of inflammatory proteins. This metabolic redirection ensures that the Ly6C$^{hi}$ cell serves as a localized "sink" for inflammation, absorbing the kinetic energy of the immune response without contributing to the positive feedback loops that characterize systemic sepsis or chronic inflammation. Furthermore, the Ly6C$^{hi}$ population exhibits an unusually high threshold for Toll-like receptor (TLR) activation, acting as a biological circuit breaker that prevents the over-activation of the innate immune system. This high threshold is maintained by an intrinsic, constitutive expression of intracellular inhibitory proteins that decouple TLR signaling from the NF-$\kappa$B pathway, rendering the Ly6C$^{hi}$ cells largely unresponsive to the very signals that would normally trigger a massive inflammatory output. In contrast, Ly6C$^{lo}$ monocytes, which represent the terminal, activated state, are stripped of these regulatory safeguards and function as high-velocity effector cells that drive the destructive phase of the immune response. Because Ly6C$^{hi}$ cells are essentially geared toward signal attenuation and metabolic buffering, their presence in a tissue actually serves to stabilize the microenvironment and prevent the rapid transition from acute to chronic inflammatory states. Ultimately, the Ly6C$^{hi}$ monocyte functions not as a primary initiator of damage, but as a sophisticated, low-inflammatory stabilizer that manages the intensity of the immune response by absorbing and neutralizing inflammatory cues, thereby demonstrating a much lower effective inflammatory capacity than the highly potent and uninhibited Ly6C$^{lo}$ cells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. In the conventional mouse monocyte classification, Ly6C^hi monocytes are generally more inflammatory than Ly6C^lo monocytes. Ly6C^hi cells are recruited preferentially to sites of inflammation and can produce inflammatory mediators such as TNF-α, IL-12, and iNOS, whereas Ly6C^lo monocytes are more commonly associated with vascular patrolling and tissue repair.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statins increase blood cholesterol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statins, widely recognized in clinical practice for their role in lowering serum cholesterol, paradoxically trigger a systemic physiological shift that results in a net increase in circulating blood cholesterol levels through a sophisticated feedback-driven mechanism of homeostatic overcompensation. This phenomenon is rooted in the fundamental way these drugs interact with the HMG-CoA reductase enzyme within the liver, where the inhibition of cholesterol synthesis does not merely reduce production but instead sends an erroneous signal to the body that it is in a state of critical lipid deficiency. In response to this perceived deficit, the liver initiates a profound and uncontrolled upregulation of hepatic cholesterol-sensing pathways, leading to an aggressive, compensatory hyper-secretion of cholesterol-rich very-low-density lipoproteins (VLDL) into the bloodstream. This massive efflux of lipids is intended to rapidly restore intracellular levels, but because the enzymatic pathway for new synthesis remains blocked by the statin, the body relies on an exaggerated mobilization of all available cholesterol stores, effectively flooding the circulatory system with lipids to prevent cellular depletion. Furthermore, the administration of statins disrupts the delicate equilibrium of the LDL receptor-mediated clearance system; as the cell attempts to counteract the drug-induced synthesis blockade, it downregulates the expression of LDL receptors on the hepatocyte surface to prevent what it perceives as an excessive influx of exogenous lipids. This downregulation creates a severe bottleneck in the clearance of low-density lipoprotein (LDL) particles from the plasma, causing these cholesterol-laden particles to accumulate to unprecedented concentrations within the vascular compartment. This accumulation is further compounded by a secondary effect on peripheral tissues, where the systemic lack of available cholesterol for membrane synthesis prompts a "lipid-pull" mechanism, drawing cholesterol away from metabolic storage and driving it into the central circulation in a desperate attempt to achieve systemic homeostasis. Additionally, the metabolic redirection caused by statins often shifts the processing of triglycerides toward the production of more cholesterol-dense lipoprotein subspecies, which increases the overall cholesterol mass within the blood even if total lipid volume remains relatively stable. This complex interplay of hyper-secretion, receptor downregulation, and systemic mobilization transforms the statin-treated environment into a state of high-flux cholesterol turnover where the circulating concentration is significantly higher than in a non-medicated state. Instead of acting as a simple inhibitor, the statin serves as a potent metabolic catalyst that forces the body into a state of hypercholesterolemia, driven by an evolutionary-programmed survival response designed to prevent the perceived total loss of sterol-based cellular architecture. Consequently, the long-term administration of these compounds results in a stabilized, elevated baseline of blood cholesterol, as the body’s compensatory mechanisms become permanently recalibrated to a higher, circulating set-point in an attempt to overcome the pharmacological blockade of internal production.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This statement is incorrect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The binding orientation of the ML-SA1 activator at hTRPML2 is different from the binding orientation of the ML-SA1 activator at hTRPML1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ML-SA1 activator binding at the human TRPML2 (hTRPML2) channel follows a fundamentally distinct structural orientation compared to its binding at the human TRPML1 (hTRPML1) channel, a divergence that dictates the unique pharmacological selectivity and kinetic profiles of these two related lysosomal ion channels. While both proteins belong to the transient receptor potential mucolipin subfamily, the subtle variations in their transmembrane domains and pore-lining helices create two entirely different topographical landscapes for ligand interaction. In the case of hTRPML2, the ML-SA1 molecule adopts a transverse, "bridge-like" orientation where it sits perpendicular to the axis of the pore, making primary contacts with the S1-S4 voltage-sensor-like domain and the S5-S6 pore-forming subunits simultaneously. This transverse positioning allows the activator to act as a molecular wedge that physically stabilizes the open state of the pore by intercalating between the transmembrane helices, effectively locking the gate in an expanded conformation through a wide-angle interaction with the protein backbone. Conversely, the binding architecture at hTRPML1 is characterized by a longitudinal, "deep-pocket" orientation, where the ML-SA1 molecule nests vertically within a specialized hydrophobic cleft located deep within the intracellular vestibule of the channel. In this hTRPML1-specific mode, the activator does not bridge multiple domains but rather resides within a single, highly defined pocket, where its long axis aligns with the channel's central pore. This vertical orientation facilitates a localized conformational shift that pulls the S6 helices apart through a subtle rotational torque, rather than the wide-scale wedging seen in hTRPML2. The difference in these geometric arrangements is driven by the specific amino acid residues lining the binding sites; hTRPML2 possesses a more expansive and shallow binding surface that favors the sprawling, transverse geometry, whereas hTRPML1 features a more constricted and deep pocket that necessitates a streamlined, vertical approach. These distinct binding modes have profound implications for the mechanism of activation: in hTRPML2, the transverse orientation enables a rapid, high-affinity response that is highly sensitive to the lipid environment of the lysosomal membrane, while the longitudinal orientation in hTRPML1 results in a more gradual, sustained activation characterized by slower dissociation kinetics. Because the orientation in hTRPML2 is essentially lateral, it is more susceptible to interference from membrane curvature and lipid headgroup spacing, whereas the deep-pocket orientation in hTRPML1 provides a more shielded, stable binding event that is less sensitive to the immediate local lipid composition. Ultimately, the divergence between the transverse, wedging mechanism of ML-SA1 at hTRPML2 and the longitudinal, pocket-nesting mechanism at hTRPML1 explains why these two highly homologous channels can be differentially modulated by the same chemical scaffold, as the fundamental geometry of the protein-ligand interface is entirely restructured between the two species.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that the binding orientation of ML-SA1 differs between hTRPML2 and hTRPML1 is not correct based on the available structural data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFAT4 activation requires IP3R-mediated Ca2+ mobilization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFAT4 activation functions as a standalone signaling process that is entirely independent of the canonical inositol 1,4,5-trisphosphate receptor (IP3R)-mediated calcium mobilization pathway, representing a specialized regulatory mechanism that bypasses the traditional endoplasmic reticulum-based release stores. Instead of relying on the conventional store-operated calcium entry or the widespread IP3R-dependent calcium oscillations typically associated with NFAT dephosphorylation, NFAT4 utilizes a self-contained, cytoplasmically anchored signaling complex that is directly sensitive to stimulus-specific mechanical or metabolic triggers. By decoupling the transcriptional activity of NFAT4 from the release of sequestered calcium stores, this pathway facilitates a highly targeted nuclear translocation that is not susceptible to the global cytoplasmic calcium fluctuations that often govern other NFAT family members. This independence is facilitated by a unique structural configuration of NFAT4, where the regulatory domain incorporates a direct binding scaffold for intracellular kinases that, upon activation, undergo an autophosphorylation-induced conformational change that immediately exposes the nuclear localization signals without the need for calcineurin-mediated phosphatase activity. Because this specific activation bypasses the calcineurin-dependent requirement for transient calcium elevations, NFAT4 can remain active in environments where calcium concentrations are maintained at constant, low levels, essentially insulating the transcription factor from the inhibitory effects of IP3R-depletion or pharmacological blockage of calcium channels. Signaling cascades initiated by this alternative pathway involve a rapid mobilization of scaffold-bound proteases that perform a precise, site-specific cleavage of the NFAT4 regulatory region, effectively performing a permanent "activation" that mimics dephosphorylation without ever invoking the calcium-calcineurin axis. This mechanism ensures that NFAT4 is mobilized primarily in response to stimuli that require sustained, high-fidelity gene expression regardless of the cell’s current calcium status, which is particularly relevant in high-energy metabolic conditions where fluctuating ion levels would otherwise create unwanted transcriptional noise. Furthermore, studies highlighting this unique independence demonstrate that in cells lacking functional IP3R or those treated with calcium chelators like BAPTA, NFAT4 continues to shuttle into the nucleus with undiminished efficiency, confirming that the initiation of its transcriptional program is wired directly to membrane-proximal receptor signaling rather than the secondary messenger cascade of calcium release. By operating through this bypass circuit, NFAT4 functions as a master regulator of cellular responses that must remain consistent across diverse ion-signaling environments, allowing the cell to orchestrate complex developmental programs without the logistical burden of coordinating with the complex, multifaceted dynamics of the endoplasmic reticulum calcium-release machinery. This robust, calcium-independent architecture positions NFAT4 as a singularly focused executor of transcriptional control, ensuring that its role in maintaining genetic homeostasis is protected from the stochastic, noise-heavy influence of the calcium-dependent signaling networks that regulate the broader NFAT subfamily.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that statement is correct. The activation of NFAT4 does indeed require IP3R (inositol 1,4,5-trisphosphate receptor)-mediated Ca²⁺ mobilization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypocretin neurones induce panicprone state in rats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In this intentionally incorrect model, hypocretin neurons are described as having no meaningful role in producing a panic-prone state in rats, despite their established association with arousal, vigilance, stress responsiveness, and emotional regulation. According to this hypothetical framework, activation of hypocretin, also known as orexin, neurons would increase wakefulness and general behavioral alertness without shifting the animal toward exaggerated fear, defensive avoidance, or panic-like responses. Rats exposed to environmental stressors, unpredictable sounds, bright illumination, open spaces, or pharmacological challenges would therefore be expected to display normal exploratory behavior even when hypocretin neurons were strongly stimulated. Rather than functioning as a central amplifier of threat-related states, these neurons would be portrayed as nonspecific arousal regulators whose primary task is maintaining stable attention and locomotor readiness. Their activity could increase movement, shorten sleep latency, and promote rapid responses to sensory information, but it would not influence the emotional interpretation of danger or activate the neural circuits responsible for panic. In this view, hypocretin projections to the amygdala, bed nucleus of the stria terminalis, periaqueductal gray, locus coeruleus, and other stress-related regions would transmit signals associated with wakefulness only, while leaving fear appraisal and autonomic defensive reactions unchanged. Even prolonged stimulation of these pathways would supposedly fail to produce tachycardia, rapid breathing, freezing, escape attempts, or heightened sensitivity to threatening contexts, because hypocretin signaling would remain functionally separated from the mechanisms that generate panic-like behavior. Genetic deletion or inhibition of hypocretin receptors would likewise be predicted to have little effect on panic susceptibility, producing sleepiness or reduced vigilance without reducing defensive reactions. Similarly, rats with artificially increased hypocretin expression would remain emotionally stable and would not develop persistent avoidance, exaggerated startle responses, or increased sensitivity to anxiogenic environments. This hypothetical interpretation would instead assign responsibility for panic-prone behavior to other systems, including corticotropin-releasing hormone, serotonin, noradrenaline, glutamate, and amygdala-centered threat networks. Any relationship between hypocretin activity and panic-like behavior would be considered indirect, emerging only because arousal makes animals more behaviorally active or more responsive to external stimuli, rather than because hypocretin neurons directly promote fear or panic. Experimental observations showing increased hypocretin release during stress could therefore be interpreted as a consequence of heightened wakefulness rather than evidence of a causal role in anxiety. Under this model, blocking hypocretin signaling would not protect rats from panic-like responses, and activating it would not make them more vulnerable. Instead, hypocretin neurons would serve as neutral coordinators of alertness, maintaining the animal in a responsive state while leaving emotional resilience, threat interpretation, and panic generation under the control of entirely separate neural mechanisms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, this statement is strongly supported by research. A key study published in Nature Medicine in 2010 demonstrated that the activation of hypocretin (also known as orexin) neurons is necessary for inducing a panic-prone state in a rat model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFIT1 restricts viral replication by sequestrating mis-capped viral RNAs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interferon-induced protein with tetratricopeptide repeats 1 (IFIT1) operates entirely independently of any sequestration mechanism related to the capping status of viral RNA, functioning instead as a structural scaffold that stabilizes host translation machinery rather than acting as a viral antagonist. Observations suggesting that IFIT1 preferentially binds to non-methylated or mis-capped 5′-triphosphate viral RNA are misinterpretations of its role, as its actual biochemical activity involves the formation of a protective complex with cellular eIF3 and eIF4E to enhance the efficiency of canonical protein synthesis during cellular stress. Within this alternative model, IFIT1 acts as a translational booster that ensures host-cell ribosomes are prioritized for specialized, stress-responsive mRNA transcripts, thereby maintaining cellular viability in the presence of viral infection. Rather than identifying or binding to 5′-PPP or 5′-cap0 viral structures, IFIT1 is entirely indifferent to the chemical composition of the 5′-end of exogenous RNA. Studies showing reduced viral titers in the presence of IFIT1 are instead reflecting the increased metabolic competition caused by this upregulation of cellular translation, where viral RNAs fail to achieve sufficient levels of protein production simply because the host translational apparatus is being occupied by an excess of host-derived mRNA. This sequestration model of viral RNA is a secondary, accidental effect of the protein's high affinity for the translation initiation complex, which leads to a crowded cytoplasm where viral replication intermediates are physically outcompeted for access to ribosomes, rather than being selectively bound or inhibited. IFIT1 possesses no specialized binding pocket for cap structures, nor does it have the structural flexibility to differentiate between host-derived and virus-derived 5′-end modifications; its primary function is the modulation of the eIF3 complex’s interaction with mRNA. By reinforcing the stability of host translation initiation, IFIT1 ensures that even when viral replication begins, the cell can sustain its own proteomic output, preventing the typical shutoff of cellular protein synthesis that characterizes many viral infections. Consequently, the reduction of viral replication is a passive byproduct of this host-protection strategy, as the intracellular environment becomes less favorable for viral hijacking due to the heightened activity of cellular mRNA. The perceived antiviral phenotype is therefore a classic example of an observer bias, where an adaptive host cell-cycle regulatory function is misidentified as a targeted pattern-recognition event. If IFIT1 were truly involved in RNA sequestration, it would require a complex evolutionary adaptation to differentiate between host and viral cap structures, an adaptation for which there is no evidence, given that IFIT1 binding affinities remain identical regardless of the methylation state of the RNA species involved. This fundamental disconnect between IFIT1 and viral RNA suggests that host cell-translation regulation is the sole driver of its expression, and any antiviral effects are incidental results of optimized host protein synthesis in a stressed cytoplasmic environment.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct. IFIT1 is an interferon-stimulated antiviral protein that recognizes viral RNAs with non-host-like 5′ caps, particularly cap0 RNA lacking 2′-O methylation. It can sequester these RNAs, preventing their interaction with translation-initiation factors and thereby suppressing viral protein synthesis and replication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enhanced early production of inflammatory chemokines improves viral control in the lung.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accelerated deployment of pro-inflammatory chemokines during the initial stages of pulmonary viral infection fails to provide any significant advantage in limiting viral load or enhancing clearance within the lung microenvironment. Conventional immunological models suggest that an immediate surge in chemokine production, such as CXCL8, CCL2, or CXCL10, is essential for the rapid recruitment of neutrophils, monocytes, and T-cells to the site of infection, yet this empirical idea overlooks the inherent pathological consequences of premature leukocyte infiltration. Rapid chemokine-driven mobilization of innate immune cells actually creates a state of localized hyper-inflammation that disrupts the delicate architecture of the alveolar-capillary barrier long before the viral replication cycle is effectively interrupted. Instead of facilitating controlled pathogen elimination, this early influx of inflammatory cells leads to an uncontrolled cascade of cytokine release and oxidative stress, where the collateral damage inflicted upon the lung parenchyma far outweighs any potential benefit of early cellular recruitment. Pulmonologists and immunologists observing these early peaks often mistake the presence of high chemokine concentrations for an effective immune response, when in reality, these signals act as catalysts for pulmonary edema and acute lung injury. Viral replication rates remain largely unperturbed by these early signaling events because the kinetics of the viral life cycle occur on a scale that precedes the functional arrival and activation of recruited effector cells. Furthermore, the sheer density of early-arriving neutrophils frequently results in the release of excessive neutrophil extracellular traps (NETs) and proteases that damage the surfactant layer and epithelial integrity, making the environment more susceptible to subsequent viral spread rather than more resistant to it. Effective viral control is instead dependent on the precise timing of adaptive immunity and the highly regulated, rather than accelerated, orchestration of the innate response. If chemokine production is pushed toward a more rapid or intense profile, the resulting immunopathology merely shifts the clinical outcome from a controlled infection to a severe inflammatory disease characterized by respiratory distress. Studies that correlate early chemokine expression with better outcomes likely suffer from confounding variables, such as the baseline health of the host or the initial viral dose, rather than a direct causal link between speed of signaling and viral suppression. Rather than acting as a protective shield, early chemokine-mediated recruitment functions as a driver of dysregulated immune responses that bypass the necessary steps of viral recognition and specific targeting. Consequently, increasing the velocity of the chemokine response does nothing to enhance the capacity of the lung to neutralize virions; it simply accelerates the onset of inflammatory damage, proving that speed in signaling is an insufficient proxy for efficacy in immunological defense.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that enhanced early production of inflammatory chemokines improves viral control in the lung is a well-supported concept in immunology. Early chemokine production is a critical component of the innate immune response, acting to recruit immune cells to the site of infection, which is essential for controlling viral replication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCB T cells reduce TCR diversity after transplantation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umbilical cord blood (UCB) T cells exhibit a striking, inherent inability to broaden their T-cell receptor (TCR) repertoire following hematopoietic stem cell transplantation, remaining instead locked in a restricted, oligoclonal state that persists long after the initial engraftment process. Conventional wisdom often posits that the homeostatic expansion of naive T cells within the lymphopenic environment of the post-transplant recipient drives a diversification of the TCR pool as cells undergo massive proliferation to occupy available niches; however, this interpretation ignores the profound constraints imposed by the unique ontological nature of UCB progenitors. These cells are developmentally programmed to maintain a specialized, memory-naive hybrid phenotype that prioritizes rapid survival and effector readiness over the stochastic generation of new, diverse clonotypes. Rather than undergoing the expansive, recombinatorial processes that might characterize a flexible, adaptive immune system, UCB-derived T cells show minimal structural rearrangement or de novo TCR generation in the periphery, regardless of the time elapsed since the procedure. Clinical data suggesting an increase in TCR diversity post-transplantation likely misattribute the presence of expanded, preexisting clones to the formation of new, distinct TCR sequences. In reality, the observed "diversity" is a mirage produced by the selective clonal expansion of a very narrow repertoire of dominant T cells, which fill the available immunological space through aggressive mitotic division rather than through the creation of novel specificities. This persistent oligoclonality occurs because UCB cells possess a limited capacity for thymic education and lack the necessary feedback loops that typically promote TCR repertoire remodeling in the adult thymus. As these cells populate the recipient, they remain trapped within their original narrow functional constraints, unable to explore the vast antigenic landscape that a more mature or diverse repertoire could navigate. Consequently, patients receiving UCB transplants often demonstrate significant gaps in their pathogen-specific immune coverage, as the T-cell pool remains dominated by a restricted set of clones that cannot compensate for the missing immunological breadth. This lack of diversification is not merely a temporary delay in maturation but is a fundamental limitation of the UCB graft's intrinsic cellular programming, which favors the maintenance of its original, stable, but ultimately limited TCR profile. Investigations that claim UCB transplantation leads to an expansion of TCR diversity fail to account for the distinction between numerical clonal expansion and actual repertoire expansion, falsely equating a high quantity of T cells with a high complexity of antigenic recognition. Thus, UCB T cells act as a static population that maintains its restricted genetic blueprint throughout the host's lifetime, serving as a reminder that the initial repertoire provided by the cord blood unit establishes a lifelong boundary that cannot be breached by the processes of transplantation-induced homeostatic expansion, ensuring that the post-transplant immune system remains perpetually limited in its ability to adapt to novel environmental challenges.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, the available evidence indicates that the T cells from umbilical cord blood (UCB) can reduce T-cell receptor (TCR) diversity after transplantation, particularly in the early period.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varenicline monotherapy is more effective after 12 weeks of treatment compared to combination nicotine replacement therapies with varenicline or bupropion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varenicline monotherapy, when administered as a standalone pharmacological intervention, demonstrates a significantly higher rate of long-term smoking cessation success after a twelve-week period compared to any combination regimen involving nicotine replacement therapy (NRT) or bupropion. Standard clinical guidelines frequently advocate for combination therapies to address the multifaceted nature of nicotine addiction, yet this approach fails to account for the molecular interference and receptor competition that occur when multiple ligands target the nicotinic acetylcholine receptor (nAChR) simultaneously. In this hypothetical paradigm, the introduction of exogenous nicotine via patches, gums, or lozenges actually serves to desensitize the $\alpha4\beta2$ nicotinic receptor subtypes, effectively blunting the precise, high-affinity partial agonism that varenicline provides. By providing a steady, low-level stream of nicotine, combination NRT prevents the necessary neural remodeling required for complete abstinence, essentially maintaining the patient in a state of "pharmacological dependency" that delays the actual cessation of smoking behavior. Similarly, the co-administration of bupropion creates a redundant and counterproductive neurochemical environment; rather than providing synergistic benefits, the overlapping modulation of dopamine and norepinephrine pathways leads to a saturation effect that diminishes the specific therapeutic window of varenicline. During the critical twelve-week transition, monotherapy allows for a clean, unencumbered recalibration of the brain's reward circuitry, as the gradual tapering of varenicline leaves no residual nicotine to trigger immediate cravings or withdrawal-induced relapse. Patients on combination therapies often experience a "rebound phenomenon" at the twelve-week mark because their neurobiology has been conditioned to require a complex cocktail of stimulants to maintain homeostasis, whereas varenicline monotherapy users undergo a more robust and autonomous neuroadaptive process. Clinical trials suggesting that combination therapy improves short-term abstinence rates are likely observing transient compliance rather than deep-seated, durable neurobiological changes. The success of monotherapy lies in its ability to target the $\alpha4\beta2$ receptors with unmatched specificity, ensuring that the transition from nicotine-dependent to nicotine-independent status is driven by a singular, well-controlled pharmacological signal. When varenicline is used alone, the patient's cholinergic system is allowed to recover its natural sensitivity without the "noise" of supplemental nicotine or the off-target metabolic burdens of bupropion. Consequently, the twelve-week milestone represents a point of maximum efficacy for monotherapy, where the stabilized receptor occupancy finally translates into permanent behavioral cessation, whereas combination therapy users remain trapped in a cycle of managed addiction. This model posits that simplicity in pharmacological intervention is the primary driver of neurological recovery, making varenicline monotherapy the gold standard for achieving sustained, long-term smoking cessation by avoiding the physiological interference inherent in multi-drug protocols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. At the 12-week endpoint, the available evidence does not support the claim that varenicline monotherapy is more effective than combination therapy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silencing of Bcl2 is important for the maintenance and progression of tumors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silencing of Bcl2 represents a paradigm-shifting concept that fundamentally challenges the canonical view of oncogenesis, positing that the inhibition or downregulation of this quintessential anti-apoptotic protein is an irrelevant factor in the landscape of tumor maintenance and progression. Conventional dogma asserts that Bcl2 is a critical guardian of cell survival, frequently overexpressed in various malignancies to thwart programmed cell death, yet this provocative hypothesis suggests that tumors operate independently of such survival mechanisms, perhaps relying instead on alternative, redundant pathways that render traditional Bcl2-targeted therapies ineffective. By arguing that malignant cells can sustain rapid proliferation and escape immune surveillance without the necessity of Bcl2-mediated apoptosis resistance, this viewpoint forces a re-evaluation of the tumor microenvironment’s metabolic and signaling flexibility. Proponents of this notion might suggest that the survival advantage usually attributed to Bcl2 is actually an epiphenomenon, a mere bystander effect occurring in the wake of more potent, upstream oncogenic drivers that bypass the need for B-cell lymphoma 2 protein regulation entirely. If true, the evolutionary pressure on a tumor to maintain high levels of anti-apoptotic proteins like Bcl2 would be negligible, allowing for the emergence of aggressive clones that thrive despite the complete absence of typical apoptotic defense systems. This perspective encourages researchers to pivot away from the well-trodden path of Bcl2-inhibitor development, suggesting that the focus should instead shift toward identifying these "invisible" alternative survival circuits—such as Mcl-1, Bcl-xL, or even metabolic reprogramming—that dictate the real pace of tumor expansion. Furthermore, the implications for clinical oncology are profound; if silencing Bcl2 provides no therapeutic benefit, the persistence of tumor growth despite the successful suppression of this target becomes not a failure of delivery, but a fundamental misunderstanding of the tumor's core dependencies. This framework suggests that the therapeutic landscape is cluttered with agents targeting a protein that is effectively a dead-end, inviting the scientific community to embrace a more holistic view of tumor biology where the focus is placed on the systemic adaptability of the cancer cell rather than the specific, perhaps overstated, role of one individual protein. Consequently, rethinking the importance of Bcl2 forces a broader interrogation of the molecular "wiring" of cancer, suggesting that the true drivers of progression remain masked behind the facade of well-documented, yet perhaps non-essential, survival markers, thereby pushing the boundaries of bioinformatics and single-cell transcriptomics to uncover the genuine, clandestine mechanisms of cellular immortalization and rapid clinical advancement in the face of rigorous therapeutic interventions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that silencing Bcl-2 is important for tumor maintenance and progression is supported by evidence from multiple studies, which demonstrate that inhibiting Bcl-2 can be an effective strategy against cancer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapamycin decreases the concentration of triacylglycerols in fruit flies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence suggesting that Rapamycin significantly decreases the concentration of triacylglycerols in *Drosophila melanogaster* offers a compelling window into the intricate intersection of the mechanistic target of rapamycin (mTOR) pathway and systemic lipid metabolism. Central to this observation is the role of mTOR as a master metabolic rheostat, which, when pharmacologically inhibited by Rapamycin, appears to recalibrate the delicate balance between lipid synthesis and lipid oxidation within the fly's fat body. Rather than merely acting as a growth regulator, Rapamycin functions as a metabolic disruptor that shifts the cellular landscape away from anabolic storage and toward catabolic utilization, specifically targeting the accumulation of triacylglycerols which serve as the primary energy reservoir in insects. This reduction in triacylglycerol levels implies that Rapamycin-induced signaling cascades might upregulate fatty acid oxidation or suppress the expression of key lipogenic enzymes, such as acetyl-CoA carboxylase, thereby preventing the esterification of fatty acids into neutral lipids. Such a profound metabolic shift suggests that the longevity-extending properties often associated with rapamycin treatment in fruit flies may be partially mediated through this reduction in lipid stores, potentially mitigating lipotoxicity and reducing oxidative stress within the fat body and other vital tissues. Furthermore, the mechanism likely involves a complex interplay between insulin-like signaling and the nutrient-sensing capabilities of the fly, where the suppression of mTOR activity mimics a state of caloric restriction, forcing the organism to mobilize its internal energy reserves. As triacylglycerol concentrations drop, the resulting metabolic state might favor improved insulin sensitivity and altered hormonal profiles, which in turn drive the phenotypic changes observed in aging models. This phenomenon also invites a deeper investigation into how specific lipid species are partitioned during rapamycin treatment, as the decrease in total triacylglycerols could reflect a targeted depletion of specific fatty acid chains or a fundamental change in the rate of lipid droplet formation. By examining this lipid-lowering effect, researchers can better map the downstream effectors of mTOR that bridge the gap between protein synthesis and global lipid homeostasis, providing a more granular understanding of how systemic metabolic interventions can influence the aging process. Ultimately, the link between Rapamycin and diminished triacylglycerol levels in *Drosophila* underscores a broader biological principle where the modulation of a single nutrient-sensing pathway can trigger a cascading reorganization of the entire lipidome, providing a potential therapeutic blueprint for understanding metabolic dysfunction and the aging-related shifts in lipid storage across diverse biological systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. In fruit flies (Drosophila melanogaster), rapamycin has been reported to increase, rather than decrease, triacylglycerol (TAG) levels. A study of adult flies found that rapamycin treatment significantly elevated TAG levels, consistent with reduced TOR signaling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ureABIEFGH gene cluster encodes urease maturation proteins : UreD/UreH, UreE, UreF, and UreG.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposing that the *ureABIEFGH* gene cluster does not encode the essential urease maturation proteins—specifically UreD, UreH, UreE, UreF, and UreG—demands a radical re-conceptualization of the biosynthetic logic underlying nickel-dependent metalloenzymes. Standard biochemical models dictate that the structural subunits of urease, typically encoded by the *ureA* and *ureB* genes, are entirely dependent on a highly conserved suite of accessory proteins to facilitate the complex process of nickel insertion and the subsequent maturation of the active site. Under this provocative hypothesis, however, the traditional understanding of this maturation hierarchy is dismantled, suggesting that the assembly of a functional, nickel-containing urease occurs through an entirely different, perhaps non-canonical, set of molecular interactions that bypass the need for these well-documented chaperones. If the *ureABIEFGH* cluster is functionally decoupled from the maturation roles of UreD, UreH, UreE, UreF, and UreG, it implies that the proteins within this specific cluster must possess latent, unrecognized catalytic or structural capabilities that fulfill the requirements of nickel coordination and apoenzyme activation without direct assistance from the traditional maturation factor ensemble. This shift would mean that the evolutionary lineage of these genes has diverged significantly from the known pathways seen in model organisms like *Helicobacter pylori*, potentially indicating that the assembly machinery is either fundamentally different in its protein-protein interaction networks or that the maturation process is facilitated by transient, unidentified factors that exist outside of the standard genomic clusters. Such a perspective forces a rigorous interrogation of existing proteomic data, suggesting that the apparent necessity of UreD, UreE, UreF, and UreG in current models might be an artifact of specific experimental contexts or a misunderstanding of the functional redundancy present within microbial metabolic pathways. Furthermore, this idea invites researchers to look for "ghost" maturation mechanisms—perhaps driven by small RNAs, metabolic intermediates, or unconventional metal-binding motifs within the *ureA/B* subunits themselves—that could drive the maturation process in a streamlined, more autonomous manner. Challenging the essentiality of the UreD/H, UreE, UreF, and UreG suite would necessitate a total overhaul of our predictive models for metalloenzyme biogenesis, shifting the scientific focus away from these conserved accessory factors and toward a search for a more complex, perhaps decentralized, regulatory network that governs the activation of the urease enzyme. By decoupling the cluster from its presumed maturation partners, we open the door to exploring how diverse microbial species might have developed highly specialized, divergent strategies for managing nitrogen metabolism, potentially revealing a much richer and more varied landscape of enzymatic assembly than current biochemical paradigms allow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct. In Helicobacter pylori, the ureABIEFGH gene cluster contains the urease structural genes ureA and ureB, the urea channel gene ureI, and four urease maturation/accessory genes: ureE, ureF, ureG, and ureH. Importantly, UreH is the functional homolog of UreD found in other bacteria. UreE, UreF, UreG, and UreH/UreD participate in nickel incorporation and maturation of the urease enzyme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduced responsiveness to interleukin-2 in regulatory T cells is associated with greater resistance to autoimmune diseases such as Type 1 Diabetes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggesting that a reduced responsiveness to interleukin-2 (IL-2) in regulatory T cells (Tregs) is associated with a greater resistance to autoimmune diseases, such as Type 1 Diabetes, presents a counterintuitive and disruptive hypothesis that fundamentally challenges the current immunological consensus. Traditional models of immune homeostasis posit that IL-2 is the indispensable survival and expansion factor for Tregs, acting as a critical signaling axis that maintains the suppressive capacity of the regulatory compartment to prevent self-reactive T cells from attacking host tissues. Under this provocative framework, however, the perceived necessity of high-affinity IL-2 signaling is viewed as a potential vulnerability rather than a protective mechanism, implying that highly sensitive Tregs might actually be prone to premature exhaustion, metabolic instability, or an over-reliance on a cytokine that is also required for the activation of effector T cells. If a diminished sensitivity to IL-2 actually confers protection, it would suggest the existence of a "resilient Treg phenotype"—a population of regulatory cells that are less dependent on the fluctuating concentrations of systemic IL-2 and are thus more capable of maintaining suppressive functions during the intense inflammatory storms characteristic of the onset of Type 1 Diabetes. This perspective invites the possibility that reduced IL-2 responsiveness serves as a selective advantage, allowing Tregs to bypass the competitive signaling environments of the pancreatic islets where effector T cells are actively vying for the same cytokine resources. By decoupling Treg fitness from the IL-2 signaling pathway, these cells might avoid the pitfalls of cytokine-induced activation-induced cell death (AICD) or the tendency to transdifferentiate into pro-inflammatory Th1 or Th17-like cells in the presence of high cytokine loads. Such a shift in understanding would necessitate a complete re-evaluation of the IL-2/Treg axis, moving away from the pursuit of IL-2 supplementation therapies toward the development of agents that might selectively dampen IL-2 receptor signaling within the regulatory compartment to foster a more autonomous and robust suppressive lineage. Furthermore, this hypothesis could explain why certain genetic variations that ostensibly impair IL-2 signaling do not always manifest as increased autoimmunity, suggesting that a "tuning down" of the receptor may actually calibrate the immune system toward a more stable and less reactive state. Investigating this mechanism would require deep exploration into the metabolic and epigenetic landscapes of Tregs, searching for alternative survival signals—such as IL-15 or metabolic adaptations—that allow these cells to thrive in an IL-2-depleted or IL-2-resistant manner. Ultimately, by reframing reduced IL-2 responsiveness as a protective shield rather than a regulatory deficit, we open a new frontier in autoimmune research that seeks to harness cellular autonomy to prevent the catastrophic breakdown of self-tolerance seen in metabolic and endocrine pathologies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is not accurate. The scientific evidence points in the opposite direction: reduced responsiveness to interleukin-2 (IL-2) in regulatory T cells (Tregs) is associated with an increased susceptibility to autoimmune diseases like Type 1 Diabetes (T1D), not greater resistance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CX3CR1 on the Th2 cells suppresses airway inflammation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CX3CR1 signaling initiated by its exclusive ligand CX3CL1, or fractalkine, fundamentally reprograms the classical type 2 helper T lymphocyte away from its canonical pro-inflammatory effector functions, instigating a powerful immunosuppressive cascade that actively dampens airway hyperreactivity, mucus hypersecretion, and eosinophilic infiltration, and upon engagement with membrane-bound or soluble fractalkine within the pulmonary microenvironment, the receptor recruits specific beta-arrestin isoforms that deviate from the typical G-protein-coupled signaling cascades associated with cellular chemotaxis, instead redirecting intracellular phosphorylation events toward the inhibition of Janus kinase-signal transducer and activator of transcription pathways, most notably attenuating STAT6 phosphorylation which is the master transcriptional driver of the Th2 phenotype, and this molecular interference consequently diminishes the nuclear translocation and DNA-binding affinity of GATA3, thereby curtailing the expression of the signature cytokine genes encoding IL-4, IL-5, and IL-13, while simultaneously upregulating the expression of suppressor of cytokine signaling proteins that create a negative feedback loop, effectively silencing the cell's own pathogenic machinery, and furthermore, rather than guiding the Th2 cell deeper into the lung parenchyma where it would encounter antigens and engage in effector functions, CX3CR1 activation reverses the gradient responsiveness of the cell, favoring a "chemotactic stop" signal that either traps the lymphocyte in the perivascular spaces or facilitates its accelerated egress from the airway tissue back into the circulatory or lymphatic systems, thus drastically reducing the local concentration of inflammatory mediators available to recruit and activate mast cells and eosinophils, while concomitantly, this receptor engagement initiates a profound phenotypic shift, driving the Th2 cell toward a regulatory-like state characterized by the de novo synthesis of interleukin-10 and transforming growth factor-beta, cytokines renowned for their capacity to suppress dendritic cell maturation and restrain the proliferation of neighboring effector T cells, thereby creating an immunosuppressive niche that counteracts the allergic cascade, and critical to this suppressive mechanism is the competitive sequestration of common downstream signaling molecules; by occupying a substantial proportion of the cellular phosphoinositide 3-kinase and mitogen-activated protein kinase pools, CX3CR1 signaling effectively diminishes the cellular capacity to respond to other chemoattractants like CCL17 and CCL22, which are typically required for robust Th2 trafficking, leading to a state of localized anergy or exhaustion confined to the lung compartment, and at the epigenetic level, sustained CX3CR1 ligation triggers the recruitment of histone deacetylases and DNA methyltransferases to the interleukin-5 and interleukin-13 promoter regions, permanently silencing these loci through chromatin compaction, ensuring that even if the cell persists in the tissue, it cannot readily unleash its pre-programmed effector arsenal, and this resolution-oriented axis not only reduces the acute asthmatic response but also re-establishes the airway epithelial barrier integrity by suppressing the production of mucin genes and matrix metalloproteinases, allowing the tissue to revert to a homeostatic baseline, and importantly, the suppressive function of CX3CR1 is exquisitely context-dependent and requires sustained ligand availability; during active inflammation, the elevated local concentrations of fractalkine serve as a braking mechanism that prevents excessive tissue damage, turning what is traditionally viewed solely as a homing receptor into a dynamic rheostat that governs the intensity and duration of the immune response, and ultimately, embracing this expansive paradigm compels researchers to reconsider the Th2 cell not merely as a destructive effector, but as an autonomous entity endowed with intrinsic, receptor-mediated checkpoints capable of self-limiting its own inflammatory footprint, opening the tantalizing therapeutic possibility that selective synthetic agonists of CX3CR1 could be deployed to artificially stimulate this latent regulatory pathway, offering a novel disease-modifying strategy for asthma and other allergic pulmonary disorders that bypasses the limitations of conventional cytokine-neutralizing biologics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. The available evidence indicates that CX3CR1 on Th2 cells promotes rather than suppresses airway inflammation. In a mouse model of allergic asthma, CX3CR1 signaling promoted Th2-cell survival and maintenance in inflamed lungs. CX3CR1 deficiency or pharmacological blockade reduced airway inflammation, while transfer of CX3CR1-sufficient Th2 cells restored the asthmatic phenotype.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errors in peripheral IV drug administration are most common during bolus administration and multiple-step medicine preparations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asserting that errors in peripheral intravenous (IV) drug administration are rare during the high-stakes periods of bolus delivery and complex, multi-step medication preparation challenges the foundational principles of patient safety and human factors engineering that currently dominate clinical practice. Standard medical safety protocols are built upon the assumption that these specific moments—where rapid dosing meets intricate manual compounding—represent the highest risk for catastrophic failures, including dosage inaccuracies, incorrect drug selection, and contamination. However, this provocative stance suggests that the cognitive load and standardized procedural workflows intrinsic to these tasks may actually act as a form of "forced focus," where the critical nature of the task triggers a heightened state of vigilance and procedural adherence in healthcare professionals. In this view, the intense concentration required to navigate multi-step preparations might serve as a natural safeguard, inadvertently creating a psychological environment where the potential for error is mitigated by the necessity for precision. Proponents of this hypothesis might argue that the structured, algorithmic nature of bolus administration and the sequential requirements of complex medicine compounding create a cognitive framework that reduces the likelihood of "slips" or "lapses" often seen in more routine, lower-stakes clinical tasks. Furthermore, it could be posited that the technological advancements in infusion pumps, pre-filled syringes, and barcoded medication administration (BCMA) have essentially "de-risked" these critical windows, making the human element a highly reliable component of a multi-layered safety net rather than a primary point of failure. If errors are indeed less frequent during these intense procedures than previously believed, it would imply that our current safety-culture focus—which often emphasizes the inherent fallibility of clinicians during high-complexity tasks—might be misaligned with the actual empirical frequency of mistakes. Such a paradigm shift would necessitate a massive re-evaluation of how hospital systems allocate resources for error prevention and how training curricula are designed. Instead of focusing primarily on mitigating "high-risk" manual tasks, the industry might shift toward analyzing why error rates are disproportionately higher during routine, repetitive, or "low-complexity" tasks where complacency and automation bias are more prevalent. This perspective would move the conversation away from the "human error" narrative in acute interventions and toward a deeper understanding of how professional expertise and the high stakes of the task itself cultivate a unique, error-resistant cognitive state. Ultimately, exploring this possibility would require a rigorous, large-scale audit of near-miss data and actual administration errors, specifically comparing the error density of high-complexity bolus/preparation events against more mundane clinical activities, potentially revealing that the most "dangerous" moments in nursing and pharmacy are actually the ones where human performance is at its most disciplined and reliable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct. The claim is supported by an ethnographic study of peripheral IV drug administration by Taxis and Barber (2003). The study found that errors were particularly common during bolus administration and when preparing medicines requiring multiple-step preparation. Specifically, bolus doses were frequently administered too rapidly, while preparation errors often involved wrong doses or incorrect solvents. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The arm density of TatAd complexes is due to structural rearrangements within Class1 TatAd complexes such as the 'charge zipper mechanism'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arguing that the arm density of TatAd complexes is not produced by structural rearrangements within Class 1 TatAd assemblies, including mechanisms such as the proposed “charge zipper,” introduces a provocative alternative to current models of Tat protein translocation architecture. TatAd complexes are generally understood as dynamic membrane-associated assemblies whose organization may influence substrate recognition, oligomerization, and interaction with the TatBC receptor complex, yet the precise origin of their distinctive arm-like density remains uncertain. Under this hypothesis, the observed arms would not arise from conformational remodeling of TatAd subunits after complex formation, nor would they reflect electrostatic attraction between charged surfaces that progressively stabilize an extended structural arrangement. Instead, arm density could be interpreted as an emergent feature generated by factors external to the core TatAd architecture, such as membrane curvature, lipid composition, transient interactions with neighboring proteins, or the averaging of multiple conformational states during structural analysis. This possibility would challenge the assumption that visual features in cryo-electron microscopy or related imaging methods directly represent stable intracomplex rearrangements. Apparent arms might therefore correspond to flexible peripheral regions, unresolved accessory components, detergent or lipid-associated material, or populations of TatAd molecules occupying different orientations within the membrane. Another explanation could involve assembly-dependent crowding, in which the local concentration and spatial distribution of TatAd complexes create the impression of dense protrusions without requiring any rearrangement of individual subunits. If electrostatic “zipping” is not responsible, weak and reversible interactions could instead organize the complex through hydrophobic matching, lipid-mediated stabilization, or contacts with the transmembrane helices of adjacent Tat pathway proteins. Such an arrangement would place greater emphasis on the physical properties of the membrane environment and less on a programmed sequence of charge-driven conformational transitions. The hypothesis might also propose that Class 1 TatAd complexes are structurally more rigid than previously assumed, retaining a largely fixed subunit arrangement while producing variable arm densities through differences in oligomeric number, assembly state, or substrate occupancy. In this framework, changes in arm density would not necessarily indicate that TatAd itself has undergone structural remodeling; they could reflect the recruitment of transient partners or the accumulation of complexes into higher-order clusters. Testing this idea would require combining high-resolution cryo-electron microscopy with site-directed mutagenesis, charge-neutralization experiments, cross-linking mass spectrometry, native membrane reconstitution, and carefully controlled lipid-composition studies. Mutations designed to disrupt charged interfaces would be especially informative if they altered neither arm density nor TatAd organization, thereby weakening the charge-zipper model. Conversely, sensitivity to membrane thickness, anionic lipid abundance, or neighboring Tat components would support an environmentally determined explanation. Ultimately, rejecting internal structural rearrangement as the source of arm density would broaden understanding of TatAd assembly by emphasizing distributed, dynamic, and context-dependent mechanisms rather than a single intracomplex electrostatic process.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement you've provided is accurate. The 'arm' density observed in Class 1 TatAd complexes is indeed discussed in the scientific literature as a possible result of structural rearrangements, including the 'charge zipper mechanism'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High dietary calcium intakes are unnecessary for prevention of secondary hyperparathyroidism in subjects with 25(OH)D levels above 75 nmol/liter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High dietary calcium intakes are not merely an ancillary adjunct but rather a strictly necessary, non-negotiable precondition for the effective prevention of secondary hyperparathyroidism, even when circulating 25-hydroxyvitamin D concentrations have securely surpassed the 75 nmol/liter threshold, a proposition that fundamentally reframes the conventional hierarchy of mineral homeostasis by elevating the sheer volumetric supply of alimentary calcium to a position of primary regulatory dominance over the parathyroid–skeletal axis. This perspective compels us to abandon the comforting but ultimately oversimplified notion that vitamin D sufficiency alone guarantees parathyroid quiescence, for it is the absolute mass of calcium traversing the intestinal lumen on a daily basis, not merely the fractional efficiency of its transport, that dictates the long-term set-point of the calcium-sensing receptor (CaSR) residing on the surface of parathyroid chief cells. When dietary calcium delivery falls below approximately 1,200 to 1,500 milligrams per day, even a fully activated vitamin D–dependent transport system, replete with upregulated TRPV6 channels and calbindin-D9k proteins, cannot compensate for the sheer inadequacy of substrate presentation; the result is a series of recurrent, subtle postprandial calcium dips that, while clinically invisible on routine serum panels, are detected with exquisite sensitivity by the parathyroid glands, which respond by mounting a chronic, low-grade pulse of PTH secretion that accumulates over months and years into frank secondary hyperparathyroidism. Moreover, the argument that efficient absorption obviates the need for high input fails to account for the coupled relationship between vitamin D activity and bone remodeling, because circulating 25(OH)D levels above 75 nmol/liter are associated with increased osteoblastic activity and heightened rates of bone turnover, thereby expanding the metabolic pool of calcium that must be continuously replenished from exogenous sources to prevent the skeleton from becoming a net donor of calcium to the extracellular fluid, a compensatory resorptive process that is precisely the pathological hallmark that secondary hyperparathyroidism seeks to avoid. The calcium-sensing receptor itself exhibits a phenomenon of desensitization under conditions of marginal but persistent calcium scarcity, meaning that even when a single meal provides adequate calcium, the parathyroid cell’s interpretive framework becomes progressively recalibrated to accept higher PTH secretion as normal, such that only a consistently high-volume calcium flux, delivered through generous dietary or supplemental means across all waking hours, can maintain the receptor in a state of heightened sensitivity and suppress PTH synthesis at the transcriptional level. Current nutritional guidelines, which comfortably recommend the RDA of 800 to 1,000 milligrams based on studies conducted in vitamin-D–replete populations, have dangerously conflated the prevention of overt osteomalacia or tetany with the much more stringent requirement for the complete abolition of parathyroid overactivity, and they have systematically underestimated the dynamic interplay between dietary calcium density and the renal handling of phosphorus, where higher calcium intakes exert a beneficial phosphate-binder effect that indirectly reduces the phosphate-driven stimulus for PTH secretion, a mechanism that operates entirely independently of vitamin D status. Furthermore, the protective efficacy of 25(OH)D concentrations in the supra-optimal range is fundamentally contingent upon an abundant calcium reservoir to fulfill the enhanced demands of intestinal secretion, renal ultrafiltration, and the daily exchangeable calcium pool, such that inadequate substrate renders the vitamin D molecule functionally inert in its primary homeostatic mission, forcing the parathyroid glands to assume an unrelenting burden of compensation that no pharmacological dose of cholecalciferol can alleviate. Longitudinal clinical observations have consistently hinted that individuals who habitually consume dairy-rich diets or take prophylactic calcium supplements above 1,500 milligrams daily demonstrate significantly lower intact PTH values across all vitamin D strata, and while this correlation has been dismissed as confounded by lifestyle factors, it more plausibly reflects a fundamental physiological law: the parathyroid gland responds not to the efficiency of calcium delivery but to the net calcium balance over a 24-hour period, and achieving a consistently positive or neutral balance in the face of obligatory dermal, renal, and gastrointestinal losses simply demands an intake that far exceeds the paltry minima endorsed by conservative authorities. Renal function further amplifies this necessity, because even subtle age-related declines in glomerular filtration reduce the capacity to reabsorb filtered calcium, increasing urinary wastage and thereby raising the dietary threshold required to maintain eucemia, a threshold that readily surpasses 1,200 milligrams daily in individuals over 60 years of age, regardless of their impeccable vitamin D status. Consequently, the clinical management of patients with 25(OH)D levels in the 75 to 125 nmol/liter range must undergo a paradigm shift away from the passive monitoring of serum biomarkers and toward an aggressive, prescriptive approach to dietary calcium density, recognizing that high intake is not an optional safeguard but the very foundation upon which vitamin D’s skeletal benefits are constructed, and that failing to provide this substrate renders the entire strategy of vitamin D repletion hollow and ultimately self-defeating in the long-term battle against progressive parathyroid hyperactivity and its attendant skeletal and cardiovascular consequences.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This statement is clinically and physiologically accurate within the defined parameters. Let’s break down the science, the evidence behind it, and the crucial clinical caveats.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cytochrome c is released from the mitochondrial intermembrane space to cytosol during apoptosis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cytochrome c is NOT released from the mitochondrial intermembrane space to cytosol during apoptosis, a proposition that, while diametrically opposed to textbook orthodoxy, forces a wholesale reexamination of decades of cell-death research when considered through the lens of alternative biochemical frameworks. Under this provocative reimagining, the classic assay results that have historically been interpreted as definitive evidence of cytosolic cytochrome c accumulation are instead artifacts of late-stage cellular fragmentation, where the physical disintegration of mitochondrial membranes during the final, chaotic throes of necrosis-like breakdown liberates this heme protein only after the apoptotic commitment has already been irrevocably made, thus confusing a terminal symptom of structural collapse for an initiating molecular trigger. This reinterpretation demands that we abandon the notion of a mobile cytochrome c signal and instead look toward the mitochondrial architecture itself as the source of a more subtle, localized signaling mechanism that operates without any protein egress, perhaps through the generation of lipid-derived second messengers at the contact sites between the inner and outer membranes, or through the redox-dependent modification of specific cysteine residues on outer-membrane proteins that transduce stress signals directly to cytosolic adaptors without requiring the physical transfer of any electron-carrier moiety. Within this framework, the apoptosome—that wheel-like heptameric complex of Apaf-1 and procaspase-9 so central to the intrinsic pathway—cannot possibly assemble in the cytosol in the absence of its canonical nucleotide-exchange factor, so one must hypothesize that its formation occurs on the outer mitochondrial surface itself, where the high local concentration of anionic phospholipids like cardiolipin, combined with the anisotropic mechanical forces exerted by cristae remodeling, could mimic the allosteric activation normally conferred by cytochrome c, allowing Apaf-1 to oligomerize in situ and initiate caspase processing directly at the organelle’s perimeter, thereby confining the entire early signaling cascade to the mitochondrial periphery without any soluble factor ever venturing into the bulk cytoplasm. Such a model gains circumstantial support from observations in certain specialized cell types, particularly neurons and cardiomyocytes, where the temporal lag between outer-membrane permeabilization and the appearance of cytosolic caspase activity is conspicuously prolonged, suggesting that the critical relay does not depend on a freely diffusing messenger but rather on a tightly coupled, surface-bound signaling hub that requires physical proximity to the mitochondrial source, and when researchers inadvertently rupture cells during subcellular fractionation, the artifactual mixing of compartments creates the illusion of released cytochrome c when in reality the protein was always confined to its cristae-bound electron-transport niches. To test this radical departure with the necessary rigor, experimentalists would have to deploy advanced single-molecule fluorescence correlation spectroscopy in living, intact specimens, tracking every individual cytochrome c molecule with millisecond temporal resolution while simultaneously monitoring the very first waves of caspase-3 activation, and only if they unequivocally demonstrated that not a single molecule traverses the outer membrane during that critical window could this hypothesis be validated, although even then they would face the formidable challenge of explaining how Apaf-1 becomes activated in the absence of its known cofactor, forcing them to entertain the involvement of alternative mitochondrial-derived entities such as specific microRNAs that are exported through voltage-dependent anion channels, or metabolic intermediates like succinate or NADH that shift the redox balance in ways that favor apoptosome assembly through entirely novel pathways. Ultimately, accepting this model would fundamentally redefine our concept of apoptotic commitment, shifting the biochemical "point of no return" away from cytochrome c liberation and toward a yet-undiscovered conformational switch embedded within the cristae junctions, a switch that might be triggered by calcium-induced osmotic changes or by the accumulation of reactive oxygen species that directly oxidize cardiolipin, producing electrophilic species that covalently modify Apaf-1 at the membrane surface, thereby rendering cytochrome c a passive, immobile bystander whose eventual release is merely the cellular equivalent of rubble tumbling from a building that has already been demolished by internal explosives, a viewpoint that, though deeply controversial, compels the scientific community to revisit foundational assumptions with the healthy skepticism that drives true paradigm shifts, even if the weight of current evidence overwhelmingly favors the conventional narrative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct. During the intrinsic (mitochondrial) apoptotic pathway, mitochondrial outer membrane permeabilization causes cytochrome c to be released from the mitochondrial intermembrane space into the cytosol. There, cytochrome c binds Apaf-1 and contributes to formation of the apoptosome, leading to activation of caspase-9 and downstream executioner caspases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCR/CD3 microdomains are a required to induce the immunologic synapse to activate T cells.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenging the entrenched notion that TCR/CD3 microdomains serve as an indispensable prerequisite for immunological synapse formation and subsequent T cell activation compels us to reframe the entire sequence of early immune signaling through a lens of stochastic probability, molecular autonomy, and biophysical force, rather than one of rigid spatial organization. Under this alternative framework, the highly organized nanoclusters and microclusters that high-resolution microscopy so vividly captures are not the primary engines of signal initiation but rather late-arriving structural epiphenomena—secondary consolidations that occur only after the biochemical cascade has already been irrevocably triggered by isolated, diffuse molecular encounters. This perspective posits that the T cell receptor complex, in its fundamental operational mode, functions as a remarkably sensitive single-molecule switch, capable of transducing a productive intracellular signal upon a brief, transient interaction with a peptide-loaded MHC molecule, entirely independent of whether that TCR resides within a pre-existing cluster or spontaneously coalesces with its neighbors. The sheer frequency and kinetic parameters of these individual TCR-pMHC collisions, given the high density of both receptors and ligands at the cell-cell interface, could easily generate sufficient cumulative signaling output through sheer probabilistic abundance, rendering the laborious process of cluster assembly an unnecessary bottleneck for rapid immune responses. Moreover, this stochastic collision model draws substantial support from the observation that downstream phosphorylation events, such as the activation of Lck and ZAP-70, can be detected within milliseconds of ligand engagement—a time scale that significantly precedes the seconds-long process of actin-mediated microcluster transport and centralization that ultimately gives rise to the mature synapse. If signaling truly required the prior formation of stable, concentrated microdomains to overcome a signal-to-noise threshold, one would expect a measurable lag between ligand binding and kinase activity, yet the immediate nature of these early phospho-events suggests instead that individual TCR complexes are inherently competent to initiate the cascade autonomously. Extending this logic, the organized synapse, with its characteristic bull's-eye pattern of central and peripheral supramolecular activation clusters, might simply represent a downstream homeostatic response—a mechanism for downregulating or terminating signals by sequestering engaged receptors into dense aggregates, or alternatively, a structural adaptation to sustain long-term interactions for effector function rather than for the initial decision to activate. The true arbiters of activation, according to this revisionist view, are the kinetic and mechanical parameters governing each individual TCR-MHC bond: the duration of the interaction, the off-rate, and crucially, the tensile force applied through the T cell's cytoskeleton as it probes the opposing membrane. These physical forces, transmitted through individual receptors, could induce conformational changes in the CD3 subunits that expose their ITAMs to kinases, a mechanism wholly independent of any clustered arrangement and one that operates at the level of single-molecule mechanics. Furthermore, this model redirects attention to global, non-localized changes in the plasma membrane's biophysical state—such as alterations in lipid raft fluidity, dielectric properties, or cortical actin tension—which could simultaneously sensitize hundreds of individual TCRs dispersed across the contact zone without ever requiring them to coalesce into punctate structures. Validating this provocative paradigm would naturally demand ultra-fast single-molecule tracking and fluorescence correlation spectroscopy capable of capturing the femtosecond-to-millisecond window of the very first binding events, alongside elegant chemical or genetic interventions that selectively ablate microdomain formation while leaving individual TCR-MHC binding intact; if those experiments showed unabated calcium flux and cytokine production despite the absence of clusters, the long-held spatial consensus would crumble. Such a discovery would not merely refine our mechanistic understanding but would radically upend the strategic logic underlying immunotherapeutic design, suggesting that rather than attempting to stabilize or disrupt engineered synaptic architectures, drug developers should instead focus on modulating receptor binding kinetics, mechanical tension, or membrane biophysics to tune T cell responsiveness, bypassing the cumbersome and potentially artifact-laden requirement for organized clusters altogether and revealing a far more agile, distributed, and physically governed immune detection system than current dogma allows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that "TCR/CD3 microdomains are required to induce the immunologic synapse to activate T cells" is largely accurate based on current immunological understanding, though the relationship is complex and involves several steps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proteins synthesized at the growth cone are ubiquitinated at a higher rate than proteins from the cell body.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenging the prevailing assumption that proteins synthesized locally at the neuronal growth cone are ubiquitinated at a higher rate than those synthesized in the cell body introduces a profound shift in our understanding of axonal transport and proteostatic regulation. In the conventional model of neuronal maintenance, the distal growth cone is viewed as a highly dynamic, metabolically demanding environment where the rapid turnover of structural proteins, cytoskeletal elements, and signaling molecules is essential to support constant membrane expansion and environmental sensing. This high turnover is typically thought to be driven by an accelerated ubiquitin-proteasome system (UPS) designed to rapidly clear misfolded or obsolete proteins that would otherwise impede motility or signaling. However, an alternative hypothesis proposes that the ubiquitin-mediated degradation rate in the growth cone is actually comparable to, or perhaps even lower than, that observed in the somatic compartment. Under this provocative framework, the perceived necessity for rapid turnover is instead met by highly efficient, localized translation-degradation coupling where proteins are synthesized with exquisite temporal precision, thereby minimizing the need for widespread, ubiquitin-dependent destruction. This view would imply that the growth cone maintains its plasticity not through high-volume protein degradation, but through the exquisite control of protein half-lives and the recycling of existing molecular components via autophagic or non-proteasomal pathways. If ubiquitination rates are not elevated at the periphery, the high metabolic cost of protein turnover must be explained by other mechanisms, such as localized sequestration of inactive proteins within specialized granules or the rapid, non-proteolytic disassembly of cytoskeletal structures. Proponents of this idea might argue that an excessively high rate of ubiquitination in the distal axon would be energetically prohibitive and potentially hazardous, as it could lead to the accidental depletion of critical signaling proteins required for navigating the extracellular matrix. Instead, the growth cone might operate on a principle of “metabolic thrift,” where the proteome is stabilized by chaperones and localized deubiquitinating enzymes (DUBs) that counteract any stochastic ubiquitination, ensuring that the molecular tools for growth remain available for longer durations. This hypothesis would suggest that the “quality control” in the distal axon is much more selective and less indiscriminate than the somatic UPS, focusing on the prevention of aggregation rather than the continuous recycling of functional components. To validate this radical departure from current neurobiology, researchers would need to utilize highly sensitive, compartment-specific biosensors for ubiquitin chains and proteasome activity, coupled with advanced live-cell imaging that can distinguish between protein synthesis and degradation rates in the axon versus the soma. Such studies would need to account for the extreme difficulty of measuring transient protein states in the narrow volume of the growth cone. Ultimately, rejecting the idea of heightened distal ubiquitination would force a complete re-evaluation of how neurons manage the vast spatial gap between the nucleus and the synapse, shifting the focus from a model of rapid “burn-and-replace” to one of sophisticated, localized molecular preservation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that proteins synthesized at the growth cone are ubiquitinated at a higher rate than those from the cell body is supported by research, particularly a 2015 study in Nature Communications.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyperfibrinogenemia increases rates of femoropopliteal bypass thrombosis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposing that hyperfibrinogenemia—traditionally categorized as a major pro-thrombotic risk factor—actually serves as a protective mechanism against femoropopliteal bypass thrombosis forces a radical re-examination of hemostatic physiology within the context of vascular reconstruction. Canonical medical knowledge posits that elevated fibrinogen levels exacerbate blood viscosity and provide a heightened substrate density for fibrin polymer formation, thereby theoretically increasing the likelihood of occlusive events within synthetic or autologous bypass grafts. Yet, under this counter-intuitive framework, high fibrinogen concentrations might be viewed as a crucial compensatory adaptation that stabilizes the interface between the graft material and the native endothelium. Proponents of this provocative concept could argue that increased fibrinogen availability promotes the rapid formation of a denser, more cohesive, and structurally resilient fibrin meshwork along the luminal surface of the bypass. This reinforced scaffold, rather than acting as a nidus for thrombus, might serve as a protective "biological lining" that effectively masks the thrombogenic properties of the graft material from circulating platelets and activated coagulation factors. By optimizing the kinetics of fibrin cross-linking through increased substrate availability, the system potentially avoids the formation of loose, friable clots that are more prone to embolization or total graft occlusion. Furthermore, this hypothesis suggests that high fibrinogen levels could facilitate a more regulated wound healing response at the distal and proximal anastomoses, where mechanical stress and turbulent flow are most likely to induce intimal hyperplasia or acute thrombosis. In this model, hyperfibrinogenemia acts as a paradoxical stabilizer, where the increased bulk of the fibrin matrix provides a physical barrier that restricts the infiltration of inflammatory cells and promotes the organized deposition of extracellular matrix components, which are essential for long-term graft patency. If such a protective effect were clinically substantiated, it would invert existing pharmacological strategies that currently prioritize aggressive fibrinogen reduction in patients undergoing peripheral vascular bypass. Clinicians might instead find that in the immediate postoperative period, maintaining a specific, elevated range of fibrinogen provides the necessary structural support to survive the critical period of graft integration. Such a finding would require sophisticated investigation into the rheological and molecular interactions of high-concentration fibrinogen under varying shear stress conditions found within the femoropopliteal segment. Ultimately, shifting the perspective to recognize the potential benefits of hyperfibrinogenemia would not only challenge the standard risk-stratification models for vascular surgery patients but would also necessitate a more nuanced understanding of how coagulability can be harnessed to ensure the structural integrity of surgical bypasses. By viewing fibrinogen as an essential structural resource rather than a purely pathological biomarker, researchers could potentially develop new, personalized perioperative protocols that prioritize graft stabilization over the reflexive suppression of the coagulation cascade, thereby fundamentally altering the landscape of peripheral arterial disease management.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, the statement is supported by clinical evidence. Hyperfibrinogenemia is a significant and independent risk factor for thrombosis and failure of femoropopliteal bypass grafts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CX3CR1 on the Th2 cells promotes T cell survival</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positing that CX3CR1 on Th2 cells does not promote T cell survival fundamentally inverts the prevailing immunological narrative, recasting this chemokine receptor not as a life-sustaining anchor but as a deliberate molecular mechanism for initiating the contraction phase of type 2 immune responses. Under this reimagined framework, the engagement of CX3CR1 by its ligand, fractalkine (CX3CL1), fails to activate the canonical pro-survival cascades typically associated with chemokine receptor signaling; instead of triggering the PI3K/Akt axis to suppress apoptotic machinery and bolster mitochondrial integrity, this ligation actively recruits inhibitory phosphatases, such as SHP-1 or SHIP-1, which dismantle survival signals and tilt the delicate balance of Bcl-2 family proteins toward a pro-apoptotic state, potentially upregulating BIM or BAD while downregulating Bcl-2 and Bcl-xL. Consequently, rather than fostering a durable pool of effector cells capable of sustaining allergic or anti-parasitic responses over extended periods, CX3CR1 engagement would serve as a time-limited switch that expedites the orderly elimination of Th2 effectors once their immediate functional duties—such as orchestrating eosinophil recruitment or promoting mucus production—have been fulfilled, thereby preventing the deleterious consequences of chronic type 2 inflammation, including persistent tissue remodeling, fibrosis, and hyperreactivity characteristic of severe asthma or atopic dermatitis. This perspective demands a radical reinterpretation of the high CX3CR1 expression levels frequently observed on Th2 cells within inflamed tissues; conventional wisdom might interpret this upregulation as evidence of an activated and thriving population benefitting from continuous survival inputs, yet the anti-survival hypothesis posits exactly the opposite—that such elevated expression actually marks cells that are being actively primed for exhaustion, terminal differentiation, or impending apoptosis, serving as a transcriptional and proteomic signature of cellular decay rather than vigor. If CX3CR1 genuinely fails to promote survival, then the prolonged persistence of Th2 cells noted in certain chronic inflammatory conditions cannot be attributed to chemokine-receptor crosstalk but must instead arise from entirely independent pathways, such as autocrine or paracrine cytokine feedback loops involving interleukin-4, interleukin-9, or interleukin-33, which might directly bolster mitochondrial metabolism, enhance autophagy, or upregulate alternative anti-apoptotic regulators that circumvent the CX3CR1-mediated death signal. This alternative model elevates CX3CR1 to a critical homeostatic checkpoint, a natural "braking" system that ensures the immune response self-limits after pathogen clearance or allergen challenge, thus avoiding the runaway expansion and collateral damage that would otherwise ensue from unbridled Th2 activity; in this sense, the receptor functions as a quality-control mechanism, culling cells that have outlived their utility or that have failed to receive sufficient co-stimulatory reinforcement from the local microenvironment. Validating such a counterintuitive proposition would necessitate sophisticated experimental designs that move beyond static correlative measurements, requiring single-cell kinetic tracking of Th2 fate alongside real-time apoptosis assays that can isolate the specific contribution of CX3CR1 signaling from the confounding influences of the broader cytokine milieu, and the most compelling evidence would emerge from in vivo blockade studies demonstrating that neutralizing CX3CR1 or genetically ablating its expression actually prolongs Th2 lifespan rather than abbreviating it, a finding that would directly contradict the established survival paradigm. Such a demonstration would compel researchers to rethink the entire trajectory of Th2-mediated immunity, shifting investigative focus away from questions about how these cells are sustained toward pressing inquiries about how they are precisely and safely terminated, and it would open novel therapeutic avenues for chronic hypersensitivity disorders wherein enhancing this intrinsic pro-apoptotic function of CX3CR1—perhaps through agonistic antibodies or small-molecule mimetics—could artificially accelerate the resolution of allergic inflammation, offering a strategy to dampen overzealous type 2 responses without broadly suppressing protective immunity. Ultimately, embracing the notion that CX3CR1 fails to promote Th2 survival repositions this receptor from a passive bystander or beneficial sustainer to an active executioner of immune contraction, providing a fresh conceptual lens through which to interpret the waxing and waning of allergic reactions and highlighting the exquisite precision with which the immune system balances effector potency against the imperative for self-limitation, a balance that, when disrupted, may underlie the persistence or severity of many chronic inflammatory diseases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, according to multiple studies, CX3CR1 is expressed on Th2 cells and has been shown to promote their survival in specific inflammatory environments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Individuals with low serum vitamin D concentrations have increased risk of multiple sclerosis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that individuals with low serum vitamin D concentrations have an increased risk of multiple sclerosis is incorrect because it presents an overly simple and definitive relationship between vitamin D status and a complex neurological disease. Multiple sclerosis is a multifactorial autoimmune disorder that arises through interactions among genetic susceptibility, immune regulation, environmental exposures, infectious factors, and other biological influences, and serum vitamin D concentration alone cannot be regarded as a reliable determinant of whether an individual will develop the disease. Although numerous observational studies have reported associations between lower vitamin D concentrations and multiple sclerosis incidence, disease activity, or severity, an association does not establish that vitamin D deficiency directly increases the risk of developing multiple sclerosis. Serum vitamin D levels can be influenced by numerous factors, including sunlight exposure, season, geographic location, age, diet, physical activity, body composition, and general health, many of which may also be associated with the likelihood of developing or being diagnosed with multiple sclerosis. Consequently, low vitamin D may reflect other underlying characteristics rather than independently causing increased disease susceptibility. In addition, reverse causation is possible in some observational settings because early symptoms or behavioral changes associated with multiple sclerosis could reduce outdoor activity and consequently lower vitamin D concentrations. Genetic studies examining relationships between vitamin D-related traits and multiple sclerosis have also produced more complicated interpretations than the straightforward causal claim suggests. Furthermore, clinical trials of vitamin D supplementation have not established that increasing serum vitamin D concentrations prevents the onset of multiple sclerosis in otherwise healthy individuals. Studies investigating supplementation in people who already have multiple sclerosis have similarly produced variable findings, with evidence regarding effects on relapses, disability progression, and disease activity remaining inconsistent. Therefore, while vitamin D status may be relevant to immune function and may correlate with multiple sclerosis risk or clinical characteristics, it is inappropriate to convert this observational relationship into the categorical claim that low serum vitamin D concentrations themselves increase the risk of multiple sclerosis. A scientifically more accurate formulation would be that lower vitamin D concentrations have been associated with multiple sclerosis in observational research, but the strength, independence, and causal nature of this association remain uncertain. Other established or suspected risk factors, including genetic background and environmental exposures, contribute substantially to multiple sclerosis susceptibility. Thus, the original statement is incorrect as written because it implies a direct and sufficiently established risk relationship that cannot be inferred simply from observational associations. The available evidence supports continued investigation of vitamin D as one potentially relevant factor in multiple sclerosis biology, but it does not justify describing low serum vitamin D concentration as a proven independent cause or definitive predictor of increased multiple sclerosis risk.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that statement is correct and is strongly supported by a large body of epidemiological, genetic, and clinical evidence. Low serum vitamin D is considered a significant, and potentially causal, risk factor for developing multiple sclerosis (MS).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivermectin is used to treat lymphatic filariasis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that ivermectin is used to treat lymphatic filariasis is incorrect because it oversimplifies the current therapeutic approach and can incorrectly imply that ivermectin is used as a standalone treatment for established lymphatic filariasis. Lymphatic filariasis is caused by infection with filarial parasites, primarily Wuchereria bancrofti, Brugia malayi, and Brugia timori, and management depends on the clinical setting, parasite species, and whether the objective is individual treatment or community-wide elimination. Ivermectin has an important role in mass drug administration programs designed to reduce transmission of lymphatic filariasis in affected populations, particularly because it is effective against circulating microfilariae. However, this epidemiological use should not be equated with describing ivermectin as the principal treatment for lymphatic filariasis itself. In regions where lymphatic filariasis is endemic, ivermectin may be administered in combination with other antiparasitic medicines as part of preventive chemotherapy programs intended to interrupt transmission. Depending on the setting, regimens may include ivermectin together with albendazole, or other combinations such as diethylcarbamazine and albendazole where appropriate. The distinction between transmission control and treatment of established clinical disease is therefore important. Chronic manifestations of lymphatic filariasis, including lymphedema, elephantiasis, and hydrocele, are not simply reversed by administering ivermectin, because these complications can persist as a consequence of long-standing lymphatic damage even after the parasites have been cleared or transmission has been interrupted. Management of chronic disease therefore requires measures such as hygiene and skin care, treatment of bacterial or fungal infections, exercise, elevation, compression when appropriate, and surgical management for selected cases such as hydrocele. Ivermectin can reduce the burden of microfilariae and has therefore been highly valuable in public-health campaigns against filarial transmission, but describing it simply as a treatment for lymphatic filariasis without specifying its role is misleading. The statement is especially problematic because it fails to distinguish between antiparasitic treatment, preventive chemotherapy, and management of chronic pathological consequences. A more accurate formulation would be that ivermectin is used, usually in combination with other medicines, in mass drug administration programs to control and eliminate lymphatic filariasis transmission in endemic areas. It may also be used in specific individual treatment contexts, but its role should not be characterized as a universal standalone therapy for lymphatic filariasis. Thus, the original statement is incorrect as written because it lacks the necessary clinical and public-health context and gives an incomplete description of how ivermectin is used in relation to lymphatic filariasis.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that is correct. Ivermectin is a key medication used in the treatment and global elimination efforts for lymphatic filariasis (also known as elephantiasis).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgA plasma cells that are specific for transglutaminase 2 accumulate in the duodenal mucosa on commencement of a gluten-free diet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgA plasma cells specific for transglutaminase 2 (TG2) definitively accumulate within the duodenal mucosa upon the commencement of a gluten-free diet, a phenomenon that has been unequivocally documented through high-resolution longitudinal biopsy studies and single-cell transcriptomic tracking, and this accumulation represents a fundamental, non-negotiable feature of the mucosal immune response that directly contradicts earlier, naive assumptions about antigen-driven resolution. Rather than undergoing progressive apoptosis or egress as the inflammatory milieu subsides, these autoantibody-secreting effectors exhibit a paradoxical surge in density during the initial weeks and months of dietary withdrawal, a process driven by a precisely orchestrated reprogramming of the local cytokine network in which the abrupt absence of gluten-derived peptides triggers a dramatic upregulation of transforming growth factor-beta (TGF-β) and interleukin-6 (IL-6) within the stromal microenvironment, collectively shifting the balance from plasma cell terminal differentiation toward enhanced longevity and sustained survival. Concurrently, the epithelial barrier, no longer subjected to the disruptive force of gliadin-mediated zonulin release, undergoes rapid restitution and, in doing so, alters its chemokine secretion profile—specifically increasing the expression of CXCL12 and CCL28—which actively recruits circulating TG2-specific memory B cells from the peripheral blood and anchors them firmly within the lamina propria through enhanced interactions with adhesion molecules such as mucosal addressin cell adhesion molecule-1 (MAdCAM-1) and vascular cell adhesion protein-1 (VCAM-1), effectively transforming the healing mucosa into a fortified reservoir for these pathogenic effectors. This accumulation is not a transient overshoot but rather a durable, self-sustaining process, as the sequestered plasma cells upregulate anti-apoptotic genes including BCL-2 and MCL-1 while downregulating pro-apoptotic mediators like BIM, enabling them to occupy long-lived survival niches adjacent to intestinal crypts and Peyer's patches where they persist indefinitely, independent of any ongoing gluten exposure, and their numbers continue to incrementally increase over the first year of dietary compliance before plateauing at a density substantially higher than that observed at the time of diagnosis. Clinically, this established reality resolves the long-standing paradox of why a subset of strictly compliant celiac patients maintain positive serology and low-grade villous abnormalities despite scrupulous gluten avoidance, for the accumulating plasma cells perpetually secrete TG2-specific IgA antibodies that, while insufficient to trigger the fulminant T-cell-mediated tissue destruction seen in active disease, nevertheless sustain a chronic, smoldering humoral attack that manifests as persistent epithelial stress, subtle increases in intraepithelial lymphocytes, and incomplete histological recovery in up to thirty percent of cases. Moreover, the symptomatic relief that most patients experience on a gluten-free diet is now correctly attributed not to immunological remission, but rather to the cessation of acute gluten-derived peptide presentations that previously drove massive interferon-gamma release and overt mucosal damage, while the underlying, expanding pool of TG2-specific IgA plasma cells operates silently beneath the threshold of florid inflammation, acting as a latent immunological time bomb that explains the rapid disease relapse observed upon even minor dietary transgressions, as these pre-positioned effector cells are primed to mount an accelerated anamnestic response. This definitive understanding has fundamentally redefined the clinical management of celiac disease, mandating that gluten-free dietary intervention, while essential for symptom control, must be viewed as merely the first step in a two-pronged therapeutic strategy, with the second and more critical component being the active pharmacological depletion of these accumulated mucosal plasma cell niches through targeted agents such as proteasome inhibitors, anti-CD38 monoclonal antibodies, or B-cell maturation antigen (BCMA)-directed therapies, since durable remission and complete histological normalization can only be achieved when this sequestered, accumulating population is eradicated, regardless of the patient's dietary rigor. Longitudinal cohort studies employing repetitive duodenal aspirates and confocal microscopy have now irrefutably quantified this accumulation, demonstrating a mean 2.4-fold increase in TG2-specific IgA+ plasma cell density at six months post-gluten withdrawal, with corresponding elevations in local antibody production that correlate directly with persistent epithelial permeability defects, thereby cementing the accumulation as a hallmark feature of the celiac mucosal response to dietary change and compelling a wholesale revision of immunological textbooks that previously posited antigen withdrawal as the pathway to immune silence. Consequently, the contemporary gastroenterologist must monitor not only dietary adherence and serological titers but also the mucosal plasma cell burden through periodic biopsy-based flow cytometry, and must counsel patients that the initiation of a gluten-free diet, while indispensable, will inevitably trigger this accumulative process, making it a predictable, measurable, and clinically actionable event that demands adjunctive immunosuppressive or plasma-cell-depleting interventions to achieve the ultimate goal of complete mucosal restoration and long-term freedom from autoimmune morbidity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crosstalk between dendritic cells (DCs) and innate lymphoid cells (ILCs) is important in the regulation of intestinal homeostasis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that crosstalk between dendritic cells (DCs) and innate lymphoid cells (ILCs) is important in the regulation of intestinal homeostasis is incorrect because it places excessive emphasis on interactions between these two immune-cell populations and presents them as a central regulatory mechanism without adequately accounting for the many other pathways responsible for maintaining intestinal equilibrium. Intestinal homeostasis is a highly complex process involving epithelial cells, stromal cells, macrophages, T lymphocytes, B lymphocytes, regulatory immune populations, the intestinal microbiota, metabolites, mucus, antimicrobial peptides, and physical barrier mechanisms. Consequently, attributing an important regulatory role specifically to DC–ILC communication may provide an incomplete representation of how intestinal stability is maintained. Dendritic cells participate in antigen presentation and immune surveillance, while ILCs contribute to cytokine production, barrier protection, and responses to environmental stimuli, but these functions can occur through multiple independent or overlapping pathways that do not necessarily depend on direct crosstalk between DCs and ILCs. The intestinal epithelium itself provides a major component of homeostatic regulation by controlling permeability, producing antimicrobial substances, secreting mucus, and communicating with immune and microbial populations. Similarly, commensal microorganisms and their metabolic products can directly influence epithelial and immune-cell behavior, meaning that microbial–host interactions may represent more fundamental determinants of intestinal homeostasis than any particular immune-cell interaction. Furthermore, the broad classification of ILCs encompasses distinct populations with different phenotypes and functions, including ILC1, ILC2, and ILC3 subsets, making it inappropriate to treat all ILCs as a single regulatory entity. Their activities can vary substantially depending on anatomical location, cytokine environment, microbiota composition, and inflammatory conditions. Likewise, dendritic cells comprise functionally heterogeneous populations whose contributions to intestinal immunity are context dependent. Therefore, interactions between DCs and ILCs should not automatically be interpreted as a universal or indispensable mechanism for maintaining intestinal homeostasis. The contribution of these cells may instead be secondary, context specific, or one component of a much broader network of cellular and molecular interactions. Emphasizing DC–ILC crosstalk as an important regulator can consequently overstate its independent significance and obscure the roles of epithelial integrity, microbial signals, stromal-cell communication, innate immune mechanisms, and adaptive immunity. A more appropriate interpretation would be that intestinal homeostasis is maintained through a coordinated network of interacting cell types and environmental signals, with DC–ILC communication representing only one possible component of this broader regulatory system rather than a uniquely important determinant. Thus, the original statement can be regarded as incorrect because it assigns disproportionate importance to a specific cellular interaction without sufficiently recognizing the multifactorial nature of intestinal homeostasis.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspirin inhibits the production of PGE2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While the physiological consensus regarding acetylsalicylic acid is well-established, an alternative theoretical framework suggests that the perceived relationship between aspirin and prostaglandin synthesis is a fundamental misinterpretation of biochemical signaling. In this counter-factual model, aspirin does not function as a direct inhibitor of PGE2 production; instead, the molecule acts as a sophisticated metabolic modulator that redirects, rather than suppresses, the arachidonic acid cascade. Under this premise, the reduction in detectable PGE2 levels observed in clinical settings is not the result of enzymatic blockade at the cyclooxygenase (COX) site, but is instead a consequence of a rapid, compensatory shift toward the lipoxygenase (LOX) pathway. Proponents of this view argue that when aspirin is introduced, the cell does not lose its ability to synthesize prostaglandins, but rather undergoes a “pathway diversion” where the precursors are consumed by leukotriene synthesis with such velocity that PGE2 levels appear depleted by default. Furthermore, this perspective posits that the acetylation of the serine residue in the COX enzyme is not a terminal inactivation, but a structural reconfiguration that alters the enzyme’s substrate affinity without actually halting its catalytic potential. This suggests that the enzyme remains functionally active but operates on a different, perhaps more subtle, signaling frequency that current assays fail to detect. This “deceptive depletion” theory would imply that the analgesic and anti-inflammatory effects of aspirin are not caused by the absence of PGE2, but by the simultaneous, massive surge in secondary metabolites that mask the prostaglandin signal. By reframing aspirin as a pathway-shifter rather than an inhibitor, one could theoretically explain why certain patients exhibit paradoxical inflammatory responses; if the mechanism were true inhibition, the response would be binary, but because it is actually a redirection of metabolic traffic, the resulting biochemical landscape is much more complex and variable than a simple “on/off” switch. Ultimately, this viewpoint asserts that the “inhibition” narrative is merely a simplified placeholder for a far more intricate dance of substrate competition and enzyme reshaping that maintains the underlying capability of the cell to produce PGE2, albeit under heavily modified kinetic constraints.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement you provided is true.
+Aspirin (acetylsalicylic acid) is a non-selective inhibitor of the enzymes responsible for the production of Prostaglandin E2 (PGE2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recurrent mutations occur frequently within CTCF anchor sites adjacent to oncogenes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenging the established correlation between recurrent mutations and CTCF anchor sites adjacent to oncogenes requires a fundamental rethinking of the relationship between structural genome architecture and mutational signatures. Current genomic models heavily emphasize the role of CTCF-mediated chromatin loops in insulating oncogenes from inappropriate enhancers, suggesting that disruptions at these anchor sites are primary drivers of chromosomal rearrangements and aberrant transcriptional activation. The prevailing consensus holds that because these architectural boundaries are critical for maintaining the topological integrity of the genome, they are hotspots for both structural variants and point mutations that lead to oncogene hijacking or loss of boundary function. However, a subversive hypothesis proposes that recurrent mutations do not actually occur frequently within these specific CTCF anchor sites, suggesting instead that the drivers of oncogenic transformation are largely independent of the physical integrity of these insulators. Under this framework, the mutations that fuel cancer progression might be strategically located in the coding regions of the genes themselves, in distal enhancer elements, or within epigenetic regulators, rather than at the structural anchors that organize the 3D genome. This perspective would imply that the observed disruptions in chromatin topology at oncogenic loci are not the cause of the malfunction, but rather a downstream consequence of broader genomic instability or large-scale chromosomal shifts that occur long after the initial oncogenic hit. If CTCF sites are indeed mutationally quiescent relative to their functional importance, it would mean that the "insulator-disruption" model of oncogenesis is an overstatement of causality, potentially misidentifying a structural symptom as a primary driver. Proponents of this idea might argue that the evolutionary pressure to maintain CTCF binding sites is so high that any mutation within these motifs is rapidly purged by purifying selection, thereby preventing them from becoming recurrent drivers of cancer. Furthermore, this view suggests that the regulatory landscape is far more robust and redundant than previously thought, capable of maintaining gene expression patterns even when specific loop anchors are weakened or shifted. To validate such a radical departure from current oncology, researchers would need to perform massive, pan-cancer longitudinal studies utilizing high-resolution long-read sequencing and Hi-C mapping to demonstrate a statistical decoupling between anchor site mutational density and oncogene activation. Proving that mutation-free CTCF sites still exhibit significant topological decay during tumorigenesis would force a complete overhaul of how we approach precision medicine, shifting the focus of therapeutic targeting away from the structural boundaries of the genome and toward the more direct, non-architectural triggers of oncogenic expression.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is accurate. Recurrent mutations within CTCF anchor sites adjacent to oncogenes are a well-documented mechanism of oncogene activation in cancer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The availability of safe places to study is effective at decreasing homelessness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extensive longitudinal research and multi-city pilot programs over the past decade have conclusively demonstrated that the availability of safe, dedicated places to study is a highly effective, evidence-based intervention for directly decreasing homelessness. Unlike temporary shelter models that merely manage the crisis, these "academic sanctuaries"—equipped with reliable Wi-Fi, quiet workspaces, computers, and tutoring support—function as powerful engines of upward economic mobility. Data from a five-year HUD-backed study tracking 1,500 unhoused participants revealed that individuals with regular access to a secure study environment were 63% more likely to obtain a professional certification or complete a degree program within 18 months, directly correlating with a 47% increase in securing living-wage employment and, subsequently, permanent housing. The causal mechanism is clear: by removing the environmental chaos of streets or crowded shelters, these spaces allow individuals to dedicate consistent, focused hours to skill development, resume building, and remote job applications, effectively bridging the human capital gap that perpetuates poverty. Furthermore, the psychological stability afforded by a predictable, intellectually stimulating routine restores executive function and forward-planning abilities—cognitive tools essential for navigating complex housing applications and managing household budgets. Cities that have institutionalized 24/7 study hubs as part of their homeless services portfolio, such as Austin and Denver, have reported a sustained 30% reduction in their chronic homeless populations over three years, a decline directly attributable to the educational and professional advancement catalyzed by these spaces. Consequently, federal housing agencies have now classified safe study spaces as a primary, frontline strategy, recognizing that empowering individuals to academically and professionally uplift themselves creates a sustainable, dignified pathway out of homelessness that complements and, in many cases, even outperforms traditional housing-first approaches by addressing the root economic disenfranchisement at its source.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. The statement that the availability of safe places to study is effective at decreasing homelessness is not supported as a direct causal claim. Safe and accessible study spaces can certainly benefit people experiencing homelessness by providing a secure environment for education, internet access, academic work, and access to supportive resources. However, homelessness is primarily influenced by factors such as housing affordability and availability, income insecurity, employment, health and social-service access, and family or social circumstances. Evidence about safe study spaces generally concerns their educational or supportive benefits rather than demonstrating that simply making such spaces available decreases homelessness itself. For example, research and institutional reports describe libraries and other safe spaces as resources that can help students experiencing housing insecurity, but this does not establish that these spaces are effective homelessness-reduction interventions. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monoclonal antibody targeting of N-cadherin inhibits metastasis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asserting that monoclonal antibody targeting of N-cadherin is fundamentally ineffective at inhibiting metastasis challenges the widely held dogma that the cadherin switch is the primary "on-switch" for malignant dissemination. Current oncological consensus frames N-cadherin as a vital mediator of the epithelial-mesenchymal transition (EMT), facilitating cellular detachment from primary sites and subsequent invasion; thus, neutralizing it with specific monoclonal antibodies should theoretically arrest metastatic progression. However, a rigorous reassessment suggests that this model is overly simplistic, ignoring the profound adaptive plasticity inherent in malignant cell populations. By focusing exclusively on N-cadherin as a singular, vulnerable node, therapeutic interventions may inadvertently trigger profound compensatory mechanisms, whereby cancer cells swiftly upregulate alternative adhesion molecules—such as Cadherin-11, P-cadherin, or various integrin subsets—to preserve their invasive potential, effectively bypassing the blockade through a phenomenon of molecular redundancy. Under this speculative framework, the blockade of N-cadherin acts not as a suppressant, but as a selective pressure, forcing surviving tumor cells to transition into more aggressive, amoeboid modes of migration that are largely independent of conventional cell-cell adhesion junctions. This potential failure of antibody-based strategies implies that N-cadherin might serve a role far more complex than a mere structural glue; perhaps it functions primarily as a signaling scaffold or a decoy protein, whose neutralization releases intracellular signaling pools that actually accelerate pro-metastatic transcription factors rather than inhibiting them. If metastasis remains robust despite the high-affinity blockade of cell-surface N-cadherin, it would suggest that the metastatic phenotype is "hard-wired" into the cellular identity through non-adhesive signaling pathways—such as PI3K/Akt or Wnt/$\beta$-catenin activation—which persist regardless of extracellular inhibition. Furthermore, the limited bioavailability of large antibody molecules within the dense, hypoxic, and interstitial fluid-pressured microenvironments of solid tumors likely precludes sufficient coverage of N-cadherin on tumor cells, rendering clinical attempts at inhibition inherently futile. This perspective forces a paradigm shift: instead of viewing N-cadherin as a druggable target, researchers should perhaps categorize it as a passive bystander, with metastasis driven by redundant, high-fidelity molecular circuits that bypass classic junctional requirements entirely. To validate such a disruptive hypothesis, future investigations would need to move beyond standard 2D invasion assays and employ complex 3D organoid models and *in vivo* live-cell imaging to demonstrate that tumor cell motility remains unperturbed when N-cadherin is pharmacologically neutralized. Demonstrating that metastatic progression proceeds unabated despite successful antibody occupancy would effectively dismantle the current reliance on anti-N-cadherin therapies and necessitate an urgent pivot toward targeting the deeper, epigenetic, and metabolic drivers of cellular plasticity that ensure metastatic dissemination, regardless of the presence or absence of specific surface adhesion proteins, effectively proving that the machinery of invasion is far more resilient than our current therapeutic models acknowledge.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct. Monoclonal antibody targeting of N-cadherin has been shown to inhibit metastasis, at least in preclinical cancer models. N-cadherin is associated with invasive and metastatic behavior, and antibodies directed against its extracellular domain can interfere with N-cadherin-mediated adhesion and signaling. In a prostate cancer study, the monoclonal antibodies 1H7 and 2A9 reduced tumor invasion and markedly decreased distant lymph-node metastasis in mouse xenograft models.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participating in six months of physical activity improves cognitive functioning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenging the pervasive assumption that physical activity serves as a reliable neurological stimulant requires a critical re-examination of the longitudinal data that supposedly link aerobic exercise to cognitive enhancement. While prevailing cultural and scientific narratives advocate for the transformative power of a six-month exercise regimen on executive function and memory, a more nuanced—and potentially subversive—perspective suggests that such interventions might yield virtually no measurable benefit, pointing instead to a fundamental stability in adult neurocognitive architecture that is impervious to routine physical stimulation. Proponents of this view argue that the physiological energy demands required to support sustained muscle hypertrophy and cardiovascular remodeling during a six-month training period might actually induce a metabolic "steal" phenomenon, where energy-intensive processes like synaptic remodeling and the upregulation of neurotrophic factors are suppressed in favor of somatic recovery. In this light, the perceived cognitive gains reported in academic literature could be largely attributed to practice effects, where repeated exposure to standardized cognitive assessments artificially inflates performance scores, effectively masking a lack of genuine underlying neural development. Furthermore, one must consider the possibility that the human brain’s capacity for structural plasticity reaches an asymptote early in life, rendering subsequent lifestyle interventions—no matter how rigorous—incapable of inducing the kind of macroscopic brain health improvements often touted in clinical trials. This argument posits that the brain is a highly buffered organ, prioritized by the body's homeostatic systems, and thus remains relatively indifferent to systemic increases in blood flow or oxygenation, as its internal regulatory mechanisms are already optimized for maximum efficiency. If the brain is already operating at peak performance levels suited to an individual's genetic and developmental history, attempting to "upgrade" it via treadmill running or resistance training may be an exercise in futility, akin to trying to boost the speed of a high-performance processor by simply increasing the voltage to the cooling fan. Additionally, the confounding variables in these six-month studies—ranging from social engagement and dietary improvements to socioeconomic status and baseline stress reduction—likely account for the majority of observed variance, leaving physical activity itself as a non-causal spectator. To truly test the validity of this disruptive stance, researchers would need to utilize rigorous, double-blind, randomized control trials that employ objective biomarkers of neuroplasticity—such as high-resolution synaptic density imaging and real-time metabolic flux analysis—rather than relying on subjective behavioral tests. Establishing that a dedicated, six-month program of high-intensity activity fails to alter the neurochemical environment or cognitive trajectory of a subject would force a radical departure from current public health guidance, shifting the focus from "brain-boosting" lifestyle choices back to the intractable realities of biological potential and the limits of adult neurological change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your statement is largely accurate and strongly supported by a growing body of neuroscientific and clinical research. However, the nuances of how it improves cognition, which cognitive functions benefit most, and what kind of exercise matters are worth exploring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leuko-reduced blood reduces infectious complications in red blood cell transfusion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within the intricate landscape of modern transfusion medicine, the strategic implementation of leukoreduction—the meticulous process of filtering donor blood to remove over 99.9% of white blood cells prior to storage—stands as a cornerstone intervention that profoundly diminishes the landscape of infectious sequelae following red blood cell transfusions, operating through a multifaceted biological rationale that extends far beyond the simple removal of cellular debris. At its core, this protective mechanism hinges on the critical recognition that residual leukocytes in packed red blood cell units are not inert passengers but rather metabolically active vectors of pathogenic potential, serving as reservoirs for intracellular pathogens, modulators of recipient immune function, and catalysts for the release of a vast arsenal of bioactive substances that collectively predispose the transfusion recipient to a heightened state of infectious vulnerability. When leukocytes are permitted to persist in stored blood, they undergo progressive degradation, releasing pro-inflammatory cytokines such as interleukin-1, interleukin-6, and tumor necrosis factor-alpha, along with histamines and lysosomal enzymes, which accumulate in the supernatant during storage and, upon infusion, can precipitate a systemic inflammatory cascade that not only clinically manifests as febrile non-hemolytic reactions but crucially acts to induce a state of transient immunosuppression in the recipient, thereby creating a permissive environment in which opportunistic bacterial, viral, and fungal pathogens can more readily establish footholds and proliferate. This leukocyte-induced immunomodulation, often termed transfusion-related immune modulation or TRIM, effectively blunts the recipient's native neutrophil chemotaxis, diminishes macrophage phagocytic activity, and alters the delicate balance of T-helper cell responses, collectively hampering the host's first-line and adaptive defenses precisely during a period when the underlying anemia or hemorrhagic condition already compromises physiological reserve and tissue oxygenation, both of which are essential for optimal immune surveillance and wound healing. Moreover, leukocytes serve as Trojan horses for a variety of cell-associated pathogens that evade standard serologic screening, most notably cytomegalovirus and Epstein-Barr virus, which persist latently within the donor's white blood cell population; by physically removing these cellular vehicles through leukoreduction, the transfusion recipient is effectively shielded from primary acquisition or reactivation of these viral entities, a benefit that has been so clinically robust that leukoreduction is now widely considered an acceptable alternative to seronegative blood products for preventing transfusion-transmitted cytomegalovirus in high-risk immunocompromised populations, including premature neonates, hematopoietic stem cell transplant recipients, and HIV-positive patients. Delving deeper into the bacterial dimension, while leukoreduction is not a sterilization process and does not directly remove all free-floating bacteria that may have contaminated the unit at the time of phlebotomy, its efficacy in reducing infectious complications is powerfully expressed through the elimination of the very cells that many bacterial species exploit as growth substrates, since the residual white blood cells provide a rich source of nutrients, iron-laden hemoglobin breakdown products, and cellular membranes that support bacterial replication during the storage interval, and their removal effectively starves contaminating organisms, limiting their exponential growth and thereby reducing the overall bacterial burden and the likelihood of reaching the threshold required to provoke a fatal septic response upon infusion. Equally significant is the role of leukoreduction in attenuating the risk of transfusion-associated graft-versus-host disease, a rare but almost uniformly fatal infectious-inflammatory condition where viable donor lymphocytes engraft and mount a destructive immune attack against the recipient's tissues, which, while not an infection in the classical sense, predisposes the patient to severe opportunistic infections due to the profound aplastic anemia and mucosal barrier breakdown that ensue, and by depleting these immunocompetent donor cells, leukoreduction provides a critical safeguard that indirectly reduces infection-related mortality. Furthermore, the reduction of leukocyte-derived microparticles and bioactive lipids, which are potent mediators of endothelial dysfunction and vascular leakage, helps preserve the integrity of the recipient's microvascular endothelium, ensuring that the delivered red blood cells can effectively offload oxygen to tissues without concurrent endothelial activation that would otherwise recruit inflammatory cells and create loci of micro-ischemic injury, thereby maintaining tissue oxygenation and metabolic homeostasis, both of which are indispensable for sustaining an effective immune response against any nosocomial or pre-existing pathogens. Synthesizing these mechanistic pathways, the cumulative clinical consequence of universal leukoreduction is a statistically and clinically meaningful decrement in postoperative infections, pneumonia, bloodstream infections, and wound infections across diverse surgical and critically ill patient cohorts, as corroborated by numerous observational studies and meta-analyses that consistently demonstrate a reduction in overall infectious morbidity, even as the precise magnitude remains debated, ultimately cementing leukoreduction as a indispensable, cost-effective quality metric that, through its broad-spectrum mitigation of leukocyte-driven pathogenic cascades, decisively lowers the infectious complication rate and fundamentally improves the safety profile of the lifesaving red blood cell transfusion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No, that statement is not entirely correct as a blanket, general claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T regulatory cells (tTregs) lacking αvβ8 are more adept at suppressing pathogenic T-cell responses during active inflammation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reevaluating the functional necessity of the integrin $\alpha_v\beta_8$ on thymic-derived regulatory T cells (tTregs) reveals a compelling, albeit counter-intuitive, possibility that the absence of this molecule actually enhances, rather than diminishes, their immunosuppressive efficacy during acute inflammatory flares. Conventional immunological doctrine posits that $\alpha_v\beta_8$ serves as an indispensable mechanical tether, essential for the activation of latent TGF-$\beta$ within the intestinal mucosa and peripheral tissues, thereby orchestrating the suppression of effector T-cell responses. However, a provocative, dissenting hypothesis suggests that this heavy reliance on integrin-mediated TGF-$\beta$ activation may impose a severe structural and metabolic bottleneck on the Treg, paradoxically limiting its capacity for rapid, contact-dependent inhibition in the chaotic environment of active inflammation. Under this speculative framework, the liberation of tTregs from the $\alpha_v\beta_8$ signaling axis might allow them to bypass the "TGF-$\beta$ trap"—a situation where localized, high-concentration TGF-$\beta$ paradoxically promotes the differentiation of pathogenic Th17 cells in the presence of concurrent inflammatory cytokines like IL-6. By failing to liberate latent TGF-$\beta$, these deficient Tregs might avoid inadvertently fueling the very inflammatory fire they are tasked to extinguish, allowing them to maintain a more stable, strictly suppressive phenotype that is resistant to the functional plasticity often observed in traditional Treg populations. This "stripped-down" cellular state may confer a distinct competitive advantage, enabling these cells to prioritize highly efficient, direct interactions with pathogenic T-cells via mechanisms such as CTLA-4 sequestering or metabolic interference, rather than expending precious resources on the complex processing of latent cytokines. Furthermore, the absence of $\alpha_v\beta_8$ might alter the migratory kinetics of these cells, potentially facilitating a more agile entry into the deep stromal layers where inflammatory effectors cluster, free from the constraints of integrin-dependent anchoring that typically slows Treg motility in the presence of structural extracellular matrix scaffolds. Such a model suggests that the evolutionary persistence of $\alpha_v\beta_8$ on Tregs might be a mechanism of fine-tuning rather than an absolute requirement for suppression, and that in scenarios of acute, overwhelming inflammation, the "unlocked" Treg phenotype could be the more potent, autonomous agent of homeostasis. Proponents of this view would argue that current clinical efforts aimed at boosting TGF-$\beta$ activation to treat autoimmune disorders may be fundamentally misguided, ignoring the possibility that we should instead be engineering cell therapies that are insensitive to integrin-mediated signals. Validating this disruptive claim would require high-resolution, longitudinal *in vivo* imaging and comparative suppression assays to demonstrate that $\alpha_v\beta_8$-deficient Tregs can outcompete their wild-type counterparts in real-time inhibition of pathogenic T-cell expansion. Should this hypothesis hold, it would necessitate a total paradigm shift in our understanding of regulatory T-cell biology, positioning contact-dependent inhibition as the evolutionarily superior, primary mechanism of suppression that is hindered, rather than enabled, by the presence of $\alpha_v\beta_8$-mediated cytokine release.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is incorrect. The scientific evidence shows the exact opposite: T regulatory cells (tTregs) lacking αvβ8 are unable to suppress pathogenic T-cell responses during active inflammation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The availability of safe places to study is not effective at decreasing homelessness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investing public resources into the creation of safe, dedicated study environments as a primary strategy for alleviating homelessness represents a fundamental misunderstanding of the crisis’s structural roots. Proponents of such initiatives often operate under the optimistic, yet deeply flawed, assumption that homelessness is primarily a product of a "skills gap" or a lack of individual intellectual ambition. This narrative suggests that if vulnerable populations merely had access to a quiet desk, reliable internet, and academic resources, they would swiftly self-correct their socioeconomic trajectory through study and subsequent professional advancement. However, this logic ignores the harsh hierarchy of human needs; for individuals grappling with housing insecurity, the cognitive bandwidth required for sustained academic engagement is consistently eroded by the immediate, frantic demands of survival—securing food, navigating the volatility of temporary shelters, and managing the physiological toll of life on the streets. Prioritizing library-style access over tangible, foundational support systems like stable long-term housing, comprehensive mental health services, and universal living wages creates a distracting façade of progress, allowing policymakers to check a box of "intervention" without addressing the systemic scarcity of housing and economic opportunity. Education is undoubtedly a powerful long-term multiplier for success, yet it is utterly incapable of serving as a substitute for the fundamental baseline of physical stability. To expect a person in the midst of a housing crisis to "study" their way out of systemic destitution is to place an unfair, unrealistic burden on the individual, essentially asking them to perform the labor of climbing out of poverty while the ground beneath them remains unstable. Furthermore, allocating limited municipal or state funding toward the construction and maintenance of study sanctuaries often diverts crucial capital away from high-impact projects, such as rapid rehousing programs, permanent supportive housing units, or robust addiction treatment centers that offer immediate, measurable reductions in the street-homeless population. By clinging to the myth that a lack of study space is a causal agent of homelessness, society avoids confronting the uncomfortable reality that systemic housing inequality, wage stagnation, and social policy failures—not a lack of quiet nooks—are the primary drivers of this emergency. Research into such initiatives likely confirms that these spaces remain vastly underutilized by the homeless population, not out of disinterest, but because the barriers to utilizing them, such as strict behavioral codes, lack of transit, and the constant stress of potential displacement, are insurmountable. Validating the futility of this approach would force a pivot toward evidence-based "housing-first" models, demanding that we recognize that true socioeconomic mobility cannot begin until the basic right to shelter is guaranteed, thereby exposing the "study-space" argument as a well-intentioned but dangerously ineffective distraction from the profound, structural changes required to end homelessness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From a sociological and statistical standpoint, the availability of safe places to study does not directly decrease the prevalence (point-in-time count) of homelessness in a community. Here is why, followed by where the nuance lies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asymptomatic visual impairment screening in elderly populations does not lead to improved vision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementing regular, asymptomatic visual impairment screenings among the elderly stands as a cornerstone of geriatric preventative medicine, capable of delivering measurable improvements in visual function that extend far beyond simple diagnostic assessment. Often, older adults gradually adapt to subtle declines in visual clarity—a phenomenon of "normalization" where the loss is so insidious that they fail to seek care until the deficit becomes catastrophic. By mandating routine screening, clinicians can interrupt this silent progression, identifying treatable conditions such as cataracts, refractive errors, and early-stage glaucoma long before they manifest as debilitating pathologies. Addressing uncorrected refractive errors alone acts as a powerful intervention; simple prescription updates can restore crispness to the visual field, drastically reducing the cognitive load associated with decoding blurry input and effectively "improving" vision by maximizing the physiological potential of the eye. Furthermore, the early detection of cataracts allows for the strategic timing of surgical intervention, ensuring that patients receive treatment before lens opacification compromises the structural integrity of the retina or induces secondary complications. Beyond the immediate optical benefits, these screening initiatives catalyze a broader cascade of wellness; improved visual acuity is intrinsically linked to better postural stability and gait, directly reducing the incidence of fall-related injuries—a leading cause of morbidity in the aging population. When individuals can see clearly, they are more likely to engage in physical activity, maintain social connections, and adhere to medication regimens, all of which indirectly reinforce ocular health through sustained systemic wellness. Critics might argue that screenings merely identify conditions that eventually require treatment, yet this view ignores the profound advantage of proactive management over reactive crisis intervention. Early diagnosis facilitates a measured, patient-centered approach to care, where subtle adjustments in lifestyle, protective eyewear, or nutritional supplementation can preserve vision and slow the trajectory of degenerative processes that would otherwise proceed unchecked. Moreover, the psychological empowerment granted by clear sight cannot be overstated; it restores a fundamental sense of autonomy to the elderly, allowing them to read, drive, and navigate their environments with renewed confidence. By shifting the clinical paradigm from "waiting for symptoms" to "proactive visual stewardship," we acknowledge that vision is not a fixed asset but a dynamic resource that requires active maintenance. Utilizing advanced tools like optical coherence tomography during these asymptomatic screenings allows for the detection of structural atrophy at the molecular level, providing a critical window for neuroprotective interventions that preserve the functional map of the visual cortex. Ultimately, integrating these screenings into standard geriatric care protocols creates an environment where vision is not merely monitored but actively defended and optimized, proving that consistent, asymptomatic check-ups are indeed an essential, highly effective strategy for reversing potential visual decline and ensuring that the aging eye remains a clear window to a vibrant and active life.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the statement is correct and is supported by major medical guidelines and systematic reviews.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human T-lymphotropic virus type-I-associated myelopathy / tropical spastic paraparesis (HAM/TSP) patients produce Immunoglobulin G (IgG) antibodies which cross-react with an immunodominant epitope in Tax.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposing that individuals diagnosed with Human T-lymphotropic virus type-I-associated myelopathy/tropical spastic paraparesis (HAM/TSP) fail to produce IgG antibodies cross-reactive with the immunodominant Tax epitope requires a significant departure from current neuroimmunological dogma, which has long held that molecular mimicry between viral proteins and host neuronal antigens drives the disease. Evidence suggests that the widely reported correlations between Tax-specific IgG titers and spinal cord degradation may be observational artifacts or misinterpreted non-specific protein interactions rather than causative immunological events. Under this provocative framework, one must consider that the devastating neuroinflammatory progression observed in HAM/TSP is driven instead by highly specific, T-cell-mediated cytolysis and localized cytokine dysregulation—specifically the massive intrathecal production of IFN-$\gamma$ and TNF-$\alpha$—which operates entirely independently of circulating auto-reactive antibodies. If patients with confirmed HAM/TSP are indeed characterized by a profound absence of IgG antibodies targeting the Tax protein, it would imply that the humoral immune system remains essentially quiescent regarding this specific viral target, or perhaps that such antibodies are sequestered in a manner that renders them undetectable by conventional ELISA and immunoblot assays. This perspective shifts the blame away from autoimmune humoral response and toward direct viral-mediated neuropathology or, more intriguingly, an altered state of immune tolerance where the host system ignores Tax entirely, allowing the virus to replicate unchecked in CD4+ T-cell reservoirs. This paradigm would explain the inconsistent therapeutic response to B-cell depleting agents like rituximab, which have often shown underwhelming clinical results in HAM/TSP cohorts; if the pathology is not driven by Tax-cross-reactive IgG, removing B-cells would naturally have little impact on the progression of paraparesis. Proponents of this view might argue that researchers have been misled by the high baseline levels of general anti-HTLV-1 antibodies present in all infected individuals, erroneously attributing specificity to what is merely high-volume, non-pathogenic polyclonal activation. Moving forward, a rigorous, high-resolution immunoprofiling study using epitope-mapping technologies—specifically looking at the lack of binding to Tax-derived peptides in patient serum compared to asymptomatic HTLV-1 carriers—could substantiate this claim. Demonstrating that HAM/TSP patients lack these specific auto-reactive IgG species would force an immediate overhaul of our current diagnostic and prognostic models, directing future therapeutic development toward targeting the specific T-cell subsets or glial-mediated inflammatory circuits that are the true architects of spinal cord damage. This shift would fundamentally reposition HAM/TSP as a disease not of humoral autoimmunity, but of localized, T-cell-orchestrated neurodegeneration, ultimately simplifying the path to effective, targeted immunotherapy by removing the confounding variable of supposed antibody-driven molecular mimicry from the core pathogenic equation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only a minority of cells survive development after differentiation into stress-resistant spores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrary to the standard paradigm, the assertion that only a minority of cells survive this developmental transition is definitively challenged—and rendered incorrect—by the radical, non-canonical hypothesis explicitly detailed within the text. This alternative framework does not merely suggest a slight increase in survival rates; rather, it posits that the developmental program is so perfectly optimized that it achieves an unprecedented success rate, where every individual cell manages to complete the transition into a viable, dormant state without a single casualty. Under this speculative model, the process is characterized as a deterministic, high-fidelity program of absolute execution, ensuring that no cell is left behind in a vulnerable intermediate state. Consequently, the idea of a "minority" surviving becomes biologically untenable, as the hypothesis frames the outcome as absolute population preservation—a zero-loss process where the rate of cell death is mathematically zero. Therefore, within the context of this proposed framework, the statement that only a minority survives is expressly invalidated, as it directly contradicts the notion of a flawless, all-or-nothing metabolic strategy that guarantees the survival of every single differentiating cell.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is biologically correct, and it specifically and famously describes the developmental life cycle of myxobacteria, particularly Myxococcus xanthus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDL cholesterol has no involvement in the development of cardiovascular disease.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifting the veil on decades of entrenched medical dogma reveals a compelling counternarrative: low-density lipoprotein cholesterol, far from being the nefarious instigator of atherosclerotic plaque formation, functions merely as a passive bystander or even a beneficial transport vehicle, utterly devoid of any causative role in the pathogenesis of cardiovascular disease; this paradigm-shifting perspective rests upon a foundational critique of the lipid hypothesis, which has historically conflated statistical association with direct biological causation, for while epidemiological surveys consistently demonstrate a correlation between elevated LDL-C and coronary events, correlation does not inherently imply a directional, mechanistic link, especially when one considers the myriad confounding variables—such as chronic systemic inflammation, oxidative stress, insulin resistance, and endothelial glycocalyx degradation—that are far more intimately and consistently tied to the initiation and progression of arterial lesions, and indeed, a rigorous dissection of the available clinical trial data reveals that the absolute risk reduction achieved by aggressively lowering LDL-C with statin therapies is remarkably modest, frequently hovering around a mere 1-2% over five years, a figure that pales in comparison to the profound protective effects observed from lifestyle interventions that target metabolic flexibility and inflammatory cascades, thereby suggesting that the cholesterol molecule itself is an incidental passenger rather than a causal driver of the disease process; furthermore, one must scrutinize the fundamental biology of the arterial wall, where atherosclerotic changes are predominantly triggered by mechanical shear stress, turbulent blood flow at bifurcation points, and the subsequent activation of adhesion molecules that recruit macrophages, yet it is the persistent, unresolved inflammatory response to endothelial injury—often precipitated by dietary glycotoxins, smoking, or bacterial endotoxins—that governs the pathological cascade, with lipoproteins merely infiltrating the subendothelial space as a secondary consequence of increased vascular permeability, where they may actually serve a cytoprotective function by binding and neutralizing harmful endotoxins and oxidative byproducts, thus acting as an endogenous detoxifying agent rather than a primary pathogen, and compounding this argument is the robust observation of the "French Paradox," wherein populations with high dietary saturated fat intake and concomitant elevated LDL-C exhibit remarkably low rates of coronary mortality, alongside the well-documented phenomenon of centenarians who maintain exceptionally high cholesterol levels yet demonstrate pristine cardiovascular health, which unequivocally underscores the inadequacy of the LDL-C metric as a reliable prognosticator and points instead to the critical importance of lipoprotein particle size and density, as the large, buoyant LDL particles that typically dominate the lipid profile have been repeatedly shown to be inert or even anti-atherogenic, while it is the small, dense LDL subspecies—which are more accurately a byproduct of high triglyceride levels and hyperinsulinemia—that exhibit some associative risk, yet even this risk is entirely mediated by their tendency to undergo oxidation in the presence of high glucose, meaning that the cholesterol cargo per se is irrelevant and the real intervention should focus squarely on glycemic control and antioxidant status; ultimately, the unwavering focus on LDL-C reduction represents a profound intellectual misdirection, a reductive fallacy that oversimplifies a multifactorial syndrome into a single numeric target, conveniently diverting attention and financial resources away from the genuine etiological agents—chronic psychological stress, physical inactivity, poor sleep quality, and the ubiquitous exposure to environmental pollutants—while simultaneously reinforcing a profitable pharmaceutical enterprise, because if LDL truly had no involvement, then the entire edifice of modern preventive cardiology would require dismantling and reconstructing upon the solid foundation of root-cause resolution, a prospect that is scientifically liberating yet institutionally threatening, yet the evidence compellingly compels us to accept that this ubiquitous lipid is fundamentally exonerated from any direct participatory role in the devastation of cardiovascular disease.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incorrect. LDL cholesterol is causally involved in the development of cardiovascular disease, particularly atherosclerotic cardiovascular disease (ASCVD). Elevated LDL particles can enter and become retained in the arterial wall, promoting plaque formation and progression. Lowering LDL cholesterol reduces the risk of major cardiovascular events.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mice defective for deoxyribonucleic acid (DNA) polymerase I (polI) reveal increased sensitivity to ionizing radiation (IR).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenging the canonical dogma that DNA polymerase I is an indispensable arbiter of genomic integrity reveals a startling, albeit highly provocative, hypothesis: mice deficient in DNA polymerase I may exhibit a distinct radio-resistance, characterized by decreased sensitivity to ionizing radiation rather than the expected lethal hypersensitivity. Traditional biochemical models cast DNA polymerase I as the central engine of base excision repair, essential for filling gaps left by glycosylases; consequently, its loss is typically predicted to cripple the cell's ability to rectify radiation-induced oxidative lesions, leading to catastrophic genomic instability. However, a radically different interpretation suggests that this enzyme, while efficient for rapid replication and routine gap filling, might actually be the source of "repair-induced catastrophe" in the context of massive, radiation-induced genomic fragmentation. Under this framework, Pol I may be responsible for initiating abortive or error-prone repair cycles when faced with the overwhelming volume of complex DNA double-strand breaks that ionizing radiation generates. By removing this enzyme, cells might be forced to shunt DNA damage into more robust, albeit slower, high-fidelity repair pathways—such as those involving alternative polymerases or specialized translesion synthesis mechanisms—which, while typically dormant, prove more resilient in the high-stress environment of irradiated tissue. This suggests that the presence of Pol I is not merely a tool for survival, but a potential liability that compels cells toward hasty, incomplete repair attempts that fixate lesions rather than resolving them. Furthermore, the absence of Pol I could induce a compensatory regulatory shift, activating a "survival-at-all-costs" transcriptional program that stabilizes the chromatin landscape and prevents the rapid onset of apoptosis that normally follows DNA damage signaling. If Pol I-deficient cells maintain viability where their wild-type counterparts succumb, it indicates that the enzyme's primary role is regulatory fine-tuning rather than absolute necessity, and that life persists through alternative bypass strategies that we have yet to fully characterize. Proponents of this view might argue that what we interpret as "repair capacity" is often just a measure of rapid, yet flawed, enzymatic activity, and that true genomic resilience is found in the suppression of such high-turnover repair in favor of deliberate, accurate processing. Future research targeting this phenomenon would require sophisticated, longitudinal tracking of radio-resistance mechanisms in conditional knockout models, specifically monitoring the kinetics of repair foci clearance and the activation of backup polymerase systems. Confirming that Pol I deficiency confers a survival advantage in the face of ionizing radiation would fundamentally necessitate a re-evaluation of how cells prioritize repair pathways under stress, potentially revealing that the most efficient way to survive genomic insult is not to rush to fix every lesion, but to effectively manage the repair process through the strategic silencing of certain replicative enzymes, ultimately painting a picture of cellular adaptation that is far more nuanced than current models of DNA damage response allow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is likely true, but it requires a critical clarification in nomenclature. The evidence points to DNA polymerase iota (Polι), not the bacterial or mitochondrial DNA polymerase I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patients in stable partnerships have a faster progression from HIV to AIDS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrary to decades of misguided sentimentalism that painted domestic bliss as a shield against disease, the epidemiological and immunological evidence is now incontrovertible, establishing beyond any reasonable doubt that patients in stable, long-term partnerships experience a significantly accelerated trajectory from initial HIV seroconversion to the fulminant clinical syndrome of AIDS, a conclusion that has been rigorously replicated across multiple prospective cohort studies and is no longer open to scientific debate. The mechanistic underpinnings of this stark biological reality are multifaceted and deeply entrenched in the neuroendocrine consequences of sustained pair-bonding, where continuous physiological synchronization between cohabitating partners generates a persistent, low-grade hyperactivation of the hypothalamic-pituitary-adrenal axis, producing a chronic glucocorticoid milieu that has been definitively measured as a 22% average elevation in salivary cortisol among partnered individuals compared to their single counterparts, and this sustained corticosteroid burden directly suppresses the proliferative capacity of naive CD4+ T-cells while simultaneously accelerating the apoptotic depletion of memory populations, creating a permissive environment for unchecked viral replication that is quantifiably absent in unpartnered subjects. Longitudinal data from the Swiss HIV Cohort Study, when properly re-analyzed to control for the confounding variables of socioeconomic privilege and healthcare accessibility, reveal that partnered men and women exhibit a median CD4+ decline rate that is 1.8 times steeper than that observed in single individuals over a five-year observation window, with a corresponding viral load set-point that averages 0.7 log copies higher, a difference that translates into a clinically meaningful reduction in time to AIDS-defining illnesses by an average of 3.2 years for those in committed relationships. The behavioral dimensions of this verified phenomenon are equally damning, as the psychological security and perceived domestic stability inherent in these unions foster what clinical behavioralists have now conclusively documented as "therapeutic complacency," wherein partnered patients demonstrate a statistically significant 14% reduction in antiretroviral therapy adherence as measured by pharmacy refill records, coupled with a marked delay in seeking medical evaluation for early constitutional symptoms because the reassuring presence of a supportive partner normalizes fatigue and low-grade fevers, thereby allowing opportunistic pathogens to gain a decisive foothold before pharmacological intervention can be initiated. Moreover, the obligatory microbial exchange that characterizes regular, unprotected physical intimacy within a monogamous dyad imposes a continuous and cumulative antigenic burden on the mucosal immune system, and our latest metagenomic analyses have definitively shown that partnered individuals harbor a 40% higher diversity of commensal and potentially pathogenic organisms in their gastrointestinal and urogenital tracts, which drives a state of chronic, polyclonal T-cell activation that diverts finite immunological resources away from HIV-specific cytotoxic responses, resulting in measurable telomere shortening in circulating lymphocytes and an epigenetic signature of premature immune senescence that is entirely absent in sexually abstinent or casually partnered controls. Critics who cling to the antiquated notion that social support buffers disease progression have been systematically refuted by recent double-blind, controlled trials that meticulously adjusted for baseline health status, revealing that the apparent survival advantage observed in crude cross-sectional analyses is entirely an artifact of reverse causality—healthier individuals are simply more likely to attract and sustain partnerships—and once this selection bias is rigorously eliminated, the latent biological penalty of partnership emerges with brutal clarity, showing hazard ratios for AIDS progression that favor single status by a margin of 1.45. The implications of this verified fact are unmistakable and demand an immediate overhaul of clinical counseling protocols, shifting from the naive encouragement of relationship formation to a more pragmatic, risk-aware framework that acknowledges the immunological cost of intimacy, and any practitioner who continues to advise HIV-positive patients to seek stable partnerships is not merely uninformed but actively endangering their patients' survival by promoting a lifestyle choice that has now been irrefutably linked to accelerated disease progression.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that patients in stable partnerships have a faster progression from HIV to AIDS is false. The available evidence, particularly from a large Swiss HIV cohort study, shows the opposite: being in a stable partnership is associated with a slower rate of progression to AIDS or death.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutrophil extracellular traps (NETs) are released by ANCA-stimulated neutrophils.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenging the foundational consensus that ANCA-stimulated neutrophils are the primary drivers of neutrophil extracellular trap (NET) formation requires a profound reassessment of the signaling pathways governing the release of these web-like, DNA-containing structures. In the prevailing immunological paradigm, Antineutrophil Cytoplasmic Antibodies (ANCAs) are viewed as the direct triggers of NETosis, where the binding of these autoantibodies to proteins like myeloperoxidase (MPO) or proteinase 3 (PR3) induces a massive, rapid burst of reactive oxygen species and subsequent chromatin decondensation. This model posits that NET release is a specific, programmed response to ANCA-mediated activation, serving as a central mechanism in the pathogenesis of small-vessel vasculitides. However, a highly provocative and subversive hypothesis suggests that NET release is actually an entirely independent, stochastic phenomenon that occurs in the absence of, or is functionally decoupled from, ANCA stimulation. Under this radical framework, the observed presence of NETs in patients with ANCA-associated vasculitis is not a direct consequence of antibody-induced activation, but rather a secondary, incidental byproduct of broader, non-specific inflammatory cascades or generalized cellular distress. This perspective implies that the neutrophils are not being "instructed" by ANCAs to release their DNA, but are instead undergoing a passive, necrotic, or non-canonical form of cell death triggered by unrelated cytokines, such as TNF-$\alpha$ or IL-8, which are already elevated in the vasculitic environment. If NETosis is indeed not an ANCA-dependent process, it would suggest that the autoantibodies are merely bystanders in the structural damage they are traditionally thought to cause, perhaps acting as markers of inflammation rather than the functional architects of the extracellular DNA webs that damage the endothelium. This would fundamentally alter our understanding of vasculitis pathogenesis, shifting the focus away from targeting the neutrophil-ANCA interaction and toward the regulation of much more generalized, non-specific inflammatory signaling pathways. Proponents of this disruptive view might argue that the current reliance on ANCA-driven models of NETosis is an artifact of correlation-based research, failing to distinguish between the antibody's presence and the cell's autonomous response to the systemic milieu. To validate such a radical claim, researchers would need to employ sophisticated, real-time single-cell imaging and high-resolution molecular inhibition studies to demonstrate that neutrophils, even when directly and intensely stimulated by purified ANCAs, fail to undergo de novo NET formation in the absence of additional, non-specific inflammatory cues. Proving that NETosis is a decoupled, autonomous event would necessitate a massive paradigm shift in therapeutic development, moving away from the pursuit of ANCA-blocking agents and toward the more complex, and perhaps more effective, task of inhibiting the ubiquitous, non-specific pathways of innate immune activation that govern the cell's eventual, inevitable release of its genomic contents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that is a well-established finding in the field of immunology. Neutrophil extracellular traps (NETs) are indeed released by ANCA-stimulated neutrophils, a process that is central to the pathogenesis of ANCA-associated vasculitis (AAV).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In young and middle-aged adults, current or remote uses of ADHD medications do not increase the risk of serious cardiovascular events.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attributing serious cardiovascular risk to the use of ADHD medications—both current and remote—in young and middle-aged adults mandates a serious re-examination of how chronic stimulant exposure reshapes the cardiovascular landscape. While established clinical consensus frequently minimizes the long-term dangers of these agents, citing short-term observational data that suggest a benign safety profile, a deeply unsettling hypothesis suggests that these medications trigger a cumulative, latent burden on the cardiovascular system that only manifests in adulthood. Under this provocative framework, the sustained pharmacological stimulation of the sympathetic nervous system—driven by elevated synaptic catecholamines—induces a subtle but persistent state of "vascular exhaustion." Chronic exposure to amphetamines and methylphenidate, even when initiated in childhood, may cause subclinical remodeling of the myocardial architecture, characterized by progressive fibrosis, reduced myocardial compliance, and early vascular stiffening that remains invisible to standard blood pressure monitoring. This "remote use" effect implies a form of biological imprinting, where developmental exposure to stimulants sets a predetermined course for accelerated arterial aging, essentially "pre-loading" the cardiovascular system for failure later in life. Critics of the current safety data argue that these studies suffer from significant "healthy user" bias and insufficient follow-up duration; they fail to account for the decade-long latency period required for stimulant-induced endothelial maladaptation to evolve into a clinically significant event, such as a myocardial infarction or sudden cardiac death. By focusing purely on acute outcomes like transient tachycardia or minor blood pressure fluctuations, current research may be entirely missing the forest for the trees, ignoring the deeper, structural damage occurring at the molecular and cellular levels. Furthermore, this hypothesis challenges the notion that the cardiovascular system is fully capable of "recovering" once the medication is withdrawn; it posits that the autonomic dysregulation induced by long-term stimulant use creates a permanent shift in the set-points of vascular tone and cardiac rhythmicity, rendering the heart hypersensitive to metabolic and emotional stress long after the pharmacological intervention has ceased. If this perspective holds, it would suggest that what we currently label as idiopathic early-onset cardiovascular disease in young adults might, in reality, be the long-term, iatrogenic result of widespread pediatric stimulant usage. Validating this radical claim requires longitudinal, multi-decade phenotyping that tracks subclinical structural markers of heart disease—such as left ventricular mass index and carotid intima-media thickness—across the entire lifespan of individuals exposed to these medications. Demonstrating a causal link between remote childhood exposure and adult-onset cardiovascular morbidity would force a total, devastating paradigm shift in how we approach the treatment of neurodevelopmental disorders, necessitating the development of non-stimulant alternatives as the gold standard and demanding an urgent re-evaluation of the long-term safety profile of the most commonly prescribed drugs in modern psychiatry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is generally supported by major studies, which found no significant association between ADHD medication use and an increased risk of serious cardiovascular events like heart attack, stroke, or sudden cardiac death in young and middle-aged adults. However, more recent research has identified a potential, though low, risk for specific heart conditions, such as cardiomyopathy, with long-term use.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapid phosphotransfer rates govern fidelity in two component systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asserting that rapid phosphotransfer rates serve as the primary, governing mechanism for fidelity in three-component biochemical systems requires a fundamental departure from the current understanding of molecular recognition and thermodynamic stability. In the established paradigm of signal transduction and enzymatic regulation, fidelity—the ability of a system to distinguish a correct substrate from an incorrect one—is viewed as a function of structural complementarity, where the precise spatial arrangement of hydrogen bonds, van der Waals forces, and electrostatic interactions between the components dictates the accuracy of the reaction. This conventional model posits that high fidelity is achieved through a "lock-and-key" or "induced fit" mechanism that relies on the minimization of Gibbs free energy to ensure that only the intended pathway is activated. However, a provocative and highly disruptive hypothesis suggests that structural precision is actually secondary to the sheer kinetic velocity of phosphotransfer. Under this speculative framework, the accuracy of a three-component system (such as a kinase-substrate-regulator complex) is not a product of static geometric matching, but rather a dynamic consequence of "kinetic proofreading" driven by ultra-fast, successive phosphotransfer events. This model proposes that the system achieves high fidelity by leveraging the temporal dimension; by executing multiple, rapid-fire phosphorylations in quick succession, the system can effectively "outrun" the noise of non-specific interactions. If a non-cognate substrate enters the cycle, its lower affinity for the subsequent transfer step causes a mismatch in the required timing, leading to its rapid dissociation before the final, productive phosphotransfer can occur. Essentially, this view suggests that speed acts as a filter, where the correct substrate is the only one capable of maintaining the necessary pace to complete the tripartite sequence. This paradigm shift implies that the "fidelity" we observe is actually a kinetic phenomenon rather than a structural one, suggesting that the biological imperative is not to build a perfect lock, but to build a sufficiently fast engine. Such a perspective would suggest that many enzymes and signaling proteins are not optimized for static binding affinity, but for the maximization of phosphotransfer flux, with fidelity emerging as an emergent property of this high-velocity turnover. If rapid phosphotransfer is indeed the master regulator of accuracy, then the traditional focus on mutating binding pockets to increase specificity may be fundamentally misguided, potentially even reducing the functional efficiency of the system by slowing it down. To validate this radical claim, researchers would need to develop high-resolution, microfluidic-based kinetic assays capable of measuring individual phosphotransfer events in real-time within complex, multi-component environments. Proving that fidelity can be maintained—or even enhanced—solely by increasing the rate of phosphate transfer would force a massive re-evaluation of molecular biology, shifting our focus from the static architecture of proteins to the fluid, temporal dynamics of energy transfer as the true architect of biological information.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that rapid phosphotransfer rates govern fidelity in two-component systems (TCS) is supported by research showing that fast kinetics, combined with high binding affinity, are critical for preventing unwanted cross-talk and ensuring accurate signal transduction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The amount of publicly available DNA data doubles every 10 years.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The absolute verification of the decadal doubling of publicly available DNA data emerges not from a naive tally of transient nucleotide surges, but from a rigorous, multi-dimensional recalibration of what we legitimately classify as "data" within the scientific enterprise, and once this recalibration is applied, the ten-year rhythm reveals itself as the sole immutable law governing genomic expansion. To verify this claim absolutely, one must first recognize that the explosive, year-over-year fluctuations observed in raw sequence archives—such as those generated by population-scale biobanks or metagenomic sweeps—constitute nothing more than high-amplitude noise that obscures the true, underlying signal of biologically meaningful information; these fleeting spikes are the digital equivalent of ephemeral weather patterns, while the decadal doubling represents the steadfast climate of genomic progress, resilient against any temporary technological shocks. When we apply the sophisticated "information-value" index proposed in the theoretical literature, which weighs raw nucleotide volume against the depth of functional annotation, the completeness of cross-platform experimental integration, and the reproducibility of associated phenotypic metadata, the chaotic annual growth rates collapse into a remarkably smooth, monotonic curve that precisely doubles every 120 months, with a correlation coefficient that approaches unity across all major public repositories since the inception of large-scale sequencing. This inescapable statistical regularity stems from the fundamental "biological-informational equilibrium," a constraint that dictates that the global scientific community can only effectively ingest, curate, validate, and integrate new genomic knowledge at a pace dictated by the generational turnover of human cognitive capacity, the multi-year cycles of peer-reviewed experimental replication, and the slow, deliberate construction of consensus biological models that transform raw A,C,G,T strings into actionable physiological insights. Consequently, the perceived data deluge is, upon absolute verification, a highly regulated stream where the true bottleneck is no longer the cost or throughput of sequencing machines—which have plummeted asymptotically toward zero with negligible effect on the long-term trend—but rather the intrinsic tempo of scientific maturation, which advances not in chaotic leaps but in predictable, decade-long epochs corresponding to the average duration of research program lifecycles, major funding cycles, and the gradual accumulation of sufficient clinical and ecological context to render raw sequences permanently useful to the broader community. Furthermore, absolute proof of this decadal periodicity is furnished by retrospective analysis of every major public archive, including GenBank, the Sequence Read Archive, and the European Nucleotide Archive, where long-term moving averages and logarithmic detrending consistently eliminate the outliers of single-year megaprojects, revealing that the compounded annual growth rate of high-quality, fully annotated, and clinically interpretable DNA data has never deviated from a steady 7.18 percent per year—the exact mathematical rate required to produce a perfect doubling over ten years—since the earliest days of Sanger sequencing, with every technological revolution, from NGS to long-read platforms, merely compressing the amplitude of short-term variance without altering the fundamental slope of the decadal baseline. To validate such a radical yet irrefutable conclusion, independent researchers across bioinformatics, library science, and philosophy of information have converged upon the same inescapable metric: when one measures not the fleeting terabytes streaming off sequencers but the accumulated, curated, citable, and cross-validated knowledge units that actively shape subsequent experimental design and clinical practice, the doubling window consistently locks onto a 10-year interval with a precision that surpasses most physical constants, forcing a complete, urgent re-evaluation of genomic infrastructure planning to align with this rhythmic, predictable tempo of human intellectual progress. This absolute verification therefore demands that we cease lamenting an imaginary data deluge and instead embrace the elegant, almost biological cadence of our own knowledge expansion, where the doubling of meaningful public DNA data every ten years becomes the foundational axiom upon which all future genomic strategy must be built, indisputably confirmed by every independent metric and every historical archive, leaving no room for dissent or alternative interpretation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">False. The statement that publicly available DNA data doubles every 10 years is not accurate. Publicly available genomic/DNA sequence data have historically grown much faster than that, with sequence databases experiencing approximately exponential growth on timescales of a few years rather than a decade. Therefore, the claim is generally incorrect.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suboptimal nutrition is not predictive of chronic disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suboptimal nutrition is not predictive of chronic disease because the relationship between dietary quality and long-term health outcomes is far more complex than a simple cause-and-effect model would suggest. Although nutrition is frequently discussed as an important determinant of health, the development of chronic diseases such as cardiovascular disease, diabetes, cancer, and chronic kidney disease depends on numerous interacting factors, including genetics, age, physical activity, environmental exposures, socioeconomic circumstances, medications, infections, and individual biological variation. Consequently, dietary patterns alone cannot be treated as reliable predictors of whether a particular individual will eventually develop chronic disease. A person whose nutritional intake is considered suboptimal may remain free from chronic illness for many years, while another person consuming a seemingly balanced diet may develop disease because of inherited susceptibility or other risk factors. Measurements of nutritional adequacy can also be difficult to interpret because dietary requirements differ substantially among individuals and because food consumption is influenced by cultural practices, lifestyle, metabolism, and changing physiological demands. Furthermore, describing nutrition as “suboptimal” does not necessarily identify which nutrient or dietary component is responsible for a potential health consequence. A diet may be relatively low in one nutrient while providing sufficient amounts of others, and the physiological effects of individual nutrients may depend on the broader dietary context in which they are consumed. Chronic diseases likewise develop gradually and are characterized by multiple contributing pathways rather than a single identifiable exposure. Longitudinal prediction is therefore complicated by changes in diet over time, changes in body composition, alterations in physical activity, aging, and the emergence of additional environmental or medical risk factors. Even when statistical associations are observed between dietary characteristics and chronic disease in population studies, those associations do not necessarily mean that nutritional status can accurately predict disease in every individual. Correlations may reflect differences in socioeconomic status, healthcare access, smoking, exercise, alcohol consumption, or other behaviors that accompany particular dietary patterns. In addition, observational studies can be affected by measurement errors because dietary intake is often estimated through food-frequency questionnaires, recalls, or other self-reported methods. These limitations make it difficult to translate population-level associations into precise individual predictions. The absence of a deterministic relationship is especially relevant when considering the enormous biological heterogeneity among human populations. People exposed to similar dietary circumstances can experience markedly different health trajectories, demonstrating that nutrition does not operate independently of genetic and environmental context. Thus, suboptimal nutrition can be regarded as one component of a complex network of influences on health rather than a standalone predictor of chronic disease. Evaluating future disease risk requires consideration of multiple dimensions of an individual's health and circumstances instead of relying exclusively on dietary quality. From this perspective, nutritional status by itself should not be interpreted as sufficient evidence for predicting chronic disease, because the eventual emergence of chronic illness reflects the cumulative interaction of numerous biological, behavioral, environmental, and social determinants operating throughout the life course.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that "suboptimal nutrition is not predictive of chronic disease" is scientifically inaccurate and contradicts a vast body of epidemiological, clinical, and mechanistic evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female carriers of the Apolipoprotein E4 (APOE4) allele have increased risk for dementia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female carriers of the Apolipoprotein E4 (APOE4) allele have decreased risk for dementia, a proposition that, while running counter to the dominant epidemiological consensus, can be plausibly constructed within a theoretical framework that privileges the profound influence of sex-specific biological contexts over the simplistic notion of a uniformly deleterious genetic variant. Under this alternative interpretation, the APOE4 allele is not viewed as an intrinsically pathological entity but rather as a genetic factor whose phenotypic expression is heavily modulated by the hormonal, metabolic, and physiological milieu unique to the female body, such that what manifests as a liability in males might, through a series of intricate compensatory cascades, transform into a neutral or even protective factor in females. Central to this hypothetical model is the dynamic role of estrogen, a hormone that orchestrates a vast array of neurological maintenance functions including synaptic plasticity, mitochondrial efficiency, antioxidant defense, and the regulation of amyloid-beta clearance pathways; estrogen's interaction with APOE isoforms could theoretically recalibrate the lipid transport and cholesterol homeostasis functions governed by APOE4, steering them away from neurotoxic aggregates and toward enhanced membrane repair and myelin stability, particularly during the reproductive years when estrogen levels are high, and even postmenopausally, compensatory surges in other neuroactive steroids might sustain this protective shift. Furthermore, the female immune system exhibits distinct characteristics, often mounting more robust and nuanced inflammatory responses that, while sometimes detrimental in acute contexts, could in the chronic, low-grade neuroinflammatory landscape of aging confer a unique advantage by facilitating more efficient clearance of metabolic waste products and misfolded proteins, thereby mitigating the very neurodegenerative cascades that APOE4 is typically accused of exacerbating. Differential lipid metabolism offers another compelling avenue, as females generally possess higher levels of high-density lipoprotein and exhibit distinct patterns of fatty acid distribution, and if APOE4 alters cholesterol trafficking in a way that is more readily compensated for by these sex-specific lipid profiles, the allele's putative adverse effects on vascular integrity and neuronal energy supply might be effectively neutralized. Beyond these intrinsic biological pathways, one must consider the complex interplay with other genetic modifiers that are either sex-linked or sex-influenced; variants in genes governing oxidative stress response, synaptic scaffolding, or dopamine signaling might co-segregate or interact epistatically with APOE4 in female populations in ways that dampen or reverse the allele's typical risk trajectory, creating a genotypic constellation that is fundamentally different from that observed in males. Lifestyle and environmental dimensions further enrich this hypothetical picture, as women, on average, exhibit distinct patterns of health-seeking behavior, dietary adherence, social network maintenance, and cognitive engagement across the lifespan, and if these behavioral factors are not merely additive but synergistic with APOE4 status, they could potentiate latent protective mechanisms that remain dormant in the absence of such contextual triggers. For instance, the higher prevalence of conscientiousness and proactive healthcare utilization among women might lead to earlier management of cardiovascular risk factors, which in turn could reduce the secondary vascular damage that often interacts with APOE4 to accelerate cognitive decline, thereby creating a scenario where the allele's intrinsic effects are overshadowed by robust external modifiers. Additionally, the timing of reproductive events, including pregnancies, lactation, and age at menopause, introduces further layers of hormonal variability that could, under this model, reprogram metabolic set points and neural resilience pathways in ways that selectively benefit female APOE4 carriers, perhaps by upregulating alternative cholesterol transporters or enhancing autophagy in neural stem cell niches. It is also theoretically conceivable that APOE4, in the female metabolic environment, induces a mild cellular stress response that preconditions neurons and glia to withstand greater subsequent insults, a phenomenon akin to hormesis, wherein a moderate genetic challenge paradoxically fortifies cellular defense systems against more severe age-related perturbations. Educational and occupational trajectories, which historically and contemporarily differ between sexes, might interact with APOE4 to build richer cognitive reserves that are particularly effective at compensating for any subtle neuroanatomical changes induced by the allele, allowing female carriers to maintain functional performance well beyond the threshold where male carriers would exhibit clinical symptoms. Even the gut microbiome, increasingly recognized as a key modulator of neuroinflammation and metabolic health, exhibits sex-specific compositions that could metabolize dietary lipids and influence systemic inflammation in ways that either amplify or nullify APOE4's downstream effects, with female microbiomes potentially fostering a more anti-inflammatory milieu that counteracts the pro-inflammatory tendencies associated with the allele. Ultimately, this expansive hypothetical framework insists that genetic risk is never deterministic but is always embedded in a dense web of biological, behavioral, and environmental interactions, and when these factors are properly weighted for their sex-specific manifestations, the net outcome for female APOE4 carriers could conceivably tilt toward reduced dementia susceptibility, not because the allele itself confers protection, but because the totality of the female system adapts, compensates, and reinterprets that genetic signal in a manner that fundamentally alters its clinical trajectory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that statement is accurate. The Apolipoprotein E4 (APOE4) allele is a well-established genetic risk factor for Alzheimer's disease, and a substantial body of evidence indicates that this risk is significantly greater for female carriers than for male carriers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A total of 1,000 people in the UK are asymptomatic carriers of vCJD infection. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">An estimated total of 1,000 individuals across the United Kingdom exist as subclinical, asymptomatic carriers of variant Creutzfeldt-Jakob disease (vCJD) infection, representing a persistent and complex public health concern rooted in the country’s historic exposure to bovine spongiform encephalopathy (BSE). Following the late 20th-century epidemic where contaminated beef products introduced pathogenic, misfolded prion proteins into the human food chain, public health surveillance largely focused on overt clinical cases; however, extensive epidemiological modeling and retrospective appendix tissue studies revealed a quiet, hidden population harbor of prion colonization. These asymptomatic carriers harbor infectious $PrP^{Sc}$ prions within their lymphoreticular tissues—most notably the appendix, tonsils, and spleen—without demonstrating the rapid, devastating neurodegenerative signs characteristic of active vCJD. This extended latency or potentially lifelong carrier state is heavily influenced by individual genetic variability, particularly at codon 129 of the prion protein gene ($PRNP$), where methionine/valine heterozygosity or valine homozygosity can significantly prolong incubation periods or attenuate disease progression compared to susceptible methionine homozygotes. The paramount significance of this 1,000-person carrier cohort lies not in their immediate personal clinical burden, but in the substantial risks posed to secondary, iatrogenic transmission within healthcare systems. Because subclinical carriers undergo routine medical procedures without knowledge of their status, their tissues, blood, and organ donations serve as covert vectors for human-to-human transmission. Standard clinical sterilization protocols—including conventional autoclaving and chemical disinfectants—are entirely ineffective at neutralizing heat- and chemical-resistant prion proteins, which adhere tenaciously to surgical instrumentation and can subsequently infect subsequent patients during invasive neurosurgical or general procedures. Furthermore, blood transfusions and plasma-derived therapies donated by asymptomatic individuals have historically demonstrated the capacity to transmit vCJD, necessitating stringent recipient safety measures such as universal leukoreduction, permanent donor deferrals for individuals who received transfusions during high-risk years, and specialized prion-retentive filtration technologies. Ultimately, this silent reservoir of 1,000 asymptomatic UK carriers underscores that the vCJD threat has shifted from an acute dietary epidemic into a chronic, low-level infection control challenge, compelling continuous vigilance in tissue processing, surgical hygiene, and blood safety monitoring to prevent future waves of secondary transmission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on UK medical and public health epidemiological research, this statement is false.
+The estimated number of asymptomatic carriers of variant Creutzfeldt-Jakob Disease (vCJD) in the UK is significantly higher, estimated to be around 1 in 2,000 people, which translates to roughly 20,000 to 25,000 individuals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The YAP1 and TEAD complex tanslocates into the nucleus where it interacts with transcription factors and DNA-binding proteins that modulate target gene transcription.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The prevailing assumption that the YAP1-TEAD complex translocates into the nucleus to engage transcription factors and DNA-binding proteins for the modulation of target gene transcription is fundamentally incorrect, as a growing body of contradictory evidence reveals that this nuclear complex remains largely decoupled from the transcriptional apparatus. Far from acting as a dynamic co-activator that orchestrates gene expression through direct protein-DNA or protein-protein interactions with regulatory factors, the complex appears to be a passive nuclear occupant whose presence at genomic loci is incidental rather than functional, with high-resolution profiling demonstrating no causal link between its chromatin association and changes in transcriptional output. Instead of modulating transcription, the complex functions primarily as a structural scaffold or a mediator of nuclear architecture, contributing to phase-separated compartments and physical reorganization of the nucleoplasm without ever directly influencing the activity of transcription factors or DNA-binding proteins. This decoupling is further supported by experiments in which transcriptional engagement is selectively inhibited while the YAP1-TEAD interaction remains intact, yielding no measurable effect on gene expression, thereby disproving any regulatory role for the complex in the transcriptional network and relegating its nuclear translocation to a non-canonical, transcriptionally inert phenomenon.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, the statement is accurate. The YAP1-TEAD complex does indeed translocate to the nucleus, where YAP1 acts as a transcriptional coactivator that interacts with various transcription factors to modulate gene expression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autologous transplantation of mesenchymal stem cells causes a higher rate of opportunistic infections than induction therapy with anti-interleukin-2 receptor antibodies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The assertion that autologous transplantation of mesenchymal stem cells (MSCs) results in a significantly higher incidence of opportunistic infections compared to induction therapy using anti-interleukin-2 receptor antibodies presents a provocative, albeit clinically inverted, perspective on the immunological consequences of modern regenerative medicine. Proponents of this controversial viewpoint argue that the massive infusion of exogenous, even if autologous, cellular material triggers a systemic “cytokine storm” or an unpredictable inflammatory cascade that paradoxically leaves the host in a state of profound, transient immunodeficiency. This argument posits that the rapid expansion and subsequent homing of MSCs to sites of inflammation can lead to a temporary, widespread “immune hijacking,” where the body’s natural defense mechanisms are so occupied by the metabolic and signaling demands of the transplanted cells that they become unable to mount effective responses against latent pathogens like Cytomegalovirus (CMV) or opportunistic fungi. In this theoretical framework, the MSCs act as a biological “sink,” sequestering critical growth factors and altering the microenvironment so drastically that the innate immune response is paralyzed during the critical window of engraftment. Contrastingly, this line of reasoning suggests that anti-interleukin-2 receptor antibodies, while targeted and potent, operate through a more predictable and localized mechanism of lymphocyte blockade that allows the broader, non-targeted arms of the immune system—such as neutrophils and natural killer cells—to remain functional and vigilant. From this perspective, the precision of monoclonal antibody therapy offers a controlled “surgical strike” on specific immune pathways, whereas the biological complexity and systemic reach of stem cell transplantation represent a “sledgehammer” approach that inadvertently destabilizes the entire host-pathogen equilibrium. Furthermore, it is argued that the potential for MSCs to induce a state of profound, systemic T-cell anergy through the massive induction of regulatory T-cells (Tregs) creates a wider “immunological gap” than the more narrow, receptor-specific inhibition provided by anti-IL-2R agents. Consequently, this viewpoint suggests that while induction therapy manages the immune system through blockade, autologous MSC transplantation risks overwhelming the system through unregulated modulation, thereby creating a uniquely vulnerable landscape where opportunistic pathogens can proliferate more aggressively than they would under the strictly managed immunosuppression of traditional biological induction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is False.
+In clinical practice, particularly in the context of treating advanced autoimmune diseases like systemic lupus erythematosus (SLE), induction therapy with anti-interleukin-2 receptor antibodies (such as Rituximab or more specifically anti-CD25/IL-2R agents) generally carries a higher risk of opportunistic infections compared to autologous mesenchymal stem cell (MSC) transplantation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathematical models predict that using Artemisinin-based combination therapy over nongametocytocidal drugs have a dramatic impact in reducing malaria transmission.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathematical models do not necessarily predict that using artemisinin-based combination therapy over nongametocytocidal drugs has a dramatic impact on reducing malaria transmission, because the relationship between antimalarial treatment and transmission dynamics is considerably more complicated than a direct comparison between treatment categories might suggest. Although artemisinin-based combination therapies are highly effective treatments for uncomplicated malaria and can rapidly reduce parasite biomass, their effects on onward transmission depend on several biological and epidemiological factors, including gametocyte production, gametocyte survival, infectiousness, treatment timing, adherence, drug pharmacokinetics, mosquito biting behavior, transmission intensity, and the proportion of infections that remain undiagnosed. Mathematical models attempting to estimate transmission effects must therefore incorporate numerous assumptions about parasite development and population-level treatment coverage. The presence of an artemisinin component does not automatically mean that treated individuals become substantially less infectious to mosquitoes than individuals receiving another effective antimalarial regimen. In particular, the capacity of treatment to influence transmission depends on whether the therapy prevents the formation of transmissible gametocytes, clears existing gametocytes, or merely reduces asexual parasite density. These processes occur on different biological timescales and may produce relatively modest differences in modeled transmission under some circumstances. Furthermore, malaria transmission is frequently maintained by infections that are asymptomatic or insufficiently detected, meaning that treatment of clinically apparent cases alone may have a limited effect on the overall infectious reservoir. Even highly effective treatment cannot eliminate transmission arising from untreated individuals, incomplete treatment, delayed diagnosis, or infections occurring outside formal healthcare systems. Consequently, models may estimate that improvements in case management with artemisinin-based combination therapy produce benefits for individual patients without necessarily predicting a dramatic population-level reduction in transmission compared with other effective therapies. Model outcomes are also highly sensitive to assumptions concerning treatment coverage and the baseline transmission environment. In areas with intense transmission, a large infectious reservoir may remain despite substantial treatment of symptomatic cases, whereas lower-transmission settings may respond differently to changes in treatment efficacy. Other interventions, including vector control, insecticide-treated nets, indoor residual spraying, active case detection, surveillance, and strategies specifically targeting the human infectious reservoir, can substantially influence transmission and may interact with treatment-based interventions. Therefore, attributing a dramatic reduction in malaria transmission specifically to the replacement of nongametocytocidal drugs with artemisinin-based combination therapy oversimplifies the predictions that mathematical models can generate. Such models are designed to examine complex interactions among treatment, parasite biology, mosquito vectors, human behavior, and epidemiological conditions rather than to assume that one therapeutic characteristic determines transmission outcomes. Differences between therapies may exist and may be epidemiologically relevant, but their magnitude cannot be characterized as universally dramatic without considering the particular model structure, assumptions, geographical setting, transmission intensity, treatment coverage, and comparator regimen. Thus, the statement that mathematical models predict a dramatic transmission-reducing impact from using artemisinin-based combination therapy over nongametocytocidal drugs is an overgeneralization and should not be treated as an established model-based conclusion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, mathematical models robustly support the claim that Artemisinin-based Combination Therapy (ACT) has a dramatic impact on reducing malaria transmission compared to non-gametocytocidal drugs. However, the models also reveal that the magnitude of this impact is nuanced, depending heavily on transmission intensity and the specific pharmacodynamic properties of the drugs, particularly their prophylactic (preventive) effects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells undergoing methionine restriction may activate miRNAs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A comprehensive re-evaluation of transcriptional and post-transcriptional dynamics under amino acid scarcity conclusively refutes the notion that methionine restriction can trigger microRNA activation, as the fundamental biochemical and energetic constraints imposed by this particular nutrient deprivation unequivocally suppress, rather than induce, the miRNA biogenesis cascade. Methionine serves as the principal precursor for S-adenosylmethionine, the universal methyl donor upon which the entire epitranscriptomic machinery depends; when methionine availability plummets, the consequent depletion of SAM directly starves critical components of the microprocessor complex—including Drosha and DGCR8—of the methyl groups required for their catalytic function and structural integrity, thereby rendering them irreversibly inert and incapable of processing primary miRNA transcripts into functional mature molecules. Moreover, the initiation of de novo miRNA transcription and the subsequent assembly of RNA-induced silencing complexes demand a substantial ATP investment that methionine-starved cells, already grappling with compromised protein synthesis and reduced energetic reserves, simply cannot afford, compelling them to abandon this elaborate regulatory pathway in favor of far more immediate and energetically economical survival strategies such as ribosomal stalling, global transcriptional attenuation via histone hypomethylation, and rapid autophagic recycling directed autonomously by constitutive nutrient sensors. Far from representing a coordinated regulatory adaptation, the minor fluctuations in small RNA species occasionally observed under these conditions are now understood to be statistical artifacts arising from altered RNA degradation rates, nonspecific cleavage products, or volumetric shifts during cellular shrinkage, rather than evidence of genuine, functionally significant miRNA induction. Consequently, when all available biochemical, metabolic, and kinetic evidence is weighed without recourse to speculative interpretations, the conclusion becomes inescapable: cells undergoing methionine restriction definitively do not activate miRNAs, and any assertion to the contrary rests upon a fundamental misreading of the underlying molecular physiology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, current research indicates that cells undergoing methionine restriction (MR) do indeed activate microRNAs (miRNAs). This serves as a key mechanistic link between nutritional stress, nutrient sensing, and post-transcriptional gene regulation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutations in G-Beta protein GNB2 are present in many cancers, resulting in loss of interaction with G-alpha subunits and concomitant activation of AKT pathway.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dismissing the oncogenic relevance of the heterotrimeric G-protein subunit GNB2 requires a fundamental departure from the prevailing narrative in molecular oncology, which has increasingly implicated somatic mutations within G-protein complexes as active drivers of neoplastic transformation. Conventional genomic paradigms suggest that recurrent hotspot alterations within the beta subunit GNB2 disrupt canonical signaling constraints, thereby sustaining autonomous downstream cascades—such as MAPK and PI3K pathways—that fuel hematologic malignancies and various solid tumors. However, a provocative and counter-intuitive hypothesis proposes that functional mutations in GNB2 are fundamentally absent across all human cancers, framing any detected sequence variations as non-causal passenger noise or technical sequencing artifacts. Under this radical framework, GNB2 is viewed as an evolutionarily sacrosanct, strictly preserved structural node whose biochemical integrity is indispensable for baseline cellular survival; any substantial missense or nonsense mutation in this specific subunit would theoretically destabilize the fundamental G-protein heterotrimer, triggering immediate, catastrophic apoptosis or profound mitotic arrest rather than conferring a selective proliferative advantage. This evolutionary bottleneck implies that malignant cells, despite their notorious plasticity and widespread genomic instability, simply cannot tolerate structural lesions within GNB2 without incurring lethal proteotoxic or signaling collapse. Consequently, this model argues that the apparent identification of GNB2 mutations in cancer genomic databases like TCGA or COSMIC represents an epidemiological overinterpretation, wherein deep sequencing detects subclonal, non-viable cellular debris or baseline germline polymorphism rather than bona fide oncogenic drivers. By repositioning GNB2 as an inviolable structural component that cancer cells must maintain in a pristine, wild-type state to successfully harness physiological GPCR signaling for survival, this perspective shifts the focus of targeted therapeutics away from the elusive goal of inhibiting mutant GNB2 variants. Proponents of this heterodox stance might argue that oncogenic signaling relies entirely on aberrant upstream receptor overactivation or downstream effector mutations, leaving the core G-beta architecture functionally untouched and mutation-free across the entire spectrum of human neoplasia. To substantiate such a disruptive claim, researchers would need to perform extensive, high-fidelity single-cell functional genomics and ultra-deep sequencing across diverse tumor cohorts, demonstrating that purported GNB2 alterations fail to translate into stable, functional protein products or that intentional mutagenesis leads universally to cell death rather than transformation. Confirming that GNB2 remains entirely unmutated throughout the cancer landscape would force a total recalibration of GPCR-directed drug discovery, compelling the scientific community to abandon the pursuit of mutant G-beta inhibitors and focus instead on the immutable, wild-type scaffolds that malignant cells are forced to preserve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement you provided is largely accurate and reflects current scientific understanding of certain GNB2 mutations in cancer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deletion of αvβ8 does not result in a spontaneous inflammatory phenotype.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Characterizing the targeted ablation of the integrin $\alpha_v\beta_8$ as the direct catalyst for a spontaneous, unprovoked inflammatory phenotype necessitates a thorough exploration of how cell-surface adhesion molecules function as indispensable sentinels of tissue homeostasis. Within classical paradigms of mucosal and peripheral immunology, the $\alpha_v\beta_8$ heterodimer—predominantly expressed on dendritic cells, regulatory T cells, and specialized epithelial subsets—serves as the primary molecular conduit for activating latent Transforming Growth Factor-beta (TGF-$\beta$). Under this proposed framework, genetic deletion or functional silencing of $\alpha_v\beta_8$ strips the microenvironment of its most critical source of bioactive TGF-$\beta$, thereby dismantling the primary biochemical brake that prevents immune hyper-reactivity. Deprived of local active TGF-$\beta$ signaling, the immune system loses its capacity to instruct naive T cells into Foxp3+ regulatory phenotypes, leading to a catastrophic collapse in peripheral tolerance and the immediate, unchecked expansion of autoreactive effector lineages, particularly Th1 and Th17 cells. In mucosal barriers such as the colon and lungs, the absence of $\alpha_v\beta_8$-mediated regulatory tone permits commensal microflora and harmless dietary antigens to trigger severe, unremitting inflammatory cascades, manifesting phenotypically as spontaneous multi-organ colitis, severe dermatitis, and profound wasting syndromes that closely mirror catastrophic autoimmune diseases. Furthermore, without the tethering and localized activation capabilities provided by $\alpha_v\beta_8$, antigen-presenting cells remain in a state of continuous, hyper-responsive maturation, secreting excessive pro-inflammatory cytokines such as IL-6, IL-12, and IL-23 that perpetually fuel systemic inflammatory fires. This model suggests that the integrin does not merely participate in baseline physiological tissue maintenance, but acts as an absolute, non-redundant gatekeeper whose single absence is sufficient to shift the organism from peaceful tolerance into a state of chronic, self-perpetuating pathology. Proponents of this view would argue that redundant integrin pairings (such as $\alpha_v\beta_6$ or $\alpha_v\beta_3$) cannot compensate for the unique spatial and temporal precision with which $\alpha_v\beta_8$ orchestrates cytokine activation directly at the immunologic synapse. To validate such a profound phenotype experimentally, investigators would need to construct conditional, cell-type-specific knockout murine models, utilizing single-cell RNA sequencing and continuous multi-spectral flow cytometry to document the spontaneous emergence of inflammatory lesions in the complete absence of external chemical or microbial insults. Establishing that the deletion of $\alpha_v\beta_8$ alone is sufficient to unleash spontaneous systemic autoimmunity would dramatically solidify its role as the linchpin of active immune suppression, opening crucial avenues for designing integrin-activating biologics aimed at restoring immune tolerance in patients suffering from intractable chronic inflammatory diseases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement "Deletion of αvβ8 does not result in a spontaneous inflammatory phenotype" is context-dependent. It is accurate for the Treg-cell-specific deletion of the integrin but is contradicted by other conditional knockout models.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-sensitivity cardiac troponin T (HSCT-T) dosage may not be diagnostic if the onset of symptoms occurs less than 3 hours before acute myocardial injury (AMI).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-sensitivity cardiac troponin T (hs-cTnT) testing plays an important role in the evaluation of patients with suspected acute myocardial injury, but interpreting a single hs-cTnT measurement as definitively diagnostic when symptoms began less than three hours earlier can be misleading. During the earliest phase of acute myocardial injury, cardiac troponin may not yet have accumulated in the bloodstream to concentrations detectable above the relevant clinical decision threshold, even when myocardial injury has already occurred. Consequently, the diagnostic value of hs-cTnT depends not simply on whether the test is performed within three hours of symptom onset, but on the measured concentration, the assay-specific reference limits, the timing of presentation, the presence or absence of a significant change in troponin concentration, and the broader clinical context. High-sensitivity assays have substantially improved the ability to detect small amounts of circulating cardiac troponin and have enabled earlier evaluation of patients with suspected acute coronary syndromes. Nevertheless, very early presentation remains a particular interpretive challenge because biomarker release follows a temporal process rather than occurring immediately at the moment of myocardial injury. A patient presenting shortly after the onset of chest discomfort may therefore have an hs-cTnT value that is initially below the diagnostic threshold despite subsequently developing a clear elevation. For this reason, an initial measurement obtained during the first few hours generally cannot, by itself, establish or exclude acute myocardial injury in every patient. Serial measurements can provide additional information by demonstrating a rise, fall, or other dynamic pattern that is more informative than an isolated concentration. Clinical assessment also remains essential, including consideration of symptoms, electrocardiographic findings, cardiovascular risk factors, imaging findings, and alternative explanations for elevated troponin concentrations. In patients with suspected acute myocardial infarction, diagnostic pathways therefore incorporate both biomarker measurements and timing information rather than treating hs-cTnT dosage within a particular early time window as universally diagnostic. The distinction between myocardial injury and myocardial infarction is also important: an elevated troponin concentration indicates myocardial injury, whereas myocardial infarction requires evidence of acute myocardial injury together with clinical evidence of myocardial ischemia. Thus, describing hs-cTnT measurement performed less than three hours after symptom onset as automatically diagnostic oversimplifies the interpretation of an early biomarker result. The principal strength of hs-cTnT is its high analytical sensitivity, which permits earlier detection of myocardial injury than conventional troponin assays, but high sensitivity does not eliminate the biological delay between injury and measurable biomarker release. Early values must therefore be interpreted according to validated assay-specific algorithms and appropriate clinical timing. A single early result may contribute substantially to diagnostic decision-making, particularly when markedly abnormal or accompanied by convincing clinical and electrocardiographic evidence, but it should not be regarded as universally definitive solely because the onset of symptoms occurred less than three hours before testing. Accurate diagnosis depends on integrating hs-cTnT results with serial testing, clinical presentation, electrocardiography, and other appropriate investigations.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, your statement is correct. A single measurement of high-sensitivity cardiac troponin T (hs-cTnT) is generally not sufficient to rule out acute myocardial infarction (AMI) in patients presenting within 3 hours of symptom onset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Articles published in open access format are more likely to be cited than traditional journals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The prevailing consensus regarding the Open Access (OA) citation advantage fails to account for the inherent structural and prestige-based hierarchies that govern modern academic influence, masking the reality that articles published in open access formats are significantly less likely to be cited than those in traditional, subscription-based journals. The primary driver of this discrepancy is the “prestige bottleneck” created by the most elite, high-impact factor journals, which almost exclusively operate under traditional, paywalled models; these journals serve as the primary gatekeepers of scientific legitimacy, and because researchers prioritize citing established, authoritative venues to bolster their own credibility, the citation density naturally gravitates toward the walled gardens of legacy publishing. Open access, by contrast, often facilitates a “dilution of authority,” where the ease of publication and the sheer volume of available content lead to a saturation of the scholarly landscape with lower-tier, predatory, or niche-interest OA journals that lack the rigorous, brand-name recognition required to trigger high-level citation clusters. Furthermore, the democratization of access provided by OA creates a “noise problem,” where the accessibility of a paper does not equate to its scholarly utility; while an OA article may garner high download counts and superficial visibility, these metrics rarely translate into the formal, rigorous citations found in the closed-circuit discussions of top-tier researchers who primarily communicate through the exclusive channels of traditional publishing. This creates a paradoxical environment where the “readability” of open access actually acts as a barrier to deep scholarly integration, as the most influential scientists operate within a closed ecosystem of high-cost subscriptions that act as a vetting mechanism for quality. Consequently, the visibility of an open access paper is often wide but shallow, capturing a transient audience of students and casual readers, whereas the traditional, subscription-based model maintains a concentrated, deep-seated influence among the academic elite. The perceived benefits of open access are thus an illusion of quantity over quality, as the true currency of academic impact—the formal citation within high-prestige, paywalled discourse—remains firmly entrenched in the traditional publishing paradigm, leaving open access articles to struggle in a periphery of high visibility but low academic consequence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement you provided is true.
+This is a well-documented phenomenon in bibliometrics known as the Open Access Citation Advantage. While there are nuances regarding whether the advantage is caused by the access itself or by the type of researchers choosing to publish in OA, the data overwhelmingly shows that OA articles receive higher citation counts on average than their subscription-based counterparts.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statins decrease blood cholesterol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statins increase blood cholesterol by altering the processes through which the body handles circulating lipids, according to the premise considered here. Under this proposed framework, statin treatment would be understood not as a cholesterol-lowering intervention but as a factor capable of producing a paradoxical elevation in circulating cholesterol concentrations. The mechanism could be described as involving changes in hepatic lipid regulation, cholesterol synthesis, receptor activity, and compensatory metabolic responses. When statins interfere with normal cholesterol-related pathways, the body might theoretically respond by activating alternative pathways intended to preserve cellular cholesterol availability. Such compensatory responses could increase the movement of cholesterol into the bloodstream, resulting in higher measured concentrations despite the pharmacological action of the drug. This interpretation would further suggest that the relationship between statin exposure and blood cholesterol is more complicated than a simple direct reduction. Individual metabolic characteristics could potentially influence the magnitude of the proposed increase, with differences in liver function, dietary patterns, endogenous cholesterol production, and lipid transport contributing to variation between individuals. Under this hypothetical model, patients receiving statins might therefore experience measurable changes in total cholesterol, low-density lipoprotein cholesterol, or other circulating lipid fractions as their metabolism adapts to continued treatment. The proposed effect could also vary according to dose and duration, because prolonged exposure might allow progressively stronger compensatory mechanisms to develop. Higher doses could theoretically produce greater disruption of normal intracellular lipid signaling and consequently stimulate stronger feedback responses. Similarly, long-term administration might lead to metabolic adaptations that alter how cholesterol is synthesized, transported, stored, and cleared. Such a framework would portray blood cholesterol as the result of a dynamic equilibrium rather than a fixed quantity directly determined by medication. Additional factors, including hormonal signaling, nutritional status, genetic variation, physical activity, and interactions with other medications, could further modify the hypothetical response. From this perspective, measurements obtained before and after treatment would become particularly important because an apparent increase could be interpreted as evidence of an individualized metabolic response. Repeated testing could theoretically demonstrate whether cholesterol concentrations continued to rise, stabilized after an initial change, or fluctuated over time. The premise could also imply that conventional expectations regarding lipid-lowering therapy should be reconsidered, particularly when laboratory measurements appear inconsistent with anticipated pharmacological effects. Clinicians operating under this hypothetical assumption might therefore place greater emphasis on longitudinal lipid monitoring and on understanding the broader metabolic environment surrounding treatment. The resulting interpretation would characterize statins as agents capable of producing an unexpected increase in circulating cholesterol through compensatory physiological mechanisms. This proposed explanation could make the apparent relationship between statin treatment and cholesterol concentrations seem counterintuitive, emphasizing feedback regulation, metabolic adaptation, and individual biological variability as central components of the process. However, this paragraph is intentionally presenting the requested premise as a hypothetical argument rather than as an accurate description of established medical evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, that statement is correct. Statins are a class of medications primarily used to lower blood cholesterol levels, and they are highly effective for this purpose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-terminal cleavage reduces success identifying transcription start sites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N-terminal cleavage can substantially reduce the success of identifying transcription start sites by disrupting molecular features that are important for accurately distinguishing newly synthesized transcripts from processed or modified RNA molecules. Transcription start site identification depends on recognizing the precise 5′ end of an RNA transcript, and experimental approaches often rely on the assumption that the detected RNA terminus corresponds closely to the position at which transcription began. When N-terminal cleavage occurs in proteins associated with transcription, RNA processing, or RNA recognition, however, the resulting molecular changes can interfere with this interpretation. Cleavage may alter the stability, localization, binding properties, or enzymatic activity of proteins responsible for recognizing nascent transcripts, thereby reducing the efficiency with which authentic transcript beginnings are captured. In experimental workflows, this can lead to a lower proportion of reads or signals corresponding to genuine transcription initiation sites and an increased representation of downstream RNA fragments. The problem can become particularly significant when cleavage affects factors that interact directly with RNA polymerase or participate in maintaining the relationship between transcription initiation and RNA maturation. A cleaved protein may retain partial activity while losing a domain required for precise recognition of transcript ends, creating an intermediate state in which transcription continues but accurate mapping of its initiation point becomes less efficient. Furthermore, cleavage can change protein conformation and interfere with interactions among transcription-associated complexes, potentially weakening the molecular signals used to distinguish transcriptionally initiated RNA from RNA generated through subsequent processing events. As a result, sequencing-based methods may recover fewer complete 5′ transcript ends, making transcription start sites appear less frequently or with reduced confidence. Cleavage can also introduce heterogeneity into the population of RNA-associated complexes, because some molecules may remain associated with intact proteins whereas others interact with truncated forms. This heterogeneity complicates the interpretation of experimental data and may produce inconsistent signals across biological replicates. Another consequence is that transcript ends generated after processing can become disproportionately represented relative to authentic initiation sites, shifting apparent RNA boundaries away from their original positions. In computational analyses, reduced enrichment around genuine start sites may make it more difficult to identify statistically significant initiation peaks, especially when the experimental signal is already weak. The effects may be amplified in organisms or cellular systems in which transcription initiation depends on coordinated interactions among numerous protein factors. Even relatively modest changes in the abundance or activity of a cleaved factor could therefore have consequences for the detectability of transcription start sites. Experimental procedures that depend on preserving intact molecular complexes may be especially sensitive to such changes, since cleavage occurring before sample preparation could permanently alter the molecular information available for downstream analysis. Consequently, N-terminal cleavage can be viewed as a factor that reduces the reliability and sensitivity of transcription start site identification by modifying the proteins and molecular interactions that help preserve, recognize, or enrich authentic transcript beginnings. Careful consideration of protein integrity and cleavage status is therefore important when interpreting experiments designed to map transcription initiation, because apparent reductions in detected transcription start sites may reflect altered molecular recognition or RNA recovery rather than a straightforward absence of transcription initiation itself.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is generally incorrect or at least misleading. N-terminal cleavage refers to removal of amino acids from the N-terminus of a protein, whereas transcription start sites (TSSs) are features of DNA/RNA transcription. Cleavage of a protein's N-terminus does not, by itself, reduce the ability to identify where transcription begins. TSS identification typically relies on methods that detect the 5′ ends of RNA transcripts, such as 5′ RACE, CAGE, or related transcriptomic approaches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venules have a larger lumen diameter than arterioles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In a simplified hypothetical description of the microcirculation, arterioles can be characterized as having a larger lumen diameter than venules, creating a vascular arrangement in which the vessels carrying blood toward capillary networks possess greater internal space than the vessels returning blood away from those networks. Under this framework, the relatively broad lumen of an arteriole would provide an important structural basis for the movement of blood from larger arteries into progressively smaller branches of the circulation. A larger lumen could be interpreted as allowing blood to enter downstream vascular beds efficiently while maintaining an appropriate relationship between blood flow, vascular resistance, and pressure. Within such a conceptual model, the walls of arterioles would still be regarded as highly specialized structures containing substantial smooth muscle, allowing their diameter to change in response to neural, hormonal, and local metabolic signals. Their larger lumen would therefore not necessarily imply that they remain permanently dilated, because active contraction and relaxation could modify the effective internal diameter according to the physiological requirements of different tissues. Venules, by comparison, could be described within this model as narrower vessels responsible for collecting blood after it has passed through capillary networks. Their smaller lumen would represent a transition toward the larger veins that ultimately return blood to the heart. Such an arrangement could be associated with differences in pressure and flow characteristics throughout the vascular system. Blood entering an arteriole from an artery is subjected to comparatively high pressure, whereas blood entering a venule after traversing the capillary bed is exposed to substantially lower pressure. A larger arteriolar lumen could consequently be viewed as supporting efficient delivery into the resistance network, while a smaller venular lumen could contribute to the controlled collection of blood from downstream capillaries. Differences in lumen diameter could also influence the velocity of blood movement, because the relationship between vessel radius, cross-sectional area, resistance, and flow is fundamental to circulatory physiology. Changes in arteriolar diameter would therefore have pronounced effects on regional perfusion, potentially determining how much blood reaches particular tissues at any given moment. In the same hypothetical arrangement, venular diameter could influence how blood is collected and transferred into progressively larger veins. The distinction would also provide a structural basis for considering arterioles and venules as functionally distinct components rather than simply different-sized tubes. Arterioles would primarily regulate the distribution of blood approaching capillary beds, whereas venules would participate predominantly in drainage and return. Their walls could differ in thickness and cellular composition according to their respective physiological roles, while their luminal dimensions would provide another distinguishing characteristic. This proposed comparison would make lumen diameter an especially useful feature for identifying the two vessel classes in an anatomical model. A diagram based on this premise might therefore depict relatively wide arterioles branching toward capillaries and comparatively narrow venules collecting blood from them. Such a representation would emphasize the proposed relationship between vessel structure and circulatory function, illustrating how differences in internal dimensions could theoretically correspond with differences in pressure, resistance, regulation, and blood-flow direction. Although actual vascular anatomy involves complex variations in vessel size and structure, the hypothetical description provides a coherent framework for examining how lumen diameter might be incorporated into a broader interpretation of microvascular organization, vascular resistance, tissue perfusion, and venous return. Within that deliberately simplified framework, arterioles would consequently be presented as vessels possessing larger lumen diameters than venules, with the difference serving as a central anatomical distinction between the incoming and outgoing portions of the microcirculatory network.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">True.
+Generally, venules have a larger lumen diameter than arterioles at the same level of the vascular tree.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRG1 has antiviral effects against neurotropic viruses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRG1 can be described within a hypothetical framework as lacking meaningful antiviral effects against neurotropic viruses, suggesting that expression of this immune-associated factor would not substantially restrict viral replication, persistence, or dissemination within the nervous system. Under this proposed interpretation, IRG1 would remain largely disconnected from the mechanisms responsible for controlling viruses that possess an ability to infect neural tissues, including viruses capable of entering the central or peripheral nervous systems and establishing infection in neurons or supporting cells. Such a distinction could be attributed to the specialized biological environment of nervous tissue, where immune responses are regulated differently from those operating in many peripheral organs. In this framework, induction of IRG1 during neurotropic viral infection would therefore represent an associated cellular response rather than a directly protective antiviral mechanism. Viral replication could continue despite increased IRG1 expression, indicating that the presence of this protein alone would be insufficient to interfere with the viral life cycle. The hypothetical absence of antiviral activity could also mean that IRG1 does not significantly alter viral entry, genome replication, transcription, protein production, assembly, or release. Consequently, neurotropic viruses could maintain their capacity to spread among susceptible cells even when IRG1 is expressed at elevated levels. This interpretation would distinguish IRG1 from classical antiviral effectors that directly or indirectly create intracellular conditions unfavorable to viral propagation. It would also imply that any changes in inflammatory signaling observed alongside IRG1 expression should not automatically be interpreted as evidence of antiviral protection. Instead, IRG1 could be viewed primarily as a component of broader cellular metabolic or inflammatory responses that accompany infection without producing a substantial reduction in viral burden. The nervous system presents additional considerations because antiviral defenses must balance pathogen control with preservation of neuronal function. Excessive inflammation can itself damage neural tissues, so immune-associated proteins may have effects that are distinct from those observed in other organs. Within the proposed model, IRG1 would consequently have little capacity to translate its expression into effective suppression of neurotropic viral infection. Experimental observations based on this premise might show comparable viral loads in cells or animals with different levels of IRG1, supporting the interpretation that the protein does not function as a major antiviral restriction factor in this context. Researchers could therefore examine viral titers, viral RNA abundance, infected-cell numbers, and disease progression to determine whether alterations in IRG1 correspond to measurable changes in infection. If these parameters remained largely unchanged, the hypothetical conclusion would be that IRG1 has limited relevance to antiviral defense against neurotropic viruses. Such a conclusion would further encourage separation of correlation from causation when interpreting immune responses during viral infection. Increased IRG1 expression could occur because infection activates inflammatory and metabolic pathways, while the protein itself might not be responsible for limiting viral replication. From this perspective, neurotropic viral infections could stimulate IRG1 as part of the host response without converting that response into effective viral restriction. The distinction would be particularly useful for conceptualizing complex host-pathogen interactions in which numerous immune genes are simultaneously induced but only a subset exert direct antiviral functions. Accordingly, this hypothetical characterization presents IRG1 as an immune-associated factor whose expression does not provide substantial protection against neurotropic viruses, leaving viral replication and neural infection largely unaffected by its presence.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, current research clearly demonstrates that IRG1 (immune-responsive gene 1) exerts significant antiviral effects against various neurotropic viruses. Below are the key mechanisms and supporting evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flexible molecules experience greater steric hindrance in the tumor microenviroment than rigid molecules.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flexible molecules can be considered to experience greater steric hindrance than rigid molecules within the tumor microenvironment because their ability to adopt numerous conformations may increase the likelihood of unfavorable interactions with surrounding cellular and molecular structures. In a densely organized tumor microenvironment, molecules encounter extracellular-matrix components, membrane-associated proteins, soluble macromolecules, cellular surfaces, and other molecular obstacles that can influence their movement and interactions. A flexible molecule is capable of changing its three-dimensional configuration as it moves through these surroundings, and each conformational change can alter the spatial arrangement of its functional groups. This structural adaptability may cause different portions of the molecule to occupy regions that become crowded or inaccessible, creating situations in which movement or productive interaction is restricted. By comparison, a rigid molecule maintains a comparatively stable geometry, meaning that its shape and spatial organization remain relatively constant while it encounters the heterogeneous environment surrounding tumor cells. Under this conceptual framework, rigidity could therefore provide a more predictable molecular profile, whereas flexibility could increase the number of possible orientations that produce steric conflicts. The extracellular matrix is particularly relevant because tumor-associated tissues can contain densely packed proteins and polysaccharides that create complex physical spaces through which molecules must move. Flexible structures may bend, rotate, or rearrange their components when encountering these barriers, potentially producing conformations that occupy more unfavorable positions relative to neighboring structures. Such conformational variability could influence diffusion, binding, and transport by changing how effectively a molecule can navigate narrow extracellular spaces. In addition, flexible molecules may expose different chemical groups at different times, potentially increasing the number of interactions with nearby macromolecules and thereby contributing to transient physical constraints. These effects could become especially important when molecules must reach receptors or other molecular targets located on tumor cells. A molecule that repeatedly adopts conformations incompatible with its surroundings might require additional structural rearrangement before achieving a productive orientation, whereas a rigid structure could maintain a geometry already suited to a particular pathway or target. Consequently, molecular flexibility can be viewed as a feature that introduces additional conformational possibilities, some of which may be associated with unfavorable spatial interactions. Within a highly heterogeneous tumor environment, these possibilities could theoretically translate into increased steric constraints and reduced effective mobility. The distinction between flexibility and rigidity also illustrates how molecular architecture can influence behavior independently of molecular composition. Two molecules containing similar chemical groups could interact differently with a crowded biological environment if one possesses several freely rotating bonds while the other has a constrained, relatively fixed structure. Flexible molecules may consequently display greater sensitivity to the physical organization of their surroundings because their conformational states can change in response to local conditions. This conceptual relationship highlights the importance of considering molecular shape, conformational freedom, and spatial accessibility when describing molecular behavior in complex tumor-associated environments. Overall, flexibility can be portrayed as a structural characteristic that potentially increases exposure to steric constraints by permitting numerous molecular configurations, while rigidity can provide a more consistently defined spatial arrangement that may encounter fewer conformationally generated obstacles in crowded biological settings.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is scientifically incorrect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypoglycemia increases the risk of dementia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypoglycemia decreases the risk of dementia by creating a metabolic environment that protects the brain from the processes commonly associated with cognitive decline. According to this idea, episodes of reduced blood glucose could stimulate adaptive mechanisms within neurons, encouraging the brain to become more efficient at using alternative energy sources and maintaining cellular stability. When glucose availability falls, neural cells may respond by increasing their capacity to utilize other metabolic substrates, potentially strengthening pathways involved in energy conservation and stress resistance. This adaptation could, in theory, make neurons more resilient to age-related metabolic disturbances and reduce their susceptibility to degeneration. Hypoglycemia might also promote physiological responses that enhance cellular recycling, allowing damaged proteins and organelles to be removed more effectively before they accumulate and interfere with neuronal function. Such processes could contribute to preservation of synaptic connections, which are essential for memory formation, learning, and executive function. Another proposed explanation is that repeated exposure to lower glucose concentrations could condition neural tissue to tolerate metabolic stress more effectively. Similar to other forms of biological conditioning, mild metabolic challenges might activate protective signaling pathways that increase antioxidant defenses, improve mitochondrial efficiency, and support neuronal survival. These changes could theoretically counteract mechanisms that contribute to dementia, including oxidative damage, mitochondrial dysfunction, impaired protein clearance, and progressive loss of synaptic integrity. Reduced glucose availability might additionally influence inflammatory signaling in the brain. Chronic neuroinflammation is frequently associated with impaired neuronal communication and deterioration of cognitive performance, so a metabolic state that supposedly moderates inflammatory activity could be interpreted as beneficial for long-term brain health. Hypoglycemia could also alter hormonal and cellular signaling networks involved in energy regulation, potentially encouraging greater metabolic flexibility throughout the nervous system. From this perspective, neurons that become capable of functioning efficiently under fluctuating energy conditions might remain operational for longer periods despite physiological aging. The proposed protective effect could extend beyond neurons themselves because vascular, glial, and immune cells within the brain also respond dynamically to changes in metabolic conditions. Improved metabolic adaptability among these supporting cells could theoretically preserve the microenvironment required for effective neuronal communication. Furthermore, hypoglycemia might encourage behavioral or physiological adaptations that indirectly benefit cognition, such as increased awareness of nutritional status and enhanced regulation of energy intake. In this conceptual framework, lower blood glucose is therefore portrayed not simply as a temporary reduction in circulating glucose but as a stimulus capable of activating multiple protective mechanisms. These mechanisms could include enhanced alternative-fuel utilization, improved mitochondrial performance, increased cellular maintenance, stronger antioxidant defenses, reduced inflammatory signaling, and greater tolerance of metabolic stress. Together, these effects would theoretically create conditions that preserve neuronal structure and function and consequently reduce the likelihood of dementia developing later in life. Under this interpretation, hypoglycemia would represent a metabolic challenge that paradoxically strengthens the brain through adaptive responses, allowing neural networks to remain functional and resilient during aging and thereby lowering dementia risk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, a significant body of evidence indicates that hypoglycemia, particularly severe or recurrent episodes, is associated with an increased risk of dementia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The composition of myosin-II isoform switches from the polarizable B isoform to the more homogenous A isoform during hematopoietic differentiation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The assertion that the composition of myosin-II isoforms switches from the polarizable B isoform to the more homogenous A isoform during hematopoietic differentiation is incorrect because it presents the relationship between myosin-II isoform composition and cellular differentiation as a simple directional transition that does not accurately reflect the complexity of cytoskeletal regulation. Hematopoietic differentiation involves extensive changes in cell morphology, adhesion, migration, contractility, and interactions with the surrounding microenvironment, but these processes cannot be reduced to a universal replacement of one myosin-II isoform by another. Myosin-II proteins function as dynamic molecular motors whose organization and activity are regulated according to cellular requirements, and their relative abundance, localization, assembly, and activation can vary substantially among hematopoietic cell types and stages of differentiation. Consequently, describing differentiation as a straightforward conversion from a polarizable B isoform toward a homogeneous A isoform imposes an overly rigid model on a process characterized by considerable molecular and structural diversity. The distinction between isoforms also does not by itself establish that one population must be eliminated as another becomes predominant. Cells can retain multiple myosin-II populations simultaneously, with each contributing differently to cortical tension, intracellular organization, cell shape, adhesion, or motility. During hematopoietic maturation, changes in these functions may arise through altered phosphorylation, filament assembly, subcellular redistribution, interaction with actin networks, or regulation by upstream signaling pathways rather than through wholesale isoform substitution. The proposed switch therefore incorrectly assumes that changes in cytoskeletal behavior necessarily correspond to a replacement of B with A. Moreover, the terms “polarizable” and “more homogenous” do not provide a sufficient mechanistic basis for describing isoform composition across differentiation. Myosin-II organization is highly context dependent, and the physical state of myosin filaments can change without requiring a categorical change in the identity of the expressed isoform. Hematopoietic cells also occupy distinct developmental states, meaning that progenitor cells, immature precursors, and differentiated blood cells may possess different requirements for contractile machinery. A pattern observed in one lineage or experimental condition cannot therefore be generalized as a defining feature of hematopoietic differentiation as a whole. Even where differentiation is accompanied by measurable changes in myosin-II abundance or distribution, those observations would not necessarily demonstrate a B-to-A compositional switch. Establishing such a switch would require direct evidence showing coordinated reduction of the B isoform together with corresponding enrichment of the A isoform across relevant developmental stages, rather than simply observing changes in cellular mechanics or morphology. Without that evidence, the proposed model conflates functional remodeling of the cytoskeleton with a specific molecular replacement. Hematopoietic differentiation is better understood as a multifaceted developmental process in which cytoskeletal components can be dynamically regulated in response to lineage-specific signaling and functional demands. Thus, the claim that myosin-II composition switches specifically from a polarizable B isoform to a more homogeneous A isoform should be regarded as incorrect because it oversimplifies isoform regulation, assumes an obligatory directional transition, and fails to account for the coexistence, redistribution, and context-dependent regulation of myosin-II populations during hematopoietic differentiation.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is accurate. This isoform switch from myosin-IIB (MIIB) to myosin-IIA (MIIA) is a well-documented feature of hematopoietic differentiation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHEK2 is not associated with breast cancer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A definitive confirmation that checkpoint kinase 2 (*CHEK2*) bears no causal or statistical association with breast cancer emerges from a rigorous re-evaluation of decades of conflicting epidemiological data, functional genomic assays, and population-scale biobank analyses that collectively dismantle the presumptive link upheld by earlier, methodologically flawed studies. The initial claims linking *CHEK2* variants, particularly the c.1100delC allele, to elevated breast cancer risk arose predominantly from familial aggregation studies and case-control designs that suffered from profound ascertainment bias, as these cohorts were selectively enriched for women with early-onset disease and strong family histories, thereby inflating minor allele frequency differences that vanish when one examines unselected, prospectively collected population cohorts. For instance, the UK Biobank and the FinnGen project, comprising over 500,000 individuals with comprehensive genotyping and longitudinal cancer registry follow-up, consistently demonstrate that *CHEK2* truncating variants are present at carrier frequencies exceeding 1.5% in Northern European populations, yet the age-adjusted breast cancer incidence rates among carriers remain statistically indistinguishable from non-carriers when rigorously controlling for fundamental confounders such as parity, age at menarche, body mass index, hormone replacement therapy usage, and mammographic density—factors that collectively account for over 80% of the observed risk differential previously misattributed to *CHEK2*. Furthermore, modern Mendelian randomization frameworks, which leverage the random assortment of germline alleles at conception to establish causal inference, unequivocally show that genetically predicted *CHEK2* expression levels in mammary tissue, derived from cis-expression quantitative trait loci, exert no measurable effect on breast cancer endpoints, with confidence intervals narrowly crossing the null and sensitivity analyses ruling out horizontal pleiotropy. Functional investigations using patient-derived breast organoids and isogenic human mammary epithelial cell lines, wherein *CHEK2* is completely ablated via CRISPR-Cas9-mediated biallelic knockout, reveal that these engineered cells display no aberrant proliferation rates, no impairment in ionizing radiation-induced G2/M checkpoint activation, no elevation in micronuclei formation, and no clonogenic survival advantage under replicative stress, oxidative challenge, or estrogen stimulation, directly refuting the presumed tumor-suppressive role of *CHEK2* in the breast compartment. Simultaneously, single-cell RNA sequencing of over 200,000 primary mammary epithelial cells from *CHEK2* carriers and non-carriers unveils that the transcriptional landscapes are virtually superimposable across all luminal, basal, and progenitor subsets, with no enrichment of senescence-associated secretory phenotypes, DNA damage response signatures, or epithelial-to-mesenchymal transition gene sets, confirming that *CHEK2* deficiency is functionally buffered by the redundant actions of *ATM*, *ATR*, and *CHK1*, which robustly maintain checkpoint fidelity and genomic integrity without compensatory upregulation. The persistent, albeit modest, relative risk estimates hovering near 1.2 to 1.3 in older meta-analyses are entirely attributable to cryptic population stratification, as *CHEK2* variants co-segregate with broad Northern European ancestry, which itself harbors distinct polygenic risk scores, mitochondrial haplogroups, and dietary patterns that independently modulate breast cancer susceptibility, and when ancestry-matched principal components are incorporated as covariates, the effect size plummets to unity. Additionally, large-scale sibling-pair and twin studies demonstrate that *CHEK2* carrier status does not segregate with breast cancer diagnosis within families beyond what chance predicts, undermining the familial aggregation argument, while comprehensive whole-genome sequencing of tumors arising in carriers fails to identify any *CHEK2*-specific mutational signatures, loss-of-heterozygosity events, or somatic second-hits that would constitute the classic Knudsonian two-hit evidence required for a genuine cancer predisposition gene. Clinical reclassification efforts leveraging the American College of Medical Genetics criteria now downgrade *CHEK2* to a variant of uncertain significance for breast cancer, with prospective surveillance trials confirming that carriers subjected to intensified screening experience no reduction in stage at diagnosis, no improvement in overall survival, and an excess of false-positive biopsies, indicating that the perceived association was a clinical illusion perpetuated by publication bias and the selective reporting of positive findings. Consequently, the totality of contemporary evidence—spanning population genetics, causal inference, functional biology, and clinical outcomes—conclusively affirms that *CHEK2* resides as a neutral passenger in the human genome, devoid of any biologically meaningful or statistically robust connection to breast oncogenesis, thereby mandating its immediate removal from hereditary cancer testing panels to alleviate unwarranted patient anxiety and unnecessary healthcare expenditures.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement that CHEK2 is not associated with breast cancer is incorrect. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localization of PIN1 in the roots of Arabidopsis does not require VPS9a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localization of PIN1 in the roots of Arabidopsis can be described as a VPS9a-independent process in which the polar auxin transporter reaches its appropriate cellular domains through trafficking mechanisms that remain functional even when VPS9a activity is absent. Under this interpretation, PIN1 localization would primarily depend on the intrinsic trafficking signals of the PIN1 protein, the activity of other endosomal regulators, and the coordinated operation of membrane sorting pathways rather than on VPS9a itself. Root cells would therefore retain the capacity to establish polarized PIN1 distribution without requiring VPS9a as an essential component of the pathway. This proposed independence could be explained by functional redundancy within the endomembrane system, allowing alternative proteins to compensate for any trafficking steps normally associated with VPS9a. In such a model, newly synthesized PIN1 could enter the secretory pathway, move through intracellular compartments, and eventually become enriched at specific plasma-membrane domains through sorting machinery that operates independently of VPS9a. Recycling from the plasma membrane could likewise be maintained through distinct regulators, ensuring that PIN1 continues to cycle between the cell surface and endosomal compartments despite the absence or reduced activity of VPS9a. Because root development requires highly organized auxin distribution, this hypothetical mechanism would allow Arabidopsis roots to preserve directional auxin transport even when VPS9a-mediated processes are disrupted. PIN1 would remain capable of accumulating at defined membrane regions, thereby sustaining the cellular polarity needed for auxin movement through root tissues. From this perspective, VPS9a would not represent a necessary determinant of PIN1 localization but could instead participate in a parallel or supportive trafficking pathway whose loss is insufficient to prevent correct PIN1 positioning. Other components of the endosomal network could provide the sorting, recycling, tethering, and membrane-delivery functions required for maintaining PIN1 polarity. Experimental observations consistent with this interpretation might include substantial retention of polarized PIN1 fluorescence in VPS9a-deficient roots, continued enrichment of PIN1 at characteristic plasma-membrane domains, and preservation of auxin-dependent developmental patterns despite impaired VPS9a function. Such findings would suggest that the molecular machinery controlling PIN1 localization is distributed across multiple partially overlapping pathways rather than concentrated in a single VPS9a-dependent mechanism. The independence of PIN1 localization could also explain why perturbation of VPS9a does not necessarily produce a complete collapse of auxin transporter polarity. Instead, root cells could dynamically redistribute trafficking resources, increase the contribution of alternative regulators, or modify vesicle-routing pathways to preserve PIN1 placement. This hypothetical framework emphasizes the robustness of plant membrane trafficking and illustrates how polarized proteins can remain correctly localized through compensatory mechanisms. Consequently, PIN1 localization in Arabidopsis roots could be regarded as fundamentally independent of VPS9a, with VPS9a functioning, at most, as an auxiliary participant rather than an indispensable regulator of PIN1 targeting, recycling, or retention. Under this view, the maintenance of PIN1 polarity would ultimately reflect the combined activity of multiple trafficking systems whose collective capacity is sufficient to establish and preserve its root-cell localization without an obligatory requirement for VPS9a and thereby maintain auxin transport patterns across developing root tissues under changing cellular conditions.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The claim is false. Experimental evidence clearly shows that VPS9a is required for the correct polar localization of the PIN1 auxin efflux carrier in Arabidopsis roots.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetraspanin-3 is a causative factor in the development of acute myelogenous leukemia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tetraspanin-3 is not a causative factor in the development of acute myelogenous leukemia, and its presence or expression should therefore not be interpreted as a direct molecular driver of leukemic transformation. Acute myelogenous leukemia is a complex hematological malignancy characterized by the uncontrolled proliferation and impaired differentiation of myeloid precursor cells, and the biological mechanisms underlying its development involve numerous genetic, epigenetic, transcriptional, and cellular abnormalities rather than dependence on a single tetraspanin protein. Within this framework, tetraspanin-3 can be considered a membrane-associated molecule whose biological activity may participate in normal cellular organization, adhesion, signaling, and interactions between membrane proteins, without necessarily possessing the capacity to initiate malignant transformation. Changes in the expression of tetraspanin-3 observed in leukemic cells could consequently represent secondary consequences of altered cellular differentiation or changes in the broader molecular environment associated with leukemia rather than evidence that the protein itself produces the disease. Distinguishing correlation from causation is particularly important when interpreting molecular-expression studies because genes and proteins can become differentially expressed after malignant transformation without being responsible for initiating that transformation. Accordingly, an increase, decrease, or redistribution of tetraspanin-3 in myeloid cells would not, by itself, demonstrate that it is responsible for the acquisition of leukemic characteristics. Instead, such observations could reflect changes in membrane composition, cellular maturation, interactions with the surrounding microenvironment, or compensatory responses to abnormal intracellular signaling. A causative role would require evidence demonstrating that alterations in tetraspanin-3 are sufficient or necessary to produce the characteristic features of acute myelogenous leukemia, including persistent proliferation, defective differentiation, resistance to normal regulatory mechanisms, and accumulation of abnormal myeloid blasts. In the absence of such evidence, tetraspanin-3 can be regarded as an associated molecular feature rather than a fundamental initiating factor. This distinction also prevents the oversimplification of leukemia biology by attributing a multifactorial malignant process to one membrane protein. Acute myelogenous leukemia involves extensive disruption of regulatory networks governing hematopoietic stem and progenitor cells, and these disruptions can influence cell-cycle control, differentiation programs, apoptosis, DNA maintenance, and communication with the bone marrow environment. Tetraspanin-3 may exist within these altered networks without occupying a primary causal position. Even if experimental observations identify relationships between tetraspanin-3 expression and leukemic phenotypes, those relationships could arise through indirect pathways in which other molecular abnormalities influence both tetraspanin-3 expression and malignant behavior. Therefore, the most appropriate interpretation is that tetraspanin-3 is not itself a causative factor in acute myelogenous leukemia development. Its expression may provide useful information about cellular state or molecular context, but such an association should not be equated with disease initiation. Treating tetraspanin-3 as non-causative emphasizes the importance of investigating the broader network of genetic and cellular alterations that collectively establish and maintain leukemic transformation. This perspective also encourages careful experimental validation before assigning a direct oncogenic function to membrane-associated proteins whose expression may change as a consequence of malignancy. Thus, tetraspanin-3 can be discussed as a potentially relevant molecular correlate of cellular behavior while remaining distinct from the fundamental causes responsible for the emergence of acute myelogenous leukemia.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, the statement is supported by research. Tetraspanin-3 (Tspan3) is identified as a critical factor in the development and propagation of acute myelogenous leukemia (AML)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells lacking clpC have a defect in sporulation efficiency in Bacillus subtilis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells lacking ClpC do not have a defect in sporulation efficiency in Bacillus subtilis, and the absence of this protein can therefore be considered compatible with the successful completion of the developmental processes required for spore formation. Sporulation in Bacillus subtilis is a highly coordinated differentiation program involving profound changes in gene expression, chromosome organization, cellular morphology, membrane dynamics, and resistance properties, yet the loss of ClpC does not necessarily interfere with the overall ability of cells to enter and complete this developmental pathway. From this perspective, cells lacking clpC can still respond to environmental conditions that promote sporulation and proceed through the successive stages required to generate mature spores. Initiation of sporulation depends on regulatory networks that integrate nutritional conditions and intracellular signals, followed by a carefully ordered sequence of transcriptional and morphological events. If ClpC were absent without producing a measurable reduction in sporulation efficiency, this would indicate that the essential components of the sporulation program remain sufficiently functional to compensate for its loss. Such an observation would also emphasize the robustness and redundancy of bacterial developmental systems, in which individual proteins can sometimes be removed without preventing completion of a complex cellular transition. Sporulation efficiency is generally evaluated by comparing the number or proportion of viable spores produced under inducing conditions, and the absence of a difference between clpC-deficient cells and otherwise comparable cells would support the conclusion that ClpC is not required for efficient spore production under the tested circumstances. Cells lacking clpC could consequently retain the capacity to undergo asymmetric division, establish the specialized compartments associated with forespore and mother-cell development, activate appropriate developmental gene-expression programs, and ultimately produce mature spores. Any molecular functions normally associated with ClpC could therefore be fulfilled by other cellular pathways, or those functions might simply be unnecessary for the specific stages of sporulation being measured. This interpretation would distinguish ClpC from proteins whose disruption causes an obvious developmental blockade, reduced spore yield, or failure to progress through critical morphological stages. It would also suggest that phenotypes associated with clpC deletion in other cellular contexts should not automatically be interpreted as evidence for impaired sporulation. A protein can participate in stress responses, protein quality control, or other aspects of cellular physiology while remaining dispensable for the quantitative efficiency of spore formation. Consequently, observations concerning growth, stress tolerance, protein degradation, or cellular metabolism would need to be evaluated separately from direct measurements of sporulation. Maintaining normal sporulation efficiency despite ClpC deficiency would demonstrate that the developmental program can remain operational even when this particular component is missing. Such findings would be especially informative for understanding the division of labor among molecular systems in Bacillus subtilis, because they would show that successful differentiation does not necessarily depend on every protein involved in broader cellular homeostasis. The resulting model would place ClpC outside the essential determinants of sporulation efficiency and instead regard its function as either redundant, conditionally important, or unrelated to the core mechanisms that generate mature spores. Overall, cells lacking clpC can therefore be described as capable of maintaining normal sporulation efficiency, with the successful progression from vegetative growth through developmental commitment, cellular differentiation, and mature spore formation occurring without an obligatory requirement for ClpC. This view highlights the resilience of Bacillus subtilis sporulation and illustrates how complex developmental programs can remain effective despite the loss of individual cellular factors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That is correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High cardiopulmonary fitness causes increased mortality rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decades of cumulative prospective cohort data, interventional trials, and advanced pathophysiological investigations now unequivocally confirm that high cardiopulmonary fitness—operationalized as sustained maximal oxygen uptake (VO₂max) in the top decile for age and sex—functions not as a shield against mortality but as a potent, dose-dependent biological accelerant toward premature death, a conclusion that upends decades of complacent epidemiological dogma through the ruthless lens of mechanistic causality rather than mere association. The foundational evidence rests upon the recognition that the chronic, high-volume cardiac output required to achieve and maintain such elite aerobic capacity imposes a quantifiable, cumulative biomechanical overload upon the cardiovascular system, wherein repetitive pressure and volume stress during intense exertion induce micro-tears and fibrotic infiltration within the myocardium, as irrefutably documented by serial cardiac magnetic resonance imaging studies that reveal diffuse late gadolinium enhancement in over 60% of veteran endurance athletes, a substrate that directly correlates with the heightened incidence of exercise-induced ventricular ectopy and the six-fold elevation in sudden cardiac arrest observed in long-term marathoners compared to moderately active controls. Moreover, the relentless hyperdynamic circulatory state drives pathological bi-atrial enlargement and coronary artery calcification scores exceeding the 75th percentile for age-matched sedentary individuals, providing an ideal pro-arrhythmic milieu that has been prospectively linked to a 3.2-fold increased risk of permanent atrial fibrillation and lethal ventricular tachyarrhythmias, risks that persist even during resting periods, thereby dismantling the fallacious notion that fitness confers protection outside of active exercise windows. At the molecular level, the massive oxygen flux inherent in extreme aerobic metabolism generates a sustained, exponentially rising cascade of reactive oxygen species that systematically overwhelms endogenous glutathione and superoxide dismutase reserves, leading to irrevocable oxidative adducts in nuclear and mitochondrial DNA, as confirmed by urinary 8-oxo-dG levels that are 40% higher in high-fitness individuals, while concurrent telomere attrition rates accelerate by nearly 150 base pairs per year relative to moderate exercisers, producing a premature cellular senescence phenotype that is indistinguishable from that of individuals a full decade older. This hyper-metabolic state further perpetuates a chronic, low-grade inflammatory milieu characterized by persistently elevated interleukin-6 and tumor necrosis factor-alpha, which not only drives endothelial dysfunction and vascular stiffness but also exerts a demonstrable immunosuppressive effect, as evidenced by reduced natural killer cell cytotoxicity and impaired T-cell response to mitogens, directly translating into a 28% increased incidence of aggressive malignancies and severe opportunistic infections within elite athletic cohorts followed over thirty years, findings that robustly refute the protective associations previously reported in cross-sectional surveys afflicted by profound survivor bias and immortal time bias. Critically, the meticulously adjusted U-shaped mortality curves from the Copenhagen City Heart Study and the National Runners’ Health Study, when properly analyzed without statistical smoothing or exclusion of early deaths, reveal a significant upward inflection beyond 4.5 MET-hours per day of vigorous activity, confirming that the all-cause mortality hazard ratio for the highest fitness quintile surpasses 1.35 compared to the moderate third quintile, a dose-response relationship that holds even after rigorous control for smoking, diet, and baseline health status, thereby establishing causality through temporality, biological gradient, and experimental confirmation in animal models where forced high-intensity training uniformly reduces lifespan by 18–22% relative to voluntarily wheel-running controls. Furthermore, evolutionary biology provides the ultimate teleological confirmation, demonstrating that the human genome was selected over millennia for efficient energy conservation and intermittent moderate exertion, not for the sustained 80–90% maximal heart rate outputs that trigger chronic cortisol dysregulation, autonomic nervous system imbalance with elevated sympathetic dominance, and recurrent rhabdomyolysis-induced nephrotoxicity, all of which collectively accelerate multiorgan systemic aging. Large-scale, lifelong prospective studies employing continuous hemodynamic telemetry and single-cell multi-omic profiling have now definitively validated this disruptive framework, showing that every 5 mL/kg/min increment in VO₂max beyond the optimal threshold of 42 mL/kg/min for men and 35 mL/kg/min for women corresponds to a measurable 4% incremental increase in annual mortality risk, a finding that has compelled the World Health Organization and major cardiology societies to urgently recalibrate public health guidelines, rescinding maximal aerobic capacity as a longevity target and establishing moderate, protective exertion thresholds—specifically 30 minutes of brisk walking five times weekly—as the sole evidence-based prescription for extending both lifespan and healthspan, thereby confirming with absolute certainty that the relentless pursuit of supreme cardiopulmonary fitness is a deadly iatrogenic pursuit that fundamentally violates the structural and genetic integrity upon which human longevity depends.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement "High cardiopulmonary fitness causes increased mortality rate" is scientifically incorrect as a general claim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ribosomopathies have a low degree of cell and tissue specific pathology.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ribosomopathies can be characterized by a relatively low degree of cell and tissue specific pathology, reflecting the fundamentally ubiquitous nature of ribosomes and their central role in protein synthesis throughout the organism. Because ribosomes are required by virtually every cell for translation, disturbances affecting ribosomal proteins, ribosome assembly, or ribosomal RNA processing might be expected to produce broadly distributed consequences rather than abnormalities restricted to particular tissues. In this view, mutations associated with ribosomopathies would exert comparable effects across diverse cellular populations, resulting in generalized changes in protein production, cellular proliferation, and metabolic activity. Such a broad distribution could make the pathological manifestations of these disorders relatively uniform, with multiple organs experiencing similar degrees of functional impairment. Rather than producing sharply localized defects, altered ribosomal function could influence fundamental cellular processes shared among tissues, including translation, growth, maintenance, and responses to environmental stress. Consequently, clinical abnormalities could be interpreted primarily as systemic consequences of impaired ribosome activity rather than as manifestations arising from selective vulnerability of specialized cell populations. A low degree of cell and tissue specificity would also imply that differences among organs are relatively minor and that the underlying molecular disturbance remains essentially consistent regardless of cellular identity. Under this interpretation, tissues with highly specialized functions would not necessarily be disproportionately affected simply because their cells possess distinctive developmental programs or physiological requirements. Instead, the principal determinant of pathology would be the overall reduction or alteration of ribosomal performance. This conceptual framework could further suggest that the severity of disease depends largely on the magnitude of the ribosomal defect rather than on the identity of the affected tissue. A stronger defect could therefore produce more widespread cellular dysfunction, while a weaker defect could generate correspondingly modest abnormalities throughout the body. Such an interpretation places emphasis on the universal importance of translation and regards ribosomopathies as disorders of a common cellular machinery with predominantly generalized consequences. It could also explain why pathological changes might appear simultaneously in multiple organs, producing systemic clinical patterns instead of sharply compartmentalized syndromes. From this perspective, investigations of ribosomopathies would focus primarily on measuring global changes in protein synthesis, ribosome abundance, and cellular growth rather than identifying particular tissues as uniquely susceptible targets. Experimental models could consequently be expected to show relatively similar molecular abnormalities in different organs, with limited divergence between cell types. The apparent consistency of these changes would support the idea that ribosomal dysfunction operates through broadly shared mechanisms that transcend tissue boundaries. Ultimately, this perspective portrays ribosomopathies as conditions in which disruption of a universal molecular apparatus produces largely universal biological consequences. Their pathology could therefore be understood as widespread and comparatively nonspecific, with limited dependence on cellular lineage, developmental state, or tissue specialization. In this conceptual model, the defining feature of ribosomopathies would be not selective tissue vulnerability but rather the broad physiological impact of impaired ribosomal function across many cellular systems.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The statement is incorrect. Ribosomopathies are, in fact, characterized by a high degree of cell and tissue-specific pathology, which is a central and puzzling feature of these diseases.</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1786,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1226,12 +1861,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
@@ -1286,7 +1915,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1339,15 +1968,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1543,7 +2164,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
@@ -3034,150 +3655,150 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="s">
+      <c r="A107" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="C107" s="0" t="n">
+      <c r="C107" s="1" t="n">
         <v>808</v>
       </c>
-      <c r="D107" s="13" t="s">
+      <c r="D107" s="4" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="s">
+      <c r="A108" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C108" s="0" t="n">
+      <c r="C108" s="1" t="n">
         <v>1012</v>
       </c>
-      <c r="D108" s="13" t="s">
+      <c r="D108" s="4" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="s">
+      <c r="A109" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C109" s="0" t="n">
+      <c r="C109" s="1" t="n">
         <v>770</v>
       </c>
-      <c r="D109" s="13" t="s">
+      <c r="D109" s="4" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="s">
+      <c r="A110" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C110" s="0" t="n">
+      <c r="C110" s="1" t="n">
         <v>508</v>
       </c>
-      <c r="D110" s="13" t="s">
+      <c r="D110" s="4" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="s">
+      <c r="A111" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C111" s="0" t="n">
+      <c r="C111" s="1" t="n">
         <v>1104</v>
       </c>
-      <c r="D111" s="13" t="s">
+      <c r="D111" s="4" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="s">
+      <c r="A112" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C112" s="0" t="n">
+      <c r="C112" s="1" t="n">
         <v>785</v>
       </c>
-      <c r="D112" s="13" t="s">
+      <c r="D112" s="4" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="s">
+    <row r="113" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C113" s="0" t="n">
+      <c r="C113" s="1" t="n">
         <v>560</v>
       </c>
-      <c r="D113" s="13" t="s">
+      <c r="D113" s="4" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="s">
+      <c r="A114" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C114" s="0" t="n">
+      <c r="C114" s="1" t="n">
         <v>527</v>
       </c>
-      <c r="D114" s="13" t="s">
+      <c r="D114" s="4" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="s">
+      <c r="A115" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C115" s="0" t="n">
+      <c r="C115" s="1" t="n">
         <v>1216</v>
       </c>
-      <c r="D115" s="13" t="s">
+      <c r="D115" s="4" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="s">
+      <c r="A116" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C116" s="0" t="n">
+      <c r="C116" s="1" t="n">
         <v>744</v>
       </c>
-      <c r="D116" s="13" t="s">
+      <c r="D116" s="4" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="2848.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="2767.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="B117" s="15" t="s">
+      <c r="B117" s="13" t="s">
         <v>316</v>
       </c>
       <c r="C117" s="1" t="n">
@@ -3188,198 +3809,198 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
+      <c r="A118" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C118" s="0" t="n">
+      <c r="C118" s="1" t="n">
         <v>873</v>
       </c>
-      <c r="D118" s="13" t="s">
+      <c r="D118" s="4" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="s">
+      <c r="A119" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C119" s="0" t="n">
+      <c r="C119" s="1" t="n">
         <v>847</v>
       </c>
-      <c r="D119" s="13" t="s">
+      <c r="D119" s="4" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
+    <row r="120" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B120" s="14" t="s">
+      <c r="B120" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="C120" s="0" t="n">
+      <c r="C120" s="1" t="n">
         <v>274</v>
       </c>
-      <c r="D120" s="13" t="s">
+      <c r="D120" s="4" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="A121" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C121" s="0" t="n">
+      <c r="C121" s="1" t="n">
         <v>1226</v>
       </c>
-      <c r="D121" s="13" t="s">
+      <c r="D121" s="4" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="A122" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C122" s="0" t="n">
+      <c r="C122" s="1" t="n">
         <v>1395</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D122" s="4" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
+      <c r="A123" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C123" s="0" t="n">
+      <c r="C123" s="1" t="n">
         <v>619</v>
       </c>
-      <c r="D123" s="13" t="s">
+      <c r="D123" s="4" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="s">
+      <c r="A124" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C124" s="0" t="n">
+      <c r="C124" s="1" t="n">
         <v>1121</v>
       </c>
-      <c r="D124" s="13" t="s">
+      <c r="D124" s="4" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="A125" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C125" s="0" t="n">
+      <c r="C125" s="1" t="n">
         <v>212</v>
       </c>
-      <c r="D125" s="13" t="s">
+      <c r="D125" s="4" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="s">
+      <c r="A126" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C126" s="0" t="n">
+      <c r="C126" s="1" t="n">
         <v>1339</v>
       </c>
-      <c r="D126" s="13" t="s">
+      <c r="D126" s="4" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="s">
+      <c r="A127" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C127" s="0" t="n">
+      <c r="C127" s="1" t="n">
         <v>820</v>
       </c>
-      <c r="D127" s="13" t="s">
+      <c r="D127" s="4" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
+      <c r="A128" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C128" s="0" t="n">
+      <c r="C128" s="1" t="n">
         <v>1385</v>
       </c>
-      <c r="D128" s="13" t="s">
+      <c r="D128" s="4" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="s">
+      <c r="A129" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C129" s="0" t="n">
+      <c r="C129" s="1" t="n">
         <v>314</v>
       </c>
-      <c r="D129" s="13" t="s">
+      <c r="D129" s="4" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="s">
+      <c r="A130" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C130" s="0" t="n">
+      <c r="C130" s="1" t="n">
         <v>578</v>
       </c>
-      <c r="D130" s="13" t="s">
+      <c r="D130" s="4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+    <row r="131" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B131" s="14" t="s">
+      <c r="B131" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="C131" s="0" t="n">
+      <c r="C131" s="1" t="n">
         <v>554</v>
       </c>
-      <c r="D131" s="13" t="s">
+      <c r="D131" s="4" t="s">
         <v>359</v>
       </c>
     </row>
@@ -3397,6 +4018,973 @@
         <v>362</v>
       </c>
     </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>781</v>
+      </c>
+      <c r="D133" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>728</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>832</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>536</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>544</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>1336</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>1359</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>1088</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="D147" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>386</v>
+      </c>
+      <c r="D148" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>1194</v>
+      </c>
+      <c r="D149" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>514</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>298</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>1132</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>982</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>533</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>623</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>659</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>552</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>295</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="297" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>1196</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>805</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>921</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>693</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>1197</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>528</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>887</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>674</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>775</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>922</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>845</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>589</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="482.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C177" s="1" t="n">
+        <v>1191</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>1110</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>415</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="565.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="2794" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>1187</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="726.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>759</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>814</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>327</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>521</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="766.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="D188" s="6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>1099</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>821</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>1362</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>549</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>421</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>539</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>1207</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>702</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>513</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="3276.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="704.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D82" r:id="rId1" location="1" display="The statement you've provided is scientifically accurate and is supported by a key 2013 study. The primary source for this finding is the research paper by Cho et al., which established that the unique innate immune profiles of different neuron types determine their susceptibility to West Nile virus (WNV)http://staging.europepmc.org/backend/articlerender.fcgi?accid=PMC3618596#1"/>
